--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BDE396F-EEBE-478A-A2BD-15606BB7F8E9}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27F0A2EA-23EF-45A0-9FB9-A6372B9AD65B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12982" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12982" uniqueCount="479">
   <si>
     <t>Id</t>
   </si>
@@ -1461,6 +1461,9 @@
   <si>
     <t>% de profesores (Contrato Indefinido- Fijo) impactados plan de desarrollo docente *</t>
   </si>
+  <si>
+    <t>Porcentaje de cumplimiento del Acuerdo de Nivel de Servicio (ANS)</t>
+  </si>
 </sst>
 </file>
 
@@ -1470,7 +1473,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1482,6 +1485,17 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1516,19 +1530,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{E6474115-E034-47AA-AE39-934325146E0E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4329,8 +4346,8 @@
       <c r="A30">
         <v>193</v>
       </c>
-      <c r="B30" t="s">
-        <v>110</v>
+      <c r="B30" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
@@ -4418,8 +4435,8 @@
       <c r="A31">
         <v>193</v>
       </c>
-      <c r="B31" t="s">
-        <v>110</v>
+      <c r="B31" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
@@ -4507,8 +4524,8 @@
       <c r="A32">
         <v>193</v>
       </c>
-      <c r="B32" t="s">
-        <v>110</v>
+      <c r="B32" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
@@ -4596,8 +4613,8 @@
       <c r="A33">
         <v>193</v>
       </c>
-      <c r="B33" t="s">
-        <v>110</v>
+      <c r="B33" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C33" t="s">
         <v>30</v>
@@ -4685,8 +4702,8 @@
       <c r="A34">
         <v>193</v>
       </c>
-      <c r="B34" t="s">
-        <v>110</v>
+      <c r="B34" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C34" t="s">
         <v>30</v>
@@ -4774,8 +4791,8 @@
       <c r="A35">
         <v>193</v>
       </c>
-      <c r="B35" t="s">
-        <v>110</v>
+      <c r="B35" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C35" t="s">
         <v>30</v>
@@ -21717,8 +21734,8 @@
       <c r="A231">
         <v>193</v>
       </c>
-      <c r="B231" t="s">
-        <v>110</v>
+      <c r="B231" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C231" t="s">
         <v>30</v>
@@ -24902,8 +24919,8 @@
       <c r="A268">
         <v>193</v>
       </c>
-      <c r="B268" t="s">
-        <v>110</v>
+      <c r="B268" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C268" t="s">
         <v>30</v>
@@ -24988,8 +25005,8 @@
       <c r="A269">
         <v>193</v>
       </c>
-      <c r="B269" t="s">
-        <v>110</v>
+      <c r="B269" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C269" t="s">
         <v>30</v>
@@ -25074,8 +25091,8 @@
       <c r="A270">
         <v>193</v>
       </c>
-      <c r="B270" t="s">
-        <v>110</v>
+      <c r="B270" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C270" t="s">
         <v>30</v>
@@ -36066,8 +36083,8 @@
       <c r="A399">
         <v>193</v>
       </c>
-      <c r="B399" t="s">
-        <v>110</v>
+      <c r="B399" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="C399" t="s">
         <v>30</v>
@@ -38515,7 +38532,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC427" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27F0A2EA-23EF-45A0-9FB9-A6372B9AD65B}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E96EE34-34C1-42F2-A3EA-FB64CA3559EE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12982" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12984" uniqueCount="479">
   <si>
     <t>Id</t>
   </si>
@@ -4830,6 +4830,12 @@
       <c r="N35">
         <v>1.038888888888889</v>
       </c>
+      <c r="O35" t="s">
+        <v>58</v>
+      </c>
+      <c r="P35" t="s">
+        <v>58</v>
+      </c>
       <c r="Q35" t="s">
         <v>120</v>
       </c>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E96EE34-34C1-42F2-A3EA-FB64CA3559EE}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2DD3FCA-76C4-4C68-9F43-37319BDA03A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1940,7 +1940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2DD3FCA-76C4-4C68-9F43-37319BDA03A5}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32867299-392E-434C-A6E6-C58FED7EA18F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1940,7 +1940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32867299-392E-434C-A6E6-C58FED7EA18F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4E8B9D-A96D-476E-ADE6-C8AF4AF08F92}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1845,9 +1845,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC427"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1940,7 +1942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2029,7 +2031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2118,7 +2120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2207,7 +2209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2296,7 +2298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2474,7 +2476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>77</v>
       </c>
@@ -2563,7 +2565,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>77</v>
       </c>
@@ -2652,7 +2654,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>77</v>
       </c>
@@ -2741,7 +2743,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>77</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>96</v>
       </c>
@@ -2919,7 +2921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>96</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>96</v>
       </c>
@@ -3097,7 +3099,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>96</v>
       </c>
@@ -3186,7 +3188,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>97</v>
       </c>
@@ -3275,7 +3277,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>97</v>
       </c>
@@ -3358,7 +3360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>97</v>
       </c>
@@ -3435,7 +3437,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>97</v>
       </c>
@@ -3512,7 +3514,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>98</v>
       </c>
@@ -3595,7 +3597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>98</v>
       </c>
@@ -3684,7 +3686,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>98</v>
       </c>
@@ -3767,7 +3769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>98</v>
       </c>
@@ -3856,7 +3858,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>109</v>
       </c>
@@ -3924,7 +3926,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>109</v>
       </c>
@@ -3992,7 +3994,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -4081,7 +4083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -4170,7 +4172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -4259,7 +4261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -4342,7 +4344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>193</v>
       </c>
@@ -4431,7 +4433,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>193</v>
       </c>
@@ -4520,7 +4522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>193</v>
       </c>
@@ -4609,7 +4611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>193</v>
       </c>
@@ -4698,7 +4700,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>193</v>
       </c>
@@ -4787,7 +4789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>193</v>
       </c>
@@ -4876,7 +4878,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>194</v>
       </c>
@@ -4965,7 +4967,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>194</v>
       </c>
@@ -5054,7 +5056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>194</v>
       </c>
@@ -5143,7 +5145,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>194</v>
       </c>
@@ -5232,7 +5234,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>194</v>
       </c>
@@ -5321,7 +5323,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>200</v>
       </c>
@@ -5401,7 +5403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>200</v>
       </c>
@@ -5484,7 +5486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>202</v>
       </c>
@@ -5567,7 +5569,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>202</v>
       </c>
@@ -5644,7 +5646,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>203</v>
       </c>
@@ -5733,7 +5735,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>203</v>
       </c>
@@ -5822,7 +5824,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>203</v>
       </c>
@@ -5911,7 +5913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>203</v>
       </c>
@@ -6000,7 +6002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>203</v>
       </c>
@@ -6089,7 +6091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>203</v>
       </c>
@@ -6178,7 +6180,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>204</v>
       </c>
@@ -6267,7 +6269,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>204</v>
       </c>
@@ -6356,7 +6358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>204</v>
       </c>
@@ -6445,7 +6447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>204</v>
       </c>
@@ -6534,7 +6536,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>204</v>
       </c>
@@ -6623,7 +6625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>204</v>
       </c>
@@ -6712,7 +6714,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>205</v>
       </c>
@@ -6801,7 +6803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>205</v>
       </c>
@@ -6890,7 +6892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>205</v>
       </c>
@@ -6979,7 +6981,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>205</v>
       </c>
@@ -7068,7 +7070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>206</v>
       </c>
@@ -7157,7 +7159,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>206</v>
       </c>
@@ -7246,7 +7248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>206</v>
       </c>
@@ -7323,7 +7325,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>207</v>
       </c>
@@ -7412,7 +7414,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>207</v>
       </c>
@@ -7501,7 +7503,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>207</v>
       </c>
@@ -7590,7 +7592,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>207</v>
       </c>
@@ -7679,7 +7681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>228</v>
       </c>
@@ -7762,7 +7764,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>228</v>
       </c>
@@ -7833,7 +7835,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>244</v>
       </c>
@@ -7916,7 +7918,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>244</v>
       </c>
@@ -7999,7 +8001,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>245</v>
       </c>
@@ -8088,7 +8090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>245</v>
       </c>
@@ -8177,7 +8179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>245</v>
       </c>
@@ -8266,7 +8268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>245</v>
       </c>
@@ -8355,7 +8357,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>245</v>
       </c>
@@ -8444,7 +8446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>245</v>
       </c>
@@ -8527,7 +8529,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>274</v>
       </c>
@@ -8616,7 +8618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>274</v>
       </c>
@@ -8705,7 +8707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>274</v>
       </c>
@@ -8794,7 +8796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>274</v>
       </c>
@@ -8883,7 +8885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>274</v>
       </c>
@@ -8972,7 +8974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>274</v>
       </c>
@@ -9061,7 +9063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>276</v>
       </c>
@@ -9144,7 +9146,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>276</v>
       </c>
@@ -9227,7 +9229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>276</v>
       </c>
@@ -9310,7 +9312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>276</v>
       </c>
@@ -9393,7 +9395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>276</v>
       </c>
@@ -9476,7 +9478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>276</v>
       </c>
@@ -9559,7 +9561,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>277</v>
       </c>
@@ -9639,7 +9641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>277</v>
       </c>
@@ -9719,7 +9721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>277</v>
       </c>
@@ -9799,7 +9801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>277</v>
       </c>
@@ -9879,7 +9881,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>323</v>
       </c>
@@ -9962,7 +9964,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>323</v>
       </c>
@@ -10045,7 +10047,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>323</v>
       </c>
@@ -10128,7 +10130,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>323</v>
       </c>
@@ -10211,7 +10213,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>323</v>
       </c>
@@ -10288,7 +10290,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>325</v>
       </c>
@@ -10377,7 +10379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>325</v>
       </c>
@@ -10466,7 +10468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>325</v>
       </c>
@@ -10555,7 +10557,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>325</v>
       </c>
@@ -10632,7 +10634,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>325</v>
       </c>
@@ -10721,7 +10723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>325</v>
       </c>
@@ -10810,7 +10812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>331</v>
       </c>
@@ -10893,7 +10895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>331</v>
       </c>
@@ -10976,7 +10978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>332</v>
       </c>
@@ -11059,7 +11061,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>332</v>
       </c>
@@ -11142,7 +11144,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>332</v>
       </c>
@@ -11225,7 +11227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>332</v>
       </c>
@@ -11308,7 +11310,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>332</v>
       </c>
@@ -11397,7 +11399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>332</v>
       </c>
@@ -11480,7 +11482,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>334</v>
       </c>
@@ -11563,7 +11565,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>334</v>
       </c>
@@ -11646,7 +11648,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>335</v>
       </c>
@@ -11732,7 +11734,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>335</v>
       </c>
@@ -11812,7 +11814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>339</v>
       </c>
@@ -11901,7 +11903,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>339</v>
       </c>
@@ -11990,7 +11992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>353</v>
       </c>
@@ -12073,7 +12075,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>353</v>
       </c>
@@ -12156,7 +12158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>361</v>
       </c>
@@ -12239,7 +12241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>361</v>
       </c>
@@ -12316,7 +12318,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>364</v>
       </c>
@@ -12405,7 +12407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>364</v>
       </c>
@@ -12494,7 +12496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>364</v>
       </c>
@@ -12583,7 +12585,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>364</v>
       </c>
@@ -12672,7 +12674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>367</v>
       </c>
@@ -12761,7 +12763,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>367</v>
       </c>
@@ -12850,7 +12852,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>369</v>
       </c>
@@ -12933,7 +12935,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>369</v>
       </c>
@@ -13016,7 +13018,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>369</v>
       </c>
@@ -13105,7 +13107,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>369</v>
       </c>
@@ -13194,7 +13196,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>376</v>
       </c>
@@ -13283,7 +13285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>376</v>
       </c>
@@ -13372,7 +13374,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>376</v>
       </c>
@@ -13461,7 +13463,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>376</v>
       </c>
@@ -13550,7 +13552,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>376</v>
       </c>
@@ -13639,7 +13641,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>376</v>
       </c>
@@ -13728,7 +13730,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>377</v>
       </c>
@@ -13817,7 +13819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>377</v>
       </c>
@@ -13906,7 +13908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>377</v>
       </c>
@@ -13995,7 +13997,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>377</v>
       </c>
@@ -14084,7 +14086,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>379</v>
       </c>
@@ -14173,7 +14175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>379</v>
       </c>
@@ -14262,7 +14264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>379</v>
       </c>
@@ -14351,7 +14353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>379</v>
       </c>
@@ -14440,7 +14442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>379</v>
       </c>
@@ -14529,7 +14531,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>379</v>
       </c>
@@ -15152,7 +15154,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>423</v>
       </c>
@@ -15235,7 +15237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>423</v>
       </c>
@@ -15318,7 +15320,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>423</v>
       </c>
@@ -15401,7 +15403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>424</v>
       </c>
@@ -15484,7 +15486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>424</v>
       </c>
@@ -15567,7 +15569,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>424</v>
       </c>
@@ -15650,7 +15652,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>460</v>
       </c>
@@ -15733,7 +15735,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>463</v>
       </c>
@@ -15816,7 +15818,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>463</v>
       </c>
@@ -15899,7 +15901,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>465</v>
       </c>
@@ -15982,7 +15984,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>465</v>
       </c>
@@ -16065,7 +16067,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>466</v>
       </c>
@@ -16148,7 +16150,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>466</v>
       </c>
@@ -16231,7 +16233,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>472</v>
       </c>
@@ -16311,7 +16313,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>472</v>
       </c>
@@ -16391,7 +16393,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>476</v>
       </c>
@@ -16474,7 +16476,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>476</v>
       </c>
@@ -16557,7 +16559,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>14.1</v>
       </c>
@@ -16646,7 +16648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>14.1</v>
       </c>
@@ -16735,7 +16737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>14.1</v>
       </c>
@@ -16824,7 +16826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>14.1</v>
       </c>
@@ -16913,7 +16915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>14.1</v>
       </c>
@@ -17002,7 +17004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>14.2</v>
       </c>
@@ -17091,7 +17093,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>14.2</v>
       </c>
@@ -17180,7 +17182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>14.2</v>
       </c>
@@ -17269,7 +17271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>14.2</v>
       </c>
@@ -17358,7 +17360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>14.2</v>
       </c>
@@ -17447,7 +17449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>14.3</v>
       </c>
@@ -17536,7 +17538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>14.3</v>
       </c>
@@ -17625,7 +17627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>14.3</v>
       </c>
@@ -17714,7 +17716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>14.3</v>
       </c>
@@ -17803,7 +17805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>14.3</v>
       </c>
@@ -17892,7 +17894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>14.4</v>
       </c>
@@ -17981,7 +17983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>14.4</v>
       </c>
@@ -18070,7 +18072,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>14.4</v>
       </c>
@@ -18159,7 +18161,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>14.4</v>
       </c>
@@ -18248,7 +18250,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>14.4</v>
       </c>
@@ -18337,7 +18339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>386.1</v>
       </c>
@@ -18420,7 +18422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>386.1</v>
       </c>
@@ -18503,7 +18505,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>386.1</v>
       </c>
@@ -18592,7 +18594,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>386.1</v>
       </c>
@@ -18681,7 +18683,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>386.2</v>
       </c>
@@ -18764,7 +18766,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>386.2</v>
       </c>
@@ -18847,7 +18849,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>386.2</v>
       </c>
@@ -18936,7 +18938,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>386.2</v>
       </c>
@@ -19025,7 +19027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>386.3</v>
       </c>
@@ -19108,7 +19110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>386.3</v>
       </c>
@@ -19191,7 +19193,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>386.3</v>
       </c>
@@ -19280,7 +19282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>386.3</v>
       </c>
@@ -19369,7 +19371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>77</v>
       </c>
@@ -19458,7 +19460,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>77</v>
       </c>
@@ -19547,7 +19549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>96</v>
       </c>
@@ -19636,7 +19638,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>97</v>
       </c>
@@ -19713,7 +19715,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>97</v>
       </c>
@@ -19790,7 +19792,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>98</v>
       </c>
@@ -19867,7 +19869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>98</v>
       </c>
@@ -19956,7 +19958,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>14.1</v>
       </c>
@@ -20045,7 +20047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>14.2</v>
       </c>
@@ -20134,7 +20136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>14.3</v>
       </c>
@@ -20223,7 +20225,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>14.4</v>
       </c>
@@ -20312,7 +20314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>194</v>
       </c>
@@ -20401,7 +20403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>476</v>
       </c>
@@ -20490,7 +20492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>148</v>
       </c>
@@ -20579,7 +20581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>339</v>
       </c>
@@ -20668,7 +20670,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>325</v>
       </c>
@@ -20757,7 +20759,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>323</v>
       </c>
@@ -20846,7 +20848,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>276</v>
       </c>
@@ -20935,7 +20937,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>14</v>
       </c>
@@ -21024,7 +21026,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>379</v>
       </c>
@@ -21113,7 +21115,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>274</v>
       </c>
@@ -21202,7 +21204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>14.1</v>
       </c>
@@ -21291,7 +21293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>14.2</v>
       </c>
@@ -21380,7 +21382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>14.3</v>
       </c>
@@ -21469,7 +21471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>14.4</v>
       </c>
@@ -21558,7 +21560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>98</v>
       </c>
@@ -21647,7 +21649,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>194</v>
       </c>
@@ -21736,7 +21738,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>193</v>
       </c>
@@ -21825,7 +21827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>245</v>
       </c>
@@ -21914,7 +21916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>205</v>
       </c>
@@ -22003,7 +22005,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>204</v>
       </c>
@@ -22092,7 +22094,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>364</v>
       </c>
@@ -22181,7 +22183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>376</v>
       </c>
@@ -22270,7 +22272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>203</v>
       </c>
@@ -22359,7 +22361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>207</v>
       </c>
@@ -22448,7 +22450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>369</v>
       </c>
@@ -22537,7 +22539,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>331</v>
       </c>
@@ -22617,7 +22619,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>332</v>
       </c>
@@ -22706,7 +22708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>202</v>
       </c>
@@ -22795,7 +22797,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>77</v>
       </c>
@@ -22884,7 +22886,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>277</v>
       </c>
@@ -22972,7 +22974,7 @@
     </row>
     <row r="245" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A245">
-        <v>525</v>
+        <v>385</v>
       </c>
       <c r="B245" t="s">
         <v>435</v>
@@ -23053,7 +23055,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>525.1</v>
       </c>
@@ -23136,7 +23138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>525.20000000000005</v>
       </c>
@@ -23219,7 +23221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>525.29999999999995</v>
       </c>
@@ -23302,7 +23304,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>14</v>
       </c>
@@ -23388,7 +23390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>14</v>
       </c>
@@ -23474,7 +23476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>14</v>
       </c>
@@ -23560,7 +23562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>77</v>
       </c>
@@ -23646,7 +23648,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>77</v>
       </c>
@@ -23732,7 +23734,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>77</v>
       </c>
@@ -23818,7 +23820,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>96</v>
       </c>
@@ -23904,7 +23906,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>96</v>
       </c>
@@ -23990,7 +23992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>96</v>
       </c>
@@ -24076,7 +24078,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>97</v>
       </c>
@@ -24162,7 +24164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>97</v>
       </c>
@@ -24242,7 +24244,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>97</v>
       </c>
@@ -24322,7 +24324,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>98</v>
       </c>
@@ -24408,7 +24410,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>98</v>
       </c>
@@ -24494,7 +24496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>98</v>
       </c>
@@ -24580,7 +24582,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>109</v>
       </c>
@@ -24663,7 +24665,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>148</v>
       </c>
@@ -24749,7 +24751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>148</v>
       </c>
@@ -24835,7 +24837,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>148</v>
       </c>
@@ -24921,7 +24923,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>193</v>
       </c>
@@ -25007,7 +25009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>193</v>
       </c>
@@ -25093,7 +25095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>193</v>
       </c>
@@ -25179,7 +25181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>194</v>
       </c>
@@ -25265,7 +25267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>194</v>
       </c>
@@ -25351,7 +25353,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>194</v>
       </c>
@@ -25437,7 +25439,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>200</v>
       </c>
@@ -25514,7 +25516,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>200</v>
       </c>
@@ -25600,7 +25602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>202</v>
       </c>
@@ -25686,7 +25688,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>202</v>
       </c>
@@ -25766,7 +25768,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>203</v>
       </c>
@@ -25852,7 +25854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>203</v>
       </c>
@@ -25938,7 +25940,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>203</v>
       </c>
@@ -26024,7 +26026,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>204</v>
       </c>
@@ -26098,7 +26100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>204</v>
       </c>
@@ -26184,7 +26186,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>204</v>
       </c>
@@ -26270,7 +26272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>205</v>
       </c>
@@ -26356,7 +26358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>205</v>
       </c>
@@ -26442,7 +26444,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>206</v>
       </c>
@@ -26528,7 +26530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>206</v>
       </c>
@@ -26614,7 +26616,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>207</v>
       </c>
@@ -26700,7 +26702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>207</v>
       </c>
@@ -26786,7 +26788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>228</v>
       </c>
@@ -26872,7 +26874,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>228</v>
       </c>
@@ -26958,7 +26960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>244</v>
       </c>
@@ -27044,7 +27046,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>244</v>
       </c>
@@ -27130,7 +27132,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>244</v>
       </c>
@@ -27216,7 +27218,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>245</v>
       </c>
@@ -27302,7 +27304,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>245</v>
       </c>
@@ -27388,7 +27390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>245</v>
       </c>
@@ -27474,7 +27476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>476</v>
       </c>
@@ -27560,7 +27562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>274</v>
       </c>
@@ -27646,7 +27648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>274</v>
       </c>
@@ -27732,7 +27734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>274</v>
       </c>
@@ -27818,7 +27820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>276</v>
       </c>
@@ -27904,7 +27906,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>276</v>
       </c>
@@ -27990,7 +27992,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>276</v>
       </c>
@@ -28076,7 +28078,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>277</v>
       </c>
@@ -28159,7 +28161,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>277</v>
       </c>
@@ -28242,7 +28244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>323</v>
       </c>
@@ -28328,7 +28330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>323</v>
       </c>
@@ -28414,7 +28416,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>323</v>
       </c>
@@ -28500,7 +28502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>325</v>
       </c>
@@ -28586,7 +28588,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>325</v>
       </c>
@@ -28672,7 +28674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>325</v>
       </c>
@@ -28758,7 +28760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>331</v>
       </c>
@@ -28835,7 +28837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>331</v>
       </c>
@@ -28912,7 +28914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>332</v>
       </c>
@@ -28998,7 +29000,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>332</v>
       </c>
@@ -29084,7 +29086,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>332</v>
       </c>
@@ -29170,7 +29172,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>334</v>
       </c>
@@ -29256,7 +29258,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>334</v>
       </c>
@@ -29342,7 +29344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>334</v>
       </c>
@@ -29428,7 +29430,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>335</v>
       </c>
@@ -29511,7 +29513,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>335</v>
       </c>
@@ -29594,7 +29596,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>339</v>
       </c>
@@ -29680,7 +29682,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>339</v>
       </c>
@@ -29766,7 +29768,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>460</v>
       </c>
@@ -29843,7 +29845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>353</v>
       </c>
@@ -29929,7 +29931,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>361</v>
       </c>
@@ -30015,7 +30017,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>361</v>
       </c>
@@ -30095,7 +30097,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>364</v>
       </c>
@@ -30172,7 +30174,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>364</v>
       </c>
@@ -30258,7 +30260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>367</v>
       </c>
@@ -30344,7 +30346,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>367</v>
       </c>
@@ -30430,7 +30432,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>367</v>
       </c>
@@ -30516,7 +30518,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>369</v>
       </c>
@@ -30593,7 +30595,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>369</v>
       </c>
@@ -30679,7 +30681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>376</v>
       </c>
@@ -30765,7 +30767,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>376</v>
       </c>
@@ -30851,7 +30853,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>376</v>
       </c>
@@ -30937,7 +30939,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>377</v>
       </c>
@@ -31023,7 +31025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>377</v>
       </c>
@@ -31109,7 +31111,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>379</v>
       </c>
@@ -31195,7 +31197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>379</v>
       </c>
@@ -31281,7 +31283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>379</v>
       </c>
@@ -31395,6 +31397,9 @@
       <c r="I344" t="s">
         <v>45</v>
       </c>
+      <c r="J344">
+        <v>2</v>
+      </c>
       <c r="K344">
         <v>13361</v>
       </c>
@@ -31481,6 +31486,9 @@
       <c r="I345" t="s">
         <v>49</v>
       </c>
+      <c r="J345">
+        <v>2</v>
+      </c>
       <c r="K345">
         <v>14097.721</v>
       </c>
@@ -31567,6 +31575,9 @@
       <c r="I346" t="s">
         <v>53</v>
       </c>
+      <c r="J346">
+        <v>2</v>
+      </c>
       <c r="K346">
         <v>15507.4931</v>
       </c>
@@ -31625,7 +31636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>423</v>
       </c>
@@ -31711,7 +31722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>423</v>
       </c>
@@ -31797,7 +31808,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>423</v>
       </c>
@@ -31883,7 +31894,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>424</v>
       </c>
@@ -31969,7 +31980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>424</v>
       </c>
@@ -32055,7 +32066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>424</v>
       </c>
@@ -32141,7 +32152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>460</v>
       </c>
@@ -32227,7 +32238,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>463</v>
       </c>
@@ -32313,7 +32324,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>465</v>
       </c>
@@ -32399,7 +32410,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>466</v>
       </c>
@@ -32485,7 +32496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>466</v>
       </c>
@@ -32571,7 +32582,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>466</v>
       </c>
@@ -32657,7 +32668,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>472</v>
       </c>
@@ -32740,7 +32751,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>476</v>
       </c>
@@ -32826,7 +32837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>109</v>
       </c>
@@ -32909,7 +32920,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>14.1</v>
       </c>
@@ -32995,7 +33006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.1</v>
       </c>
@@ -33081,7 +33092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.1</v>
       </c>
@@ -33167,7 +33178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.2</v>
       </c>
@@ -33253,7 +33264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.2</v>
       </c>
@@ -33339,7 +33350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>14.2</v>
       </c>
@@ -33425,7 +33436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>14.3</v>
       </c>
@@ -33511,7 +33522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.3</v>
       </c>
@@ -33597,7 +33608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.3</v>
       </c>
@@ -33683,7 +33694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.4</v>
       </c>
@@ -33769,7 +33780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.4</v>
       </c>
@@ -33855,7 +33866,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>14.4</v>
       </c>
@@ -33941,7 +33952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>386.1</v>
       </c>
@@ -34027,7 +34038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>386.1</v>
       </c>
@@ -34113,7 +34124,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>386.2</v>
       </c>
@@ -34199,7 +34210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>386.2</v>
       </c>
@@ -34285,7 +34296,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>386.3</v>
       </c>
@@ -34371,7 +34382,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>386.3</v>
       </c>
@@ -34457,7 +34468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>228</v>
       </c>
@@ -34543,7 +34554,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>476</v>
       </c>
@@ -34629,7 +34640,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>460</v>
       </c>
@@ -34715,7 +34726,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>148</v>
       </c>
@@ -34801,7 +34812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>339</v>
       </c>
@@ -34887,7 +34898,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>325</v>
       </c>
@@ -34973,7 +34984,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>323</v>
       </c>
@@ -35059,7 +35070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>276</v>
       </c>
@@ -35145,7 +35156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>14</v>
       </c>
@@ -35231,7 +35242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>379</v>
       </c>
@@ -35317,7 +35328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>274</v>
       </c>
@@ -35403,7 +35414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>14.1</v>
       </c>
@@ -35489,7 +35500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>14.2</v>
       </c>
@@ -35575,7 +35586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>14.3</v>
       </c>
@@ -35661,7 +35672,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>14.4</v>
       </c>
@@ -35747,7 +35758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>423</v>
       </c>
@@ -35833,7 +35844,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>97</v>
       </c>
@@ -35913,7 +35924,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>98</v>
       </c>
@@ -35999,7 +36010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>194</v>
       </c>
@@ -36085,7 +36096,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>193</v>
       </c>
@@ -36171,7 +36182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>466</v>
       </c>
@@ -36257,7 +36268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>245</v>
       </c>
@@ -36343,7 +36354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>205</v>
       </c>
@@ -36429,7 +36440,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>204</v>
       </c>
@@ -36515,7 +36526,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>377</v>
       </c>
@@ -36601,7 +36612,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>367</v>
       </c>
@@ -36687,7 +36698,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="406" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>364</v>
       </c>
@@ -36773,7 +36784,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="407" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>376</v>
       </c>
@@ -36859,7 +36870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="408" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>228</v>
       </c>
@@ -36945,7 +36956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="409" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>203</v>
       </c>
@@ -37031,7 +37042,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="410" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>207</v>
       </c>
@@ -37117,7 +37128,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="411" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>361</v>
       </c>
@@ -37203,7 +37214,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>244</v>
       </c>
@@ -37289,7 +37300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>369</v>
       </c>
@@ -37375,7 +37386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>331</v>
       </c>
@@ -37452,7 +37463,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>332</v>
       </c>
@@ -37538,7 +37549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>202</v>
       </c>
@@ -37624,7 +37635,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>200</v>
       </c>
@@ -37710,7 +37721,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>109</v>
       </c>
@@ -37793,7 +37804,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>335</v>
       </c>
@@ -37876,7 +37887,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>334</v>
       </c>
@@ -37962,7 +37973,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>77</v>
       </c>
@@ -38048,7 +38059,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>424</v>
       </c>
@@ -38134,7 +38145,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>277</v>
       </c>
@@ -38219,7 +38230,7 @@
     </row>
     <row r="424" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A424">
-        <v>525</v>
+        <v>385</v>
       </c>
       <c r="B424" t="s">
         <v>435</v>
@@ -38245,6 +38256,9 @@
       <c r="I424" t="s">
         <v>404</v>
       </c>
+      <c r="J424">
+        <v>1</v>
+      </c>
       <c r="K424">
         <v>6845.8773119999996</v>
       </c>
@@ -38297,7 +38311,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>525.1</v>
       </c>
@@ -38377,7 +38391,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>525.20000000000005</v>
       </c>
@@ -38457,7 +38471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>525.29999999999995</v>
       </c>
@@ -38538,6 +38552,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC427" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Ingresos totales de educación para la vida"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{767A2A7D-6D72-4B86-AF52-9EC89A58AE9C}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8696CC5-D6A3-49E2-83AA-AAD47473D105}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12487" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12487" uniqueCount="481">
   <si>
     <t>Id</t>
   </si>
@@ -1480,6 +1480,9 @@
   <si>
     <t>Índice de Inclusión</t>
   </si>
+  <si>
+    <t>Total Matriculados antiguos</t>
+  </si>
 </sst>
 </file>
 
@@ -8294,7 +8297,7 @@
         <v>274</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C75" t="s">
         <v>194</v>
@@ -8383,7 +8386,7 @@
         <v>274</v>
       </c>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C76" t="s">
         <v>194</v>
@@ -8472,7 +8475,7 @@
         <v>274</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C77" t="s">
         <v>194</v>
@@ -8561,7 +8564,7 @@
         <v>274</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C78" t="s">
         <v>194</v>
@@ -8650,7 +8653,7 @@
         <v>274</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C79" t="s">
         <v>194</v>
@@ -8739,7 +8742,7 @@
         <v>274</v>
       </c>
       <c r="B80" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C80" t="s">
         <v>194</v>
@@ -19470,7 +19473,7 @@
         <v>274</v>
       </c>
       <c r="B204" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C204" t="s">
         <v>194</v>
@@ -21327,7 +21330,7 @@
         <v>385</v>
       </c>
       <c r="B225" t="s">
-        <v>435</v>
+        <v>309</v>
       </c>
       <c r="C225" t="s">
         <v>310</v>
@@ -21410,7 +21413,7 @@
         <v>386.1</v>
       </c>
       <c r="B226" t="s">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="C226" t="s">
         <v>310</v>
@@ -21490,10 +21493,10 @@
     </row>
     <row r="227" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A227">
-        <v>525.20000000000005</v>
+        <v>386.2</v>
       </c>
       <c r="B227" t="s">
-        <v>439</v>
+        <v>382</v>
       </c>
       <c r="C227" t="s">
         <v>310</v>
@@ -21576,7 +21579,7 @@
         <v>386.3</v>
       </c>
       <c r="B228" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="C228" t="s">
         <v>310</v>
@@ -25659,7 +25662,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C276" t="s">
         <v>194</v>
@@ -25745,7 +25748,7 @@
         <v>274</v>
       </c>
       <c r="B277" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C277" t="s">
         <v>194</v>
@@ -25831,7 +25834,7 @@
         <v>274</v>
       </c>
       <c r="B278" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C278" t="s">
         <v>194</v>
@@ -32992,7 +32995,7 @@
         <v>274</v>
       </c>
       <c r="B362" t="s">
-        <v>193</v>
+        <v>480</v>
       </c>
       <c r="C362" t="s">
         <v>194</v>
@@ -35892,7 +35895,7 @@
         <v>385</v>
       </c>
       <c r="B396" t="s">
-        <v>435</v>
+        <v>309</v>
       </c>
       <c r="C396" t="s">
         <v>310</v>
@@ -35975,7 +35978,7 @@
         <v>386.1</v>
       </c>
       <c r="B397" t="s">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="C397" t="s">
         <v>310</v>
@@ -36052,10 +36055,10 @@
     </row>
     <row r="398" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A398">
-        <v>525.20000000000005</v>
+        <v>386.2</v>
       </c>
       <c r="B398" t="s">
-        <v>439</v>
+        <v>382</v>
       </c>
       <c r="C398" t="s">
         <v>310</v>
@@ -36135,7 +36138,7 @@
         <v>386.3</v>
       </c>
       <c r="B399" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="C399" t="s">
         <v>310</v>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8696CC5-D6A3-49E2-83AA-AAD47473D105}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B4BE982-A0F4-426A-A552-CD3BDDEFDDEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1864,6 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC399"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1960,7 +1961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2049,7 +2050,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2316,7 +2317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2405,7 +2406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2494,7 +2495,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>77</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>77</v>
       </c>
@@ -2672,7 +2673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>77</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>77</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>96</v>
       </c>
@@ -2939,7 +2940,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>96</v>
       </c>
@@ -3028,7 +3029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>96</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>96</v>
       </c>
@@ -3206,7 +3207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>97</v>
       </c>
@@ -3295,7 +3296,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>97</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>97</v>
       </c>
@@ -3455,7 +3456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>97</v>
       </c>
@@ -3532,7 +3533,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>98</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>98</v>
       </c>
@@ -3704,7 +3705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>98</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>98</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>109</v>
       </c>
@@ -3944,7 +3945,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>109</v>
       </c>
@@ -4012,7 +4013,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -4101,7 +4102,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>193</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>193</v>
       </c>
@@ -4540,7 +4541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>193</v>
       </c>
@@ -4629,7 +4630,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>193</v>
       </c>
@@ -4718,7 +4719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>193</v>
       </c>
@@ -4807,7 +4808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>193</v>
       </c>
@@ -4896,7 +4897,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>194</v>
       </c>
@@ -4985,7 +4986,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>194</v>
       </c>
@@ -5074,7 +5075,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>194</v>
       </c>
@@ -5163,7 +5164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>194</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>194</v>
       </c>
@@ -5341,7 +5342,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>200</v>
       </c>
@@ -5421,7 +5422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>200</v>
       </c>
@@ -5504,7 +5505,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>202</v>
       </c>
@@ -5587,7 +5588,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>202</v>
       </c>
@@ -5664,7 +5665,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>203</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>203</v>
       </c>
@@ -5842,7 +5843,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>203</v>
       </c>
@@ -5931,7 +5932,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>203</v>
       </c>
@@ -6020,7 +6021,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>203</v>
       </c>
@@ -6109,7 +6110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>203</v>
       </c>
@@ -6198,7 +6199,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>204</v>
       </c>
@@ -6287,7 +6288,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>204</v>
       </c>
@@ -6376,7 +6377,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>204</v>
       </c>
@@ -6465,7 +6466,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>204</v>
       </c>
@@ -6554,7 +6555,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>204</v>
       </c>
@@ -6643,7 +6644,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>204</v>
       </c>
@@ -6732,7 +6733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>205</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>205</v>
       </c>
@@ -6910,7 +6911,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>205</v>
       </c>
@@ -6999,7 +7000,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>205</v>
       </c>
@@ -7088,7 +7089,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>207</v>
       </c>
@@ -7177,7 +7178,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>207</v>
       </c>
@@ -7266,7 +7267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>207</v>
       </c>
@@ -7355,7 +7356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>207</v>
       </c>
@@ -7444,7 +7445,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>228</v>
       </c>
@@ -7527,7 +7528,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>228</v>
       </c>
@@ -7598,7 +7599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>244</v>
       </c>
@@ -7681,7 +7682,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>244</v>
       </c>
@@ -7764,7 +7765,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>245</v>
       </c>
@@ -7853,7 +7854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>245</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>245</v>
       </c>
@@ -8031,7 +8032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>245</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>245</v>
       </c>
@@ -8209,7 +8210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>245</v>
       </c>
@@ -8292,7 +8293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>274</v>
       </c>
@@ -8381,7 +8382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>274</v>
       </c>
@@ -8470,7 +8471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>274</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>274</v>
       </c>
@@ -8648,7 +8649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>274</v>
       </c>
@@ -8737,7 +8738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>274</v>
       </c>
@@ -8826,7 +8827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>276</v>
       </c>
@@ -8909,7 +8910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>276</v>
       </c>
@@ -8992,7 +8993,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>276</v>
       </c>
@@ -9075,7 +9076,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>276</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>276</v>
       </c>
@@ -9241,7 +9242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>276</v>
       </c>
@@ -9324,7 +9325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>277</v>
       </c>
@@ -9404,7 +9405,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>277</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>277</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>277</v>
       </c>
@@ -9644,7 +9645,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>323</v>
       </c>
@@ -9727,7 +9728,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>323</v>
       </c>
@@ -9810,7 +9811,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>323</v>
       </c>
@@ -9893,7 +9894,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>323</v>
       </c>
@@ -9976,7 +9977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>323</v>
       </c>
@@ -10053,7 +10054,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>325</v>
       </c>
@@ -10142,7 +10143,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>325</v>
       </c>
@@ -10231,7 +10232,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>325</v>
       </c>
@@ -10320,7 +10321,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>325</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>325</v>
       </c>
@@ -10486,7 +10487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>325</v>
       </c>
@@ -10575,7 +10576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>331</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>331</v>
       </c>
@@ -10741,7 +10742,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>332</v>
       </c>
@@ -10824,7 +10825,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>332</v>
       </c>
@@ -10907,7 +10908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>332</v>
       </c>
@@ -10990,7 +10991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>332</v>
       </c>
@@ -11073,7 +11074,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>332</v>
       </c>
@@ -11162,7 +11163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>332</v>
       </c>
@@ -11245,7 +11246,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>334</v>
       </c>
@@ -11328,7 +11329,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>334</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>335</v>
       </c>
@@ -11497,7 +11498,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>335</v>
       </c>
@@ -11583,7 +11584,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>339</v>
       </c>
@@ -11672,7 +11673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>339</v>
       </c>
@@ -11761,7 +11762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>361</v>
       </c>
@@ -11844,7 +11845,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>361</v>
       </c>
@@ -11921,7 +11922,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>364</v>
       </c>
@@ -12010,7 +12011,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>364</v>
       </c>
@@ -12099,7 +12100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>364</v>
       </c>
@@ -12188,7 +12189,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>364</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>367</v>
       </c>
@@ -12366,7 +12367,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>367</v>
       </c>
@@ -12455,7 +12456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>369</v>
       </c>
@@ -12538,7 +12539,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>369</v>
       </c>
@@ -12621,7 +12622,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>369</v>
       </c>
@@ -12710,7 +12711,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>369</v>
       </c>
@@ -12799,7 +12800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>376</v>
       </c>
@@ -12889,7 +12890,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>376</v>
       </c>
@@ -12978,7 +12979,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>376</v>
       </c>
@@ -13067,7 +13068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>377</v>
       </c>
@@ -13156,7 +13157,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>377</v>
       </c>
@@ -13245,7 +13246,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>377</v>
       </c>
@@ -13334,7 +13335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>377</v>
       </c>
@@ -13423,7 +13424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>379</v>
       </c>
@@ -13512,7 +13513,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>379</v>
       </c>
@@ -13601,7 +13602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>379</v>
       </c>
@@ -13690,7 +13691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>379</v>
       </c>
@@ -13779,7 +13780,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>379</v>
       </c>
@@ -13868,7 +13869,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>379</v>
       </c>
@@ -13957,7 +13958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>385</v>
       </c>
@@ -14046,7 +14047,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>385</v>
       </c>
@@ -14135,7 +14136,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>385</v>
       </c>
@@ -14224,7 +14225,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>423</v>
       </c>
@@ -14307,7 +14308,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>423</v>
       </c>
@@ -14390,7 +14391,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>423</v>
       </c>
@@ -14473,7 +14474,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>424</v>
       </c>
@@ -14556,7 +14557,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>424</v>
       </c>
@@ -14639,7 +14640,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>424</v>
       </c>
@@ -14722,7 +14723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>460</v>
       </c>
@@ -14811,7 +14812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>466</v>
       </c>
@@ -14894,7 +14895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>466</v>
       </c>
@@ -14977,7 +14978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>14.1</v>
       </c>
@@ -15066,7 +15067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>14.1</v>
       </c>
@@ -15155,7 +15156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>14.1</v>
       </c>
@@ -15244,7 +15245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>14.1</v>
       </c>
@@ -15333,7 +15334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>14.1</v>
       </c>
@@ -15422,7 +15423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>14.2</v>
       </c>
@@ -15511,7 +15512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>14.2</v>
       </c>
@@ -15600,7 +15601,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>14.2</v>
       </c>
@@ -15689,7 +15690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>14.2</v>
       </c>
@@ -15778,7 +15779,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>14.2</v>
       </c>
@@ -15867,7 +15868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>14.3</v>
       </c>
@@ -15956,7 +15957,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>14.3</v>
       </c>
@@ -16045,7 +16046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>14.3</v>
       </c>
@@ -16134,7 +16135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>14.3</v>
       </c>
@@ -16223,7 +16224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>14.3</v>
       </c>
@@ -16312,7 +16313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>14.4</v>
       </c>
@@ -16401,7 +16402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>14.4</v>
       </c>
@@ -16490,7 +16491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>14.4</v>
       </c>
@@ -16579,7 +16580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>14.4</v>
       </c>
@@ -16668,7 +16669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>14.4</v>
       </c>
@@ -16757,7 +16758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>386.1</v>
       </c>
@@ -16840,7 +16841,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>386.1</v>
       </c>
@@ -16923,7 +16924,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>386.1</v>
       </c>
@@ -17012,7 +17013,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>386.1</v>
       </c>
@@ -17457,7 +17458,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>386.3</v>
       </c>
@@ -17546,7 +17547,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>386.3</v>
       </c>
@@ -17635,7 +17636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>386.3</v>
       </c>
@@ -17724,7 +17725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>386.3</v>
       </c>
@@ -17813,7 +17814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>77</v>
       </c>
@@ -17902,7 +17903,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>77</v>
       </c>
@@ -17991,7 +17992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>96</v>
       </c>
@@ -18080,7 +18081,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>97</v>
       </c>
@@ -18157,7 +18158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>97</v>
       </c>
@@ -18234,7 +18235,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>98</v>
       </c>
@@ -18311,7 +18312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>98</v>
       </c>
@@ -18400,7 +18401,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>14.1</v>
       </c>
@@ -18489,7 +18490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>14.2</v>
       </c>
@@ -18578,7 +18579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>14.3</v>
       </c>
@@ -18667,7 +18668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>14.4</v>
       </c>
@@ -18756,7 +18757,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18845,7 +18846,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>148</v>
       </c>
@@ -18934,7 +18935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>339</v>
       </c>
@@ -19023,7 +19024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>325</v>
       </c>
@@ -19112,7 +19113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>323</v>
       </c>
@@ -19201,7 +19202,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>276</v>
       </c>
@@ -19290,7 +19291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>14</v>
       </c>
@@ -19379,7 +19380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>379</v>
       </c>
@@ -19468,7 +19469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>274</v>
       </c>
@@ -19557,7 +19558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>14.1</v>
       </c>
@@ -19646,7 +19647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>14.2</v>
       </c>
@@ -19735,7 +19736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14.3</v>
       </c>
@@ -19824,7 +19825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>14.4</v>
       </c>
@@ -19913,7 +19914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>98</v>
       </c>
@@ -20002,7 +20003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>194</v>
       </c>
@@ -20091,7 +20092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>193</v>
       </c>
@@ -20180,7 +20181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>245</v>
       </c>
@@ -20269,7 +20270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>205</v>
       </c>
@@ -20358,7 +20359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>204</v>
       </c>
@@ -20447,7 +20448,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>364</v>
       </c>
@@ -20536,7 +20537,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>376</v>
       </c>
@@ -20625,7 +20626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>203</v>
       </c>
@@ -20714,7 +20715,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>207</v>
       </c>
@@ -20803,7 +20804,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>369</v>
       </c>
@@ -20892,7 +20893,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>331</v>
       </c>
@@ -20972,7 +20973,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>332</v>
       </c>
@@ -21061,7 +21062,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>202</v>
       </c>
@@ -21150,7 +21151,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>77</v>
       </c>
@@ -21239,7 +21240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>277</v>
       </c>
@@ -21325,7 +21326,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>385</v>
       </c>
@@ -21408,7 +21409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>386.1</v>
       </c>
@@ -21574,7 +21575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>386.3</v>
       </c>
@@ -21657,7 +21658,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>14</v>
       </c>
@@ -21743,7 +21744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>14</v>
       </c>
@@ -21829,7 +21830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>14</v>
       </c>
@@ -21915,7 +21916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>77</v>
       </c>
@@ -22001,7 +22002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>77</v>
       </c>
@@ -22087,7 +22088,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>77</v>
       </c>
@@ -22173,7 +22174,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>96</v>
       </c>
@@ -22259,7 +22260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>96</v>
       </c>
@@ -22345,7 +22346,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>96</v>
       </c>
@@ -22431,7 +22432,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>97</v>
       </c>
@@ -22517,7 +22518,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>97</v>
       </c>
@@ -22597,7 +22598,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>97</v>
       </c>
@@ -22677,7 +22678,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>98</v>
       </c>
@@ -22763,7 +22764,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>98</v>
       </c>
@@ -22849,7 +22850,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>98</v>
       </c>
@@ -22935,7 +22936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>109</v>
       </c>
@@ -23018,7 +23019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>148</v>
       </c>
@@ -23104,7 +23105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>148</v>
       </c>
@@ -23190,7 +23191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>148</v>
       </c>
@@ -23276,7 +23277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>193</v>
       </c>
@@ -23362,7 +23363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>193</v>
       </c>
@@ -23448,7 +23449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>193</v>
       </c>
@@ -23534,7 +23535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>194</v>
       </c>
@@ -23620,7 +23621,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>194</v>
       </c>
@@ -23706,7 +23707,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>194</v>
       </c>
@@ -23792,7 +23793,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>200</v>
       </c>
@@ -23869,7 +23870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>200</v>
       </c>
@@ -23955,7 +23956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>202</v>
       </c>
@@ -24041,7 +24042,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>202</v>
       </c>
@@ -24121,7 +24122,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>203</v>
       </c>
@@ -24207,7 +24208,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>203</v>
       </c>
@@ -24293,7 +24294,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>203</v>
       </c>
@@ -24379,7 +24380,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>204</v>
       </c>
@@ -24453,7 +24454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>204</v>
       </c>
@@ -24539,7 +24540,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>204</v>
       </c>
@@ -24625,7 +24626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>205</v>
       </c>
@@ -24711,7 +24712,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>205</v>
       </c>
@@ -24797,7 +24798,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>207</v>
       </c>
@@ -24883,7 +24884,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>207</v>
       </c>
@@ -24969,7 +24970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>228</v>
       </c>
@@ -25055,7 +25056,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>228</v>
       </c>
@@ -25141,7 +25142,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>244</v>
       </c>
@@ -25227,7 +25228,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>244</v>
       </c>
@@ -25313,7 +25314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>244</v>
       </c>
@@ -25399,7 +25400,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>245</v>
       </c>
@@ -25485,7 +25486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>245</v>
       </c>
@@ -25571,7 +25572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>245</v>
       </c>
@@ -25657,7 +25658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>274</v>
       </c>
@@ -25743,7 +25744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25829,7 +25830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25915,7 +25916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>276</v>
       </c>
@@ -26001,7 +26002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>276</v>
       </c>
@@ -26087,7 +26088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>276</v>
       </c>
@@ -26173,7 +26174,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>277</v>
       </c>
@@ -26256,7 +26257,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>277</v>
       </c>
@@ -26339,7 +26340,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>323</v>
       </c>
@@ -26425,7 +26426,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>323</v>
       </c>
@@ -26511,7 +26512,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>323</v>
       </c>
@@ -26597,7 +26598,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>325</v>
       </c>
@@ -26683,7 +26684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>325</v>
       </c>
@@ -26769,7 +26770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>325</v>
       </c>
@@ -26855,7 +26856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>331</v>
       </c>
@@ -26932,7 +26933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>331</v>
       </c>
@@ -27009,7 +27010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>332</v>
       </c>
@@ -27095,7 +27096,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>332</v>
       </c>
@@ -27181,7 +27182,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>332</v>
       </c>
@@ -27267,7 +27268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>334</v>
       </c>
@@ -27353,7 +27354,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>334</v>
       </c>
@@ -27439,7 +27440,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>334</v>
       </c>
@@ -27525,7 +27526,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>335</v>
       </c>
@@ -27608,7 +27609,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>335</v>
       </c>
@@ -27691,7 +27692,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>339</v>
       </c>
@@ -27777,7 +27778,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>339</v>
       </c>
@@ -27863,7 +27864,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>460</v>
       </c>
@@ -27943,7 +27944,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>460</v>
       </c>
@@ -28020,7 +28021,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>361</v>
       </c>
@@ -28106,7 +28107,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>361</v>
       </c>
@@ -28186,7 +28187,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>364</v>
       </c>
@@ -28263,7 +28264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>364</v>
       </c>
@@ -28349,7 +28350,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>367</v>
       </c>
@@ -28435,7 +28436,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>367</v>
       </c>
@@ -28521,7 +28522,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>367</v>
       </c>
@@ -28607,7 +28608,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>369</v>
       </c>
@@ -28684,7 +28685,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>369</v>
       </c>
@@ -28770,7 +28771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>376</v>
       </c>
@@ -28856,7 +28857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>376</v>
       </c>
@@ -28942,7 +28943,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>376</v>
       </c>
@@ -29028,7 +29029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>377</v>
       </c>
@@ -29114,7 +29115,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>377</v>
       </c>
@@ -29200,7 +29201,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>379</v>
       </c>
@@ -29286,7 +29287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>379</v>
       </c>
@@ -29372,7 +29373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>379</v>
       </c>
@@ -29458,7 +29459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>385</v>
       </c>
@@ -29547,7 +29548,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>385</v>
       </c>
@@ -29636,7 +29637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>385</v>
       </c>
@@ -29725,7 +29726,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>423</v>
       </c>
@@ -29811,7 +29812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>423</v>
       </c>
@@ -29897,7 +29898,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>423</v>
       </c>
@@ -29983,7 +29984,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>424</v>
       </c>
@@ -30069,7 +30070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>424</v>
       </c>
@@ -30155,7 +30156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>424</v>
       </c>
@@ -30241,7 +30242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>460</v>
       </c>
@@ -30327,7 +30328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>466</v>
       </c>
@@ -30413,7 +30414,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>466</v>
       </c>
@@ -30499,7 +30500,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>466</v>
       </c>
@@ -30585,7 +30586,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>109</v>
       </c>
@@ -30668,7 +30669,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>14.1</v>
       </c>
@@ -30754,7 +30755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>14.1</v>
       </c>
@@ -30840,7 +30841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.1</v>
       </c>
@@ -30926,7 +30927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.2</v>
       </c>
@@ -31012,7 +31013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.2</v>
       </c>
@@ -31098,7 +31099,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.2</v>
       </c>
@@ -31184,7 +31185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.3</v>
       </c>
@@ -31270,7 +31271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.3</v>
       </c>
@@ -31356,7 +31357,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.3</v>
       </c>
@@ -31442,7 +31443,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="344" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.4</v>
       </c>
@@ -31528,7 +31529,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="345" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.4</v>
       </c>
@@ -31614,7 +31615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="346" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.4</v>
       </c>
@@ -31700,7 +31701,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>386.1</v>
       </c>
@@ -31786,7 +31787,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>386.1</v>
       </c>
@@ -32044,7 +32045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>386.3</v>
       </c>
@@ -32130,7 +32131,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>386.3</v>
       </c>
@@ -32216,7 +32217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>228</v>
       </c>
@@ -32302,7 +32303,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>460</v>
       </c>
@@ -32388,7 +32389,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>148</v>
       </c>
@@ -32474,7 +32475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>339</v>
       </c>
@@ -32560,7 +32561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>325</v>
       </c>
@@ -32646,7 +32647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>323</v>
       </c>
@@ -32732,7 +32733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>276</v>
       </c>
@@ -32818,7 +32819,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>14</v>
       </c>
@@ -32904,7 +32905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>379</v>
       </c>
@@ -32990,7 +32991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>274</v>
       </c>
@@ -33076,7 +33077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>14.1</v>
       </c>
@@ -33162,7 +33163,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>14.2</v>
       </c>
@@ -33248,7 +33249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>14.3</v>
       </c>
@@ -33334,7 +33335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14.4</v>
       </c>
@@ -33420,7 +33421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>423</v>
       </c>
@@ -33506,7 +33507,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>97</v>
       </c>
@@ -33586,7 +33587,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>98</v>
       </c>
@@ -33672,7 +33673,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>194</v>
       </c>
@@ -33758,7 +33759,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>193</v>
       </c>
@@ -33844,7 +33845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>466</v>
       </c>
@@ -33930,7 +33931,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>245</v>
       </c>
@@ -34016,7 +34017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>205</v>
       </c>
@@ -34102,7 +34103,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>204</v>
       </c>
@@ -34188,7 +34189,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>377</v>
       </c>
@@ -34274,7 +34275,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>367</v>
       </c>
@@ -34360,7 +34361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>364</v>
       </c>
@@ -34446,7 +34447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>376</v>
       </c>
@@ -34532,7 +34533,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>228</v>
       </c>
@@ -34618,7 +34619,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>203</v>
       </c>
@@ -34704,7 +34705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>207</v>
       </c>
@@ -34790,7 +34791,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>361</v>
       </c>
@@ -34876,7 +34877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>244</v>
       </c>
@@ -34962,7 +34963,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>369</v>
       </c>
@@ -35048,7 +35049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>331</v>
       </c>
@@ -35125,7 +35126,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>332</v>
       </c>
@@ -35211,7 +35212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>202</v>
       </c>
@@ -35297,7 +35298,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>200</v>
       </c>
@@ -35383,7 +35384,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>109</v>
       </c>
@@ -35466,7 +35467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>335</v>
       </c>
@@ -35549,7 +35550,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>334</v>
       </c>
@@ -35635,7 +35636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>77</v>
       </c>
@@ -35721,7 +35722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>424</v>
       </c>
@@ -35807,7 +35808,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>277</v>
       </c>
@@ -35890,7 +35891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>385</v>
       </c>
@@ -35973,7 +35974,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>386.1</v>
       </c>
@@ -36133,7 +36134,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>386.3</v>
       </c>
@@ -36214,6 +36215,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC399" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Total Ingresos B2G"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B4BE982-A0F4-426A-A552-CD3BDDEFDDEC}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D896B2DA-72CC-4BDE-BECD-3D2C3E1B2C3D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1869,7 +1869,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -17102,7 +17104,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>386.2</v>
       </c>
@@ -17191,7 +17193,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>386.2</v>
       </c>
@@ -17280,7 +17282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>386.2</v>
       </c>
@@ -17369,7 +17371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>386.2</v>
       </c>
@@ -21492,7 +21494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>386.2</v>
       </c>
@@ -36220,6 +36222,9 @@
       <filters>
         <filter val="Total Ingresos B2G"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8DEA3DD-3B4D-441A-953E-3AB50C2855A9}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F0A488-72DA-40C4-AF71-1D1A8040FF4D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21726,10 +21726,10 @@
         <v>2</v>
       </c>
       <c r="K229">
-        <v>53038</v>
+        <v>56505</v>
       </c>
       <c r="L229">
-        <v>53038</v>
+        <v>56505</v>
       </c>
       <c r="M229">
         <v>1</v>
@@ -30919,7 +30919,7 @@
         <v>8200</v>
       </c>
       <c r="L337">
-        <v>8200</v>
+        <v>8743</v>
       </c>
       <c r="M337">
         <v>1</v>
@@ -31266,7 +31266,7 @@
         <v>44838</v>
       </c>
       <c r="L341">
-        <v>44838</v>
+        <v>47762</v>
       </c>
       <c r="M341">
         <v>1</v>
@@ -31613,7 +31613,7 @@
         <v>49176</v>
       </c>
       <c r="L345">
-        <v>49176</v>
+        <v>52096</v>
       </c>
       <c r="M345">
         <v>1</v>
@@ -31960,7 +31960,7 @@
         <v>3862</v>
       </c>
       <c r="L349">
-        <v>3862</v>
+        <v>4409</v>
       </c>
       <c r="M349">
         <v>1</v>
@@ -36787,10 +36787,7 @@
       </c>
     </row>
     <row r="408" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="K408" s="6">
-        <f>+K229/K2-1</f>
-        <v>8.2319810627703882E-2</v>
-      </c>
+      <c r="K408" s="6"/>
     </row>
     <row r="409" spans="1:29" x14ac:dyDescent="0.3">
       <c r="K409" s="5"/>
@@ -36808,7 +36805,6 @@
       <c r="K413" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC405" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F0A488-72DA-40C4-AF71-1D1A8040FF4D}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FFB2365-0777-4EF2-B6EE-1BDD3CA07595}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1508,7 +1508,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1533,6 +1533,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1578,7 +1586,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1588,6 +1596,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -1893,10 +1902,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC413"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="2" max="2" width="59.44140625" customWidth="1"/>
     <col min="3" max="4" width="8.88671875" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
@@ -2525,7 +2535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>77</v>
       </c>
@@ -2614,7 +2624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>77</v>
       </c>
@@ -2703,7 +2713,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>77</v>
       </c>
@@ -2792,7 +2802,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>77</v>
       </c>
@@ -2881,7 +2891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>96</v>
       </c>
@@ -2970,7 +2980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>96</v>
       </c>
@@ -3059,7 +3069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>96</v>
       </c>
@@ -3148,7 +3158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>96</v>
       </c>
@@ -3237,7 +3247,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>97</v>
       </c>
@@ -3326,7 +3336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>97</v>
       </c>
@@ -3409,7 +3419,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>97</v>
       </c>
@@ -3486,7 +3496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>97</v>
       </c>
@@ -3563,7 +3573,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>98</v>
       </c>
@@ -3646,7 +3656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>98</v>
       </c>
@@ -3735,7 +3745,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>98</v>
       </c>
@@ -3818,7 +3828,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>98</v>
       </c>
@@ -3907,7 +3917,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>109</v>
       </c>
@@ -3975,7 +3985,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>109</v>
       </c>
@@ -4043,7 +4053,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>148</v>
       </c>
@@ -4132,7 +4142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>148</v>
       </c>
@@ -4221,7 +4231,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>148</v>
       </c>
@@ -4310,7 +4320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>148</v>
       </c>
@@ -4393,7 +4403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>193</v>
       </c>
@@ -4482,7 +4492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>193</v>
       </c>
@@ -4571,7 +4581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>193</v>
       </c>
@@ -4660,7 +4670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>193</v>
       </c>
@@ -4749,7 +4759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>193</v>
       </c>
@@ -4838,7 +4848,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>193</v>
       </c>
@@ -4927,7 +4937,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>194</v>
       </c>
@@ -5016,7 +5026,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>194</v>
       </c>
@@ -5105,7 +5115,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>194</v>
       </c>
@@ -5194,7 +5204,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>194</v>
       </c>
@@ -5283,7 +5293,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>194</v>
       </c>
@@ -5372,7 +5382,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>200</v>
       </c>
@@ -5452,7 +5462,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>200</v>
       </c>
@@ -5535,7 +5545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>202</v>
       </c>
@@ -5618,7 +5628,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>202</v>
       </c>
@@ -5698,7 +5708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>203</v>
       </c>
@@ -5787,7 +5797,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>203</v>
       </c>
@@ -5876,7 +5886,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>203</v>
       </c>
@@ -5965,7 +5975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>203</v>
       </c>
@@ -6054,7 +6064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>203</v>
       </c>
@@ -6143,7 +6153,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>203</v>
       </c>
@@ -6232,7 +6242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>204</v>
       </c>
@@ -6321,7 +6331,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>204</v>
       </c>
@@ -6410,7 +6420,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>204</v>
       </c>
@@ -6499,7 +6509,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>204</v>
       </c>
@@ -6588,7 +6598,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>204</v>
       </c>
@@ -6677,7 +6687,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>204</v>
       </c>
@@ -6766,7 +6776,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>205</v>
       </c>
@@ -6855,7 +6865,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>205</v>
       </c>
@@ -6944,7 +6954,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>205</v>
       </c>
@@ -7033,7 +7043,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>205</v>
       </c>
@@ -7122,7 +7132,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>207</v>
       </c>
@@ -7211,7 +7221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>207</v>
       </c>
@@ -7300,7 +7310,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>207</v>
       </c>
@@ -7389,7 +7399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>207</v>
       </c>
@@ -7478,7 +7488,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>228</v>
       </c>
@@ -7561,7 +7571,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>228</v>
       </c>
@@ -7632,7 +7642,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>244</v>
       </c>
@@ -7715,7 +7725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>244</v>
       </c>
@@ -7798,7 +7808,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>245</v>
       </c>
@@ -7887,7 +7897,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>245</v>
       </c>
@@ -7976,7 +7986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>245</v>
       </c>
@@ -8065,7 +8075,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>245</v>
       </c>
@@ -8154,7 +8164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>245</v>
       </c>
@@ -8243,7 +8253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>245</v>
       </c>
@@ -8326,7 +8336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>274</v>
       </c>
@@ -8415,7 +8425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>274</v>
       </c>
@@ -8504,7 +8514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>274</v>
       </c>
@@ -8593,7 +8603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>274</v>
       </c>
@@ -8682,7 +8692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>274</v>
       </c>
@@ -8771,7 +8781,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>274</v>
       </c>
@@ -8860,7 +8870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>276</v>
       </c>
@@ -8943,7 +8953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>276</v>
       </c>
@@ -9026,7 +9036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>276</v>
       </c>
@@ -9109,7 +9119,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>276</v>
       </c>
@@ -9192,7 +9202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>276</v>
       </c>
@@ -9275,7 +9285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>276</v>
       </c>
@@ -9358,7 +9368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>277</v>
       </c>
@@ -9438,7 +9448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>277</v>
       </c>
@@ -9518,7 +9528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>277</v>
       </c>
@@ -9598,7 +9608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>277</v>
       </c>
@@ -9678,7 +9688,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>323</v>
       </c>
@@ -9761,7 +9771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>323</v>
       </c>
@@ -9844,7 +9854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>323</v>
       </c>
@@ -9927,7 +9937,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>323</v>
       </c>
@@ -10010,7 +10020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>323</v>
       </c>
@@ -10087,7 +10097,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>325</v>
       </c>
@@ -10176,7 +10186,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>325</v>
       </c>
@@ -10265,7 +10275,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>325</v>
       </c>
@@ -10354,7 +10364,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>325</v>
       </c>
@@ -10431,7 +10441,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>325</v>
       </c>
@@ -10520,7 +10530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>325</v>
       </c>
@@ -10609,7 +10619,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>331</v>
       </c>
@@ -10692,7 +10702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>331</v>
       </c>
@@ -10775,7 +10785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>332</v>
       </c>
@@ -10858,7 +10868,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>332</v>
       </c>
@@ -10941,7 +10951,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>332</v>
       </c>
@@ -11024,7 +11034,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>332</v>
       </c>
@@ -11107,7 +11117,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>332</v>
       </c>
@@ -11196,7 +11206,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>332</v>
       </c>
@@ -11279,7 +11289,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>334</v>
       </c>
@@ -11362,7 +11372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>334</v>
       </c>
@@ -11445,7 +11455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>335</v>
       </c>
@@ -11531,7 +11541,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>335</v>
       </c>
@@ -11617,7 +11627,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>339</v>
       </c>
@@ -11706,7 +11716,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>339</v>
       </c>
@@ -11795,7 +11805,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>361</v>
       </c>
@@ -11878,7 +11888,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>361</v>
       </c>
@@ -11958,7 +11968,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>364</v>
       </c>
@@ -12047,7 +12057,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>364</v>
       </c>
@@ -12136,7 +12146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>364</v>
       </c>
@@ -12225,7 +12235,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>364</v>
       </c>
@@ -12314,7 +12324,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>367</v>
       </c>
@@ -12403,7 +12413,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>367</v>
       </c>
@@ -12492,7 +12502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>369</v>
       </c>
@@ -12575,7 +12585,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>369</v>
       </c>
@@ -12658,7 +12668,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>369</v>
       </c>
@@ -12747,7 +12757,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>369</v>
       </c>
@@ -12836,7 +12846,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>376</v>
       </c>
@@ -12926,7 +12936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>376</v>
       </c>
@@ -13015,7 +13025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>376</v>
       </c>
@@ -13104,7 +13114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>377</v>
       </c>
@@ -13193,7 +13203,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>377</v>
       </c>
@@ -13282,7 +13292,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>377</v>
       </c>
@@ -13371,7 +13381,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>377</v>
       </c>
@@ -13460,7 +13470,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>379</v>
       </c>
@@ -13549,7 +13559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>379</v>
       </c>
@@ -13638,7 +13648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>379</v>
       </c>
@@ -13727,7 +13737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>379</v>
       </c>
@@ -13816,7 +13826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>379</v>
       </c>
@@ -13905,7 +13915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>379</v>
       </c>
@@ -13994,7 +14004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>385</v>
       </c>
@@ -14083,7 +14093,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>385</v>
       </c>
@@ -14172,7 +14182,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>385</v>
       </c>
@@ -14261,7 +14271,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>423</v>
       </c>
@@ -14344,7 +14354,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>423</v>
       </c>
@@ -14427,7 +14437,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>423</v>
       </c>
@@ -14510,7 +14520,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>424</v>
       </c>
@@ -14593,7 +14603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>424</v>
       </c>
@@ -14676,7 +14686,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>424</v>
       </c>
@@ -14759,7 +14769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>460</v>
       </c>
@@ -14848,7 +14858,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>466</v>
       </c>
@@ -14931,7 +14941,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>466</v>
       </c>
@@ -15014,7 +15024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>14.1</v>
       </c>
@@ -15103,7 +15113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>14.1</v>
       </c>
@@ -15192,7 +15202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>14.1</v>
       </c>
@@ -15281,7 +15291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>14.1</v>
       </c>
@@ -15370,7 +15380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>14.1</v>
       </c>
@@ -15459,7 +15469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>14.2</v>
       </c>
@@ -15548,7 +15558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>14.2</v>
       </c>
@@ -15637,7 +15647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>14.2</v>
       </c>
@@ -15726,7 +15736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>14.2</v>
       </c>
@@ -15815,7 +15825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>14.2</v>
       </c>
@@ -15904,7 +15914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>14.3</v>
       </c>
@@ -15993,7 +16003,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>14.3</v>
       </c>
@@ -16082,7 +16092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>14.3</v>
       </c>
@@ -16171,7 +16181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>14.3</v>
       </c>
@@ -16260,7 +16270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>14.3</v>
       </c>
@@ -16349,7 +16359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>14.4</v>
       </c>
@@ -16438,7 +16448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>14.4</v>
       </c>
@@ -16527,7 +16537,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>14.4</v>
       </c>
@@ -16616,7 +16626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>14.4</v>
       </c>
@@ -16705,7 +16715,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>14.4</v>
       </c>
@@ -16794,7 +16804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>386.1</v>
       </c>
@@ -16877,7 +16887,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>386.1</v>
       </c>
@@ -16960,7 +16970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>386.1</v>
       </c>
@@ -17049,7 +17059,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>386.1</v>
       </c>
@@ -17138,7 +17148,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>386.2</v>
       </c>
@@ -17227,7 +17237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>386.2</v>
       </c>
@@ -17316,7 +17326,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>386.2</v>
       </c>
@@ -17405,7 +17415,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>386.2</v>
       </c>
@@ -17494,7 +17504,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>386.3</v>
       </c>
@@ -17583,7 +17593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>386.3</v>
       </c>
@@ -17672,7 +17682,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>386.3</v>
       </c>
@@ -17761,7 +17771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>386.3</v>
       </c>
@@ -17850,7 +17860,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>77</v>
       </c>
@@ -17939,7 +17949,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>77</v>
       </c>
@@ -18028,7 +18038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>96</v>
       </c>
@@ -18117,7 +18127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>97</v>
       </c>
@@ -18194,7 +18204,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>97</v>
       </c>
@@ -18271,7 +18281,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>98</v>
       </c>
@@ -18348,7 +18358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>98</v>
       </c>
@@ -18437,7 +18447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>14.1</v>
       </c>
@@ -18526,7 +18536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>14.2</v>
       </c>
@@ -18615,7 +18625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>14.3</v>
       </c>
@@ -18704,7 +18714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>14.4</v>
       </c>
@@ -18793,7 +18803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18882,7 +18892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>148</v>
       </c>
@@ -18971,7 +18981,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>339</v>
       </c>
@@ -19060,7 +19070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>325</v>
       </c>
@@ -19149,7 +19159,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>323</v>
       </c>
@@ -19238,7 +19248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>276</v>
       </c>
@@ -19416,7 +19426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>379</v>
       </c>
@@ -19505,7 +19515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>274</v>
       </c>
@@ -19594,7 +19604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>14.1</v>
       </c>
@@ -19683,7 +19693,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>14.2</v>
       </c>
@@ -19772,7 +19782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>14.3</v>
       </c>
@@ -19861,7 +19871,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>14.4</v>
       </c>
@@ -19950,7 +19960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>98</v>
       </c>
@@ -20039,7 +20049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>194</v>
       </c>
@@ -20128,7 +20138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>193</v>
       </c>
@@ -20217,7 +20227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>245</v>
       </c>
@@ -20306,7 +20316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>205</v>
       </c>
@@ -20395,7 +20405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>204</v>
       </c>
@@ -20484,7 +20494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>364</v>
       </c>
@@ -20573,7 +20583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>376</v>
       </c>
@@ -20662,7 +20672,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>203</v>
       </c>
@@ -20751,7 +20761,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>207</v>
       </c>
@@ -20840,7 +20850,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>369</v>
       </c>
@@ -20929,7 +20939,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>331</v>
       </c>
@@ -21009,7 +21019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>332</v>
       </c>
@@ -21098,7 +21108,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>202</v>
       </c>
@@ -21187,7 +21197,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>77</v>
       </c>
@@ -21276,7 +21286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>277</v>
       </c>
@@ -21362,7 +21372,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>385</v>
       </c>
@@ -21445,7 +21455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>386.1</v>
       </c>
@@ -21528,7 +21538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>386.2</v>
       </c>
@@ -21611,7 +21621,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>386.3</v>
       </c>
@@ -21728,7 +21738,7 @@
       <c r="K229">
         <v>56505</v>
       </c>
-      <c r="L229">
+      <c r="L229" s="7">
         <v>56505</v>
       </c>
       <c r="M229">
@@ -21783,7 +21793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>14</v>
       </c>
@@ -21869,7 +21879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>14</v>
       </c>
@@ -21955,7 +21965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>14</v>
       </c>
@@ -22041,7 +22051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>77</v>
       </c>
@@ -22127,7 +22137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>77</v>
       </c>
@@ -22213,7 +22223,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>77</v>
       </c>
@@ -22299,7 +22309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>96</v>
       </c>
@@ -22385,7 +22395,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>96</v>
       </c>
@@ -22471,7 +22481,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>96</v>
       </c>
@@ -22557,7 +22567,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>97</v>
       </c>
@@ -22643,7 +22653,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>97</v>
       </c>
@@ -22723,7 +22733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>97</v>
       </c>
@@ -22803,7 +22813,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>98</v>
       </c>
@@ -22889,7 +22899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>98</v>
       </c>
@@ -22975,7 +22985,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>98</v>
       </c>
@@ -23061,7 +23071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>109</v>
       </c>
@@ -23144,7 +23154,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>148</v>
       </c>
@@ -23230,7 +23240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>148</v>
       </c>
@@ -23316,7 +23326,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>148</v>
       </c>
@@ -23402,7 +23412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>193</v>
       </c>
@@ -23488,7 +23498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>193</v>
       </c>
@@ -23574,7 +23584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>193</v>
       </c>
@@ -23660,7 +23670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>194</v>
       </c>
@@ -23746,7 +23756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>194</v>
       </c>
@@ -23832,7 +23842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>194</v>
       </c>
@@ -23918,7 +23928,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>200</v>
       </c>
@@ -23995,7 +24005,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>200</v>
       </c>
@@ -24081,7 +24091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>202</v>
       </c>
@@ -24167,7 +24177,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>202</v>
       </c>
@@ -24247,7 +24257,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>203</v>
       </c>
@@ -24333,7 +24343,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>203</v>
       </c>
@@ -24419,7 +24429,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>203</v>
       </c>
@@ -24505,7 +24515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>204</v>
       </c>
@@ -24579,7 +24589,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>204</v>
       </c>
@@ -24665,7 +24675,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>204</v>
       </c>
@@ -24751,7 +24761,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>205</v>
       </c>
@@ -24837,7 +24847,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>205</v>
       </c>
@@ -24923,7 +24933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>207</v>
       </c>
@@ -25009,7 +25019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>207</v>
       </c>
@@ -25095,7 +25105,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>228</v>
       </c>
@@ -25181,7 +25191,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>228</v>
       </c>
@@ -25267,7 +25277,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>244</v>
       </c>
@@ -25353,7 +25363,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>244</v>
       </c>
@@ -25439,7 +25449,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>244</v>
       </c>
@@ -25525,7 +25535,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>245</v>
       </c>
@@ -25611,7 +25621,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>245</v>
       </c>
@@ -25697,7 +25707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>245</v>
       </c>
@@ -25783,7 +25793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25869,7 +25879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25955,7 +25965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -26041,7 +26051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>276</v>
       </c>
@@ -26127,7 +26137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>276</v>
       </c>
@@ -26213,7 +26223,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>276</v>
       </c>
@@ -26299,7 +26309,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>277</v>
       </c>
@@ -26382,7 +26392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>277</v>
       </c>
@@ -26465,7 +26475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>323</v>
       </c>
@@ -26551,7 +26561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>323</v>
       </c>
@@ -26637,7 +26647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>323</v>
       </c>
@@ -26723,7 +26733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>325</v>
       </c>
@@ -26809,7 +26819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>325</v>
       </c>
@@ -26895,7 +26905,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>325</v>
       </c>
@@ -26981,7 +26991,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>331</v>
       </c>
@@ -27058,7 +27068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>331</v>
       </c>
@@ -27135,7 +27145,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>332</v>
       </c>
@@ -27221,7 +27231,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>332</v>
       </c>
@@ -27307,7 +27317,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>332</v>
       </c>
@@ -27393,7 +27403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>334</v>
       </c>
@@ -27479,7 +27489,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>334</v>
       </c>
@@ -27565,7 +27575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>334</v>
       </c>
@@ -27651,7 +27661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>335</v>
       </c>
@@ -27734,7 +27744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>335</v>
       </c>
@@ -27817,7 +27827,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>339</v>
       </c>
@@ -27903,7 +27913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>339</v>
       </c>
@@ -27989,7 +27999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>460</v>
       </c>
@@ -28069,7 +28079,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>460</v>
       </c>
@@ -28146,7 +28156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>361</v>
       </c>
@@ -28236,7 +28246,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>361</v>
       </c>
@@ -28322,7 +28332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>361</v>
       </c>
@@ -28402,7 +28412,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>364</v>
       </c>
@@ -28479,7 +28489,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>364</v>
       </c>
@@ -28565,7 +28575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>367</v>
       </c>
@@ -28651,7 +28661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>367</v>
       </c>
@@ -28737,7 +28747,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>367</v>
       </c>
@@ -28823,7 +28833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>369</v>
       </c>
@@ -28900,7 +28910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>369</v>
       </c>
@@ -28986,7 +28996,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>376</v>
       </c>
@@ -29072,7 +29082,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>376</v>
       </c>
@@ -29158,7 +29168,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>376</v>
       </c>
@@ -29244,7 +29254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>377</v>
       </c>
@@ -29330,7 +29340,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>377</v>
       </c>
@@ -29416,7 +29426,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>379</v>
       </c>
@@ -29502,7 +29512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>379</v>
       </c>
@@ -29588,7 +29598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>379</v>
       </c>
@@ -29674,7 +29684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>385</v>
       </c>
@@ -29763,7 +29773,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>385</v>
       </c>
@@ -29852,7 +29862,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>385</v>
       </c>
@@ -29941,7 +29951,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>423</v>
       </c>
@@ -30027,7 +30037,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>423</v>
       </c>
@@ -30113,7 +30123,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>423</v>
       </c>
@@ -30199,7 +30209,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>424</v>
       </c>
@@ -30285,7 +30295,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>424</v>
       </c>
@@ -30371,7 +30381,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>424</v>
       </c>
@@ -30457,7 +30467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>460</v>
       </c>
@@ -30543,7 +30553,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>466</v>
       </c>
@@ -30629,7 +30639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>466</v>
       </c>
@@ -30715,7 +30725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>466</v>
       </c>
@@ -30801,7 +30811,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>109</v>
       </c>
@@ -30884,7 +30894,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>14.1</v>
       </c>
@@ -30973,7 +30983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>14.1</v>
       </c>
@@ -31059,7 +31069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>14.1</v>
       </c>
@@ -31145,7 +31155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>14.1</v>
       </c>
@@ -31231,7 +31241,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>14.2</v>
       </c>
@@ -31320,7 +31330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>14.2</v>
       </c>
@@ -31406,7 +31416,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>14.2</v>
       </c>
@@ -31492,7 +31502,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="344" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>14.2</v>
       </c>
@@ -31578,7 +31588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="345" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>14.3</v>
       </c>
@@ -31667,7 +31677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="346" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>14.3</v>
       </c>
@@ -31753,7 +31763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>14.3</v>
       </c>
@@ -31839,7 +31849,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>14.3</v>
       </c>
@@ -31925,7 +31935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="349" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>14.4</v>
       </c>
@@ -32014,7 +32024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="350" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>14.4</v>
       </c>
@@ -32100,7 +32110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>14.4</v>
       </c>
@@ -32186,7 +32196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>14.4</v>
       </c>
@@ -32272,7 +32282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>386.1</v>
       </c>
@@ -32358,7 +32368,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>386.1</v>
       </c>
@@ -32444,7 +32454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>386.2</v>
       </c>
@@ -32530,7 +32540,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>386.2</v>
       </c>
@@ -32616,7 +32626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>386.3</v>
       </c>
@@ -32702,7 +32712,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>386.3</v>
       </c>
@@ -32788,7 +32798,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>228</v>
       </c>
@@ -32874,7 +32884,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>460</v>
       </c>
@@ -32960,7 +32970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>148</v>
       </c>
@@ -33046,7 +33056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>339</v>
       </c>
@@ -33132,7 +33142,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>325</v>
       </c>
@@ -33218,7 +33228,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>323</v>
       </c>
@@ -33304,7 +33314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>276</v>
       </c>
@@ -33390,7 +33400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>14</v>
       </c>
@@ -33476,7 +33486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>379</v>
       </c>
@@ -33562,7 +33572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>274</v>
       </c>
@@ -33648,7 +33658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>14.1</v>
       </c>
@@ -33734,7 +33744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>14.2</v>
       </c>
@@ -33820,7 +33830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>14.3</v>
       </c>
@@ -33906,7 +33916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>14.4</v>
       </c>
@@ -33992,7 +34002,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>423</v>
       </c>
@@ -34078,7 +34088,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>97</v>
       </c>
@@ -34158,7 +34168,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>98</v>
       </c>
@@ -34244,7 +34254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>194</v>
       </c>
@@ -34330,7 +34340,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>193</v>
       </c>
@@ -34416,7 +34426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>466</v>
       </c>
@@ -34502,7 +34512,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>245</v>
       </c>
@@ -34588,7 +34598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>205</v>
       </c>
@@ -34674,7 +34684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>204</v>
       </c>
@@ -34760,7 +34770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>377</v>
       </c>
@@ -34846,7 +34856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>367</v>
       </c>
@@ -34932,7 +34942,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>364</v>
       </c>
@@ -35018,7 +35028,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>376</v>
       </c>
@@ -35104,7 +35114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>228</v>
       </c>
@@ -35190,7 +35200,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>203</v>
       </c>
@@ -35276,7 +35286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>207</v>
       </c>
@@ -35362,7 +35372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>361</v>
       </c>
@@ -35449,7 +35459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>244</v>
       </c>
@@ -35535,7 +35545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>369</v>
       </c>
@@ -35621,7 +35631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>331</v>
       </c>
@@ -35698,7 +35708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>332</v>
       </c>
@@ -35784,7 +35794,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>202</v>
       </c>
@@ -35870,7 +35880,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>200</v>
       </c>
@@ -35956,7 +35966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>109</v>
       </c>
@@ -36039,7 +36049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>335</v>
       </c>
@@ -36122,7 +36132,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>334</v>
       </c>
@@ -36208,7 +36218,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>77</v>
       </c>
@@ -36294,7 +36304,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>424</v>
       </c>
@@ -36380,7 +36390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>277</v>
       </c>
@@ -36463,7 +36473,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>385</v>
       </c>
@@ -36546,7 +36556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>386.1</v>
       </c>
@@ -36626,7 +36636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>386.2</v>
       </c>
@@ -36706,7 +36716,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>386.3</v>
       </c>
@@ -36805,6 +36815,18 @@
       <c r="K413" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC405" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="14"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2C944C1-FE1C-4D19-ACFE-D23ABF99BCBB}"/>
+  <xr:revisionPtr revIDLastSave="770" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F95DD4-F1FB-43F2-A93B-05093ED4A4A0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,11 +1522,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1887,7 +1889,7 @@
   <dimension ref="A1:AC494"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="59.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" customWidth="1"/>
     <col min="3" max="4" width="8.88671875" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="770" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F95DD4-F1FB-43F2-A93B-05093ED4A4A0}"/>
+  <xr:revisionPtr revIDLastSave="782" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83AC9FE9-1E81-4E4E-94BB-F346269A1E4B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1886,6 +1886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC494"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1986,7 +1987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2069,7 +2070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2152,7 +2153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2233,7 +2234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2401,7 +2402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2482,7 +2483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2566,7 +2567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2731,7 +2732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14</v>
       </c>
@@ -2899,7 +2900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2980,7 +2981,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -3069,7 +3070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3244,7 +3245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3333,7 +3334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>14</v>
       </c>
@@ -3422,7 +3423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>14</v>
       </c>
@@ -3508,7 +3509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>14</v>
       </c>
@@ -3597,7 +3598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>14</v>
       </c>
@@ -3686,7 +3687,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>14</v>
       </c>
@@ -3772,7 +3773,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>14</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>14</v>
       </c>
@@ -3941,7 +3942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>14</v>
       </c>
@@ -4024,7 +4025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>14.1</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14.1</v>
       </c>
@@ -4192,7 +4193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>14.1</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>14.1</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>14.1</v>
       </c>
@@ -4441,7 +4442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>14.1</v>
       </c>
@@ -4522,7 +4523,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>14.1</v>
       </c>
@@ -4606,7 +4607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>14.1</v>
       </c>
@@ -4690,7 +4691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>14.1</v>
       </c>
@@ -4771,7 +4772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>14.1</v>
       </c>
@@ -4855,7 +4856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>14.1</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>14.1</v>
       </c>
@@ -5020,7 +5021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>14.1</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>14.1</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>14.1</v>
       </c>
@@ -5284,7 +5285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>14.1</v>
       </c>
@@ -5373,7 +5374,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>14.1</v>
       </c>
@@ -5462,7 +5463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>14.1</v>
       </c>
@@ -5548,7 +5549,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14.1</v>
       </c>
@@ -5637,7 +5638,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14.1</v>
       </c>
@@ -5726,7 +5727,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14.1</v>
       </c>
@@ -5812,7 +5813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14.1</v>
       </c>
@@ -5901,7 +5902,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14.1</v>
       </c>
@@ -5981,7 +5982,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>14.1</v>
       </c>
@@ -6064,7 +6065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>14.2</v>
       </c>
@@ -6148,7 +6149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>14.2</v>
       </c>
@@ -6232,7 +6233,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>14.2</v>
       </c>
@@ -6313,7 +6314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>14.2</v>
       </c>
@@ -6397,7 +6398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>14.2</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>14.2</v>
       </c>
@@ -6562,7 +6563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>14.2</v>
       </c>
@@ -6646,7 +6647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>14.2</v>
       </c>
@@ -6730,7 +6731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>14.2</v>
       </c>
@@ -6811,7 +6812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>14.2</v>
       </c>
@@ -6895,7 +6896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>14.2</v>
       </c>
@@ -6979,7 +6980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>14.2</v>
       </c>
@@ -7060,7 +7061,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>14.2</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>14.2</v>
       </c>
@@ -7238,7 +7239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>14.2</v>
       </c>
@@ -7324,7 +7325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>14.2</v>
       </c>
@@ -7413,7 +7414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>14.2</v>
       </c>
@@ -7502,7 +7503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>14.2</v>
       </c>
@@ -7588,7 +7589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>14.2</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>14.2</v>
       </c>
@@ -7766,7 +7767,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>14.2</v>
       </c>
@@ -7852,7 +7853,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>14.2</v>
       </c>
@@ -7941,7 +7942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>14.2</v>
       </c>
@@ -8021,7 +8022,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>14.2</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>14.3</v>
       </c>
@@ -8182,7 +8183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>14.3</v>
       </c>
@@ -8266,7 +8267,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>14.3</v>
       </c>
@@ -8347,7 +8348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14.3</v>
       </c>
@@ -8431,7 +8432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14.3</v>
       </c>
@@ -8515,7 +8516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14.3</v>
       </c>
@@ -8596,7 +8597,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>14.3</v>
       </c>
@@ -8680,7 +8681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>14.3</v>
       </c>
@@ -8764,7 +8765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>14.3</v>
       </c>
@@ -8845,7 +8846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>14.3</v>
       </c>
@@ -8929,7 +8930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>14.3</v>
       </c>
@@ -9013,7 +9014,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>14.3</v>
       </c>
@@ -9094,7 +9095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>14.3</v>
       </c>
@@ -9183,7 +9184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>14.3</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>14.3</v>
       </c>
@@ -9358,7 +9359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>14.3</v>
       </c>
@@ -9447,7 +9448,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>14.3</v>
       </c>
@@ -9536,7 +9537,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>14.3</v>
       </c>
@@ -9622,7 +9623,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>14.3</v>
       </c>
@@ -9711,7 +9712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>14.3</v>
       </c>
@@ -9800,7 +9801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>14.3</v>
       </c>
@@ -9886,7 +9887,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>14.3</v>
       </c>
@@ -9975,7 +9976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>14.3</v>
       </c>
@@ -10064,7 +10065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>14.3</v>
       </c>
@@ -10141,7 +10142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>14.4</v>
       </c>
@@ -10225,7 +10226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>14.4</v>
       </c>
@@ -10309,7 +10310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>14.4</v>
       </c>
@@ -10390,7 +10391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>14.4</v>
       </c>
@@ -10474,7 +10475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>14.4</v>
       </c>
@@ -10558,7 +10559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>14.4</v>
       </c>
@@ -10639,7 +10640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>14.4</v>
       </c>
@@ -10723,7 +10724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>14.4</v>
       </c>
@@ -10807,7 +10808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>14.4</v>
       </c>
@@ -10888,7 +10889,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>14.4</v>
       </c>
@@ -10972,7 +10973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>14.4</v>
       </c>
@@ -11056,7 +11057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>14.4</v>
       </c>
@@ -11137,7 +11138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>14.4</v>
       </c>
@@ -11226,7 +11227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>14.4</v>
       </c>
@@ -11315,7 +11316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>14.4</v>
       </c>
@@ -11401,7 +11402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>14.4</v>
       </c>
@@ -11490,7 +11491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>14.4</v>
       </c>
@@ -11579,7 +11580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>14.4</v>
       </c>
@@ -11665,7 +11666,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>14.4</v>
       </c>
@@ -11754,7 +11755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>14.4</v>
       </c>
@@ -11843,7 +11844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>14.4</v>
       </c>
@@ -11929,7 +11930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>14.4</v>
       </c>
@@ -12018,7 +12019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.4</v>
       </c>
@@ -12107,7 +12108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>14.4</v>
       </c>
@@ -12184,7 +12185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>77</v>
       </c>
@@ -12273,7 +12274,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>77</v>
       </c>
@@ -12362,7 +12363,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>77</v>
       </c>
@@ -12448,7 +12449,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>77</v>
       </c>
@@ -12537,7 +12538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>77</v>
       </c>
@@ -12626,7 +12627,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>77</v>
       </c>
@@ -12712,7 +12713,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>77</v>
       </c>
@@ -12801,7 +12802,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>77</v>
       </c>
@@ -12890,7 +12891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>77</v>
       </c>
@@ -12976,7 +12977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>77</v>
       </c>
@@ -13065,7 +13066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>77</v>
       </c>
@@ -13151,7 +13152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>96</v>
       </c>
@@ -13240,7 +13241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>96</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>96</v>
       </c>
@@ -13415,7 +13416,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>96</v>
       </c>
@@ -13504,7 +13505,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>96</v>
       </c>
@@ -13590,7 +13591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>96</v>
       </c>
@@ -13679,7 +13680,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>96</v>
       </c>
@@ -13768,7 +13769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>96</v>
       </c>
@@ -13854,7 +13855,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>97</v>
       </c>
@@ -13943,7 +13944,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>97</v>
       </c>
@@ -14026,7 +14027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>97</v>
       </c>
@@ -14112,7 +14113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>97</v>
       </c>
@@ -14189,7 +14190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>97</v>
       </c>
@@ -14266,7 +14267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>97</v>
       </c>
@@ -14346,7 +14347,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>97</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>97</v>
       </c>
@@ -14500,7 +14501,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>97</v>
       </c>
@@ -14580,7 +14581,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>97</v>
       </c>
@@ -14660,7 +14661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>98</v>
       </c>
@@ -14743,7 +14744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>98</v>
       </c>
@@ -14832,7 +14833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>98</v>
       </c>
@@ -14918,7 +14919,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>98</v>
       </c>
@@ -15001,7 +15002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>98</v>
       </c>
@@ -15090,7 +15091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>98</v>
       </c>
@@ -15176,7 +15177,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>98</v>
       </c>
@@ -15253,7 +15254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>98</v>
       </c>
@@ -15342,7 +15343,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>98</v>
       </c>
@@ -15428,7 +15429,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>98</v>
       </c>
@@ -15517,7 +15518,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>98</v>
       </c>
@@ -15603,7 +15604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>109</v>
       </c>
@@ -15671,7 +15672,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>109</v>
       </c>
@@ -15754,7 +15755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>109</v>
       </c>
@@ -15822,7 +15823,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>109</v>
       </c>
@@ -15905,7 +15906,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>109</v>
       </c>
@@ -15988,7 +15989,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>148</v>
       </c>
@@ -16074,7 +16075,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>148</v>
       </c>
@@ -16163,7 +16164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>148</v>
       </c>
@@ -16252,7 +16253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>148</v>
       </c>
@@ -16338,7 +16339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>148</v>
       </c>
@@ -16427,7 +16428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>148</v>
       </c>
@@ -16510,7 +16511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>148</v>
       </c>
@@ -16596,7 +16597,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>148</v>
       </c>
@@ -16685,7 +16686,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>148</v>
       </c>
@@ -16771,7 +16772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>193</v>
       </c>
@@ -16860,7 +16861,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>193</v>
       </c>
@@ -16949,7 +16950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>193</v>
       </c>
@@ -17035,7 +17036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>193</v>
       </c>
@@ -17124,7 +17125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>193</v>
       </c>
@@ -17213,7 +17214,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>193</v>
       </c>
@@ -17299,7 +17300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>193</v>
       </c>
@@ -17388,7 +17389,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>193</v>
       </c>
@@ -17477,7 +17478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>193</v>
       </c>
@@ -17563,7 +17564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>193</v>
       </c>
@@ -17652,7 +17653,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>193</v>
       </c>
@@ -17738,7 +17739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>194</v>
       </c>
@@ -17827,7 +17828,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>194</v>
       </c>
@@ -17916,7 +17917,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>194</v>
       </c>
@@ -18002,7 +18003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>194</v>
       </c>
@@ -18091,7 +18092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>194</v>
       </c>
@@ -18180,7 +18181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>194</v>
       </c>
@@ -18266,7 +18267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>194</v>
       </c>
@@ -18355,7 +18356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>194</v>
       </c>
@@ -18444,7 +18445,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -18530,7 +18531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18619,7 +18620,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>194</v>
       </c>
@@ -18705,7 +18706,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>200</v>
       </c>
@@ -18785,7 +18786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>200</v>
       </c>
@@ -18862,7 +18863,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>200</v>
       </c>
@@ -18945,7 +18946,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -19031,7 +19032,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>200</v>
       </c>
@@ -19117,7 +19118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -19201,7 +19202,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>202</v>
       </c>
@@ -19285,7 +19286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>202</v>
       </c>
@@ -19369,7 +19370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>202</v>
       </c>
@@ -19458,7 +19459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>202</v>
       </c>
@@ -19544,7 +19545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>202</v>
       </c>
@@ -19624,7 +19625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>202</v>
       </c>
@@ -19713,7 +19714,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>202</v>
       </c>
@@ -19799,7 +19800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>203</v>
       </c>
@@ -19888,7 +19889,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>203</v>
       </c>
@@ -19977,7 +19978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>203</v>
       </c>
@@ -20063,7 +20064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>203</v>
       </c>
@@ -20152,7 +20153,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>203</v>
       </c>
@@ -20241,7 +20242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>203</v>
       </c>
@@ -20327,7 +20328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>203</v>
       </c>
@@ -20416,7 +20417,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>203</v>
       </c>
@@ -20505,7 +20506,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>203</v>
       </c>
@@ -20591,7 +20592,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>203</v>
       </c>
@@ -20680,7 +20681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>204</v>
       </c>
@@ -20769,7 +20770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>204</v>
       </c>
@@ -20858,7 +20859,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>204</v>
       </c>
@@ -20932,7 +20933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>204</v>
       </c>
@@ -21021,7 +21022,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>204</v>
       </c>
@@ -21110,7 +21111,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>204</v>
       </c>
@@ -21196,7 +21197,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>204</v>
       </c>
@@ -21285,7 +21286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>204</v>
       </c>
@@ -21374,7 +21375,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>204</v>
       </c>
@@ -21460,7 +21461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>204</v>
       </c>
@@ -21549,7 +21550,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>204</v>
       </c>
@@ -21635,7 +21636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>205</v>
       </c>
@@ -21724,7 +21725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>205</v>
       </c>
@@ -21813,7 +21814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>205</v>
       </c>
@@ -21899,7 +21900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>205</v>
       </c>
@@ -21988,7 +21989,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>205</v>
       </c>
@@ -22077,7 +22078,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>205</v>
       </c>
@@ -22163,7 +22164,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>205</v>
       </c>
@@ -22252,7 +22253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>205</v>
       </c>
@@ -22338,7 +22339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>207</v>
       </c>
@@ -22427,7 +22428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>207</v>
       </c>
@@ -22516,7 +22517,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>207</v>
       </c>
@@ -22602,7 +22603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>207</v>
       </c>
@@ -22691,7 +22692,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>207</v>
       </c>
@@ -22780,7 +22781,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>207</v>
       </c>
@@ -22866,7 +22867,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>207</v>
       </c>
@@ -22955,7 +22956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>207</v>
       </c>
@@ -23041,7 +23042,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>228</v>
       </c>
@@ -23124,7 +23125,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>228</v>
       </c>
@@ -23210,7 +23211,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>228</v>
       </c>
@@ -23296,7 +23297,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>228</v>
       </c>
@@ -23367,7 +23368,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>228</v>
       </c>
@@ -23453,7 +23454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>228</v>
       </c>
@@ -23539,7 +23540,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>244</v>
       </c>
@@ -23625,7 +23626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>244</v>
       </c>
@@ -23708,7 +23709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>244</v>
       </c>
@@ -23794,7 +23795,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>244</v>
       </c>
@@ -23877,7 +23878,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>244</v>
       </c>
@@ -23963,7 +23964,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>244</v>
       </c>
@@ -24049,7 +24050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>245</v>
       </c>
@@ -24138,7 +24139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>245</v>
       </c>
@@ -24227,7 +24228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>245</v>
       </c>
@@ -24313,7 +24314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>245</v>
       </c>
@@ -24402,7 +24403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>245</v>
       </c>
@@ -24491,7 +24492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>245</v>
       </c>
@@ -24577,7 +24578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>245</v>
       </c>
@@ -24666,7 +24667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>245</v>
       </c>
@@ -24749,7 +24750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>245</v>
       </c>
@@ -24835,7 +24836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>245</v>
       </c>
@@ -24924,7 +24925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>245</v>
       </c>
@@ -25010,7 +25011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>274</v>
       </c>
@@ -25094,7 +25095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>274</v>
       </c>
@@ -25178,7 +25179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>274</v>
       </c>
@@ -25259,7 +25260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>274</v>
       </c>
@@ -25343,7 +25344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -25427,7 +25428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>274</v>
       </c>
@@ -25508,7 +25509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25592,7 +25593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25676,7 +25677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -25757,7 +25758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>274</v>
       </c>
@@ -25841,7 +25842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>274</v>
       </c>
@@ -25925,7 +25926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>274</v>
       </c>
@@ -26006,7 +26007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -26095,7 +26096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>274</v>
       </c>
@@ -26184,7 +26185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>274</v>
       </c>
@@ -26270,7 +26271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>274</v>
       </c>
@@ -26359,7 +26360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>274</v>
       </c>
@@ -26448,7 +26449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>274</v>
       </c>
@@ -26534,7 +26535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>274</v>
       </c>
@@ -26623,7 +26624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>274</v>
       </c>
@@ -26712,7 +26713,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>274</v>
       </c>
@@ -26798,7 +26799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>274</v>
       </c>
@@ -26887,7 +26888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>274</v>
       </c>
@@ -26974,7 +26975,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>274</v>
       </c>
@@ -27058,7 +27059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>276</v>
       </c>
@@ -27141,7 +27142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>276</v>
       </c>
@@ -27224,7 +27225,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>276</v>
       </c>
@@ -27310,7 +27311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>276</v>
       </c>
@@ -27393,7 +27394,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>276</v>
       </c>
@@ -27476,7 +27477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>276</v>
       </c>
@@ -27562,7 +27563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>276</v>
       </c>
@@ -27645,7 +27646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>276</v>
       </c>
@@ -27728,7 +27729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>276</v>
       </c>
@@ -27814,7 +27815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>276</v>
       </c>
@@ -27903,7 +27904,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>276</v>
       </c>
@@ -27989,7 +27990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>277</v>
       </c>
@@ -28069,7 +28070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>277</v>
       </c>
@@ -28149,7 +28150,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>277</v>
       </c>
@@ -28232,7 +28233,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>277</v>
       </c>
@@ -28312,7 +28313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>277</v>
       </c>
@@ -28392,7 +28393,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>277</v>
       </c>
@@ -28475,7 +28476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>277</v>
       </c>
@@ -28561,7 +28562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>277</v>
       </c>
@@ -28644,7 +28645,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>323</v>
       </c>
@@ -28727,7 +28728,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>323</v>
       </c>
@@ -28813,7 +28814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>323</v>
       </c>
@@ -28896,7 +28897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>323</v>
       </c>
@@ -28979,7 +28980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>323</v>
       </c>
@@ -29065,7 +29066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>323</v>
       </c>
@@ -29148,7 +29149,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>323</v>
       </c>
@@ -29225,7 +29226,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>323</v>
       </c>
@@ -29311,7 +29312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>323</v>
       </c>
@@ -29400,7 +29401,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -29486,7 +29487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>325</v>
       </c>
@@ -29575,7 +29576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>325</v>
       </c>
@@ -29664,7 +29665,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -29750,7 +29751,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>325</v>
       </c>
@@ -29839,7 +29840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>325</v>
       </c>
@@ -29916,7 +29917,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>325</v>
       </c>
@@ -30002,7 +30003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>325</v>
       </c>
@@ -30091,7 +30092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>325</v>
       </c>
@@ -30180,7 +30181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>325</v>
       </c>
@@ -30266,7 +30267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>325</v>
       </c>
@@ -30355,7 +30356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>325</v>
       </c>
@@ -30441,7 +30442,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>331</v>
       </c>
@@ -30524,7 +30525,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>331</v>
       </c>
@@ -30601,7 +30602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>331</v>
       </c>
@@ -30684,7 +30685,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>331</v>
       </c>
@@ -30761,7 +30762,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>331</v>
       </c>
@@ -30841,7 +30842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>331</v>
       </c>
@@ -30918,7 +30919,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>332</v>
       </c>
@@ -31001,7 +31002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>332</v>
       </c>
@@ -31084,7 +31085,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>332</v>
       </c>
@@ -31170,7 +31171,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="344" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>332</v>
       </c>
@@ -31253,7 +31254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="345" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>332</v>
       </c>
@@ -31336,7 +31337,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="346" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>332</v>
       </c>
@@ -31422,7 +31423,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>332</v>
       </c>
@@ -31511,7 +31512,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>332</v>
       </c>
@@ -31594,7 +31595,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>332</v>
       </c>
@@ -31680,7 +31681,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>332</v>
       </c>
@@ -31769,7 +31770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>332</v>
       </c>
@@ -31855,7 +31856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>334</v>
       </c>
@@ -31941,7 +31942,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>334</v>
       </c>
@@ -32024,7 +32025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>334</v>
       </c>
@@ -32110,7 +32111,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>334</v>
       </c>
@@ -32193,7 +32194,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>334</v>
       </c>
@@ -32279,7 +32280,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>334</v>
       </c>
@@ -32365,7 +32366,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>335</v>
       </c>
@@ -32451,7 +32452,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>335</v>
       </c>
@@ -32534,7 +32535,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>335</v>
       </c>
@@ -32620,7 +32621,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>335</v>
       </c>
@@ -32703,7 +32704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>335</v>
       </c>
@@ -32786,7 +32787,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>339</v>
       </c>
@@ -32875,7 +32876,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>339</v>
       </c>
@@ -32961,7 +32962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>339</v>
       </c>
@@ -33050,7 +33051,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>339</v>
       </c>
@@ -33136,7 +33137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>339</v>
       </c>
@@ -33225,7 +33226,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>339</v>
       </c>
@@ -33311,7 +33312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>361</v>
       </c>
@@ -33392,7 +33393,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>361</v>
       </c>
@@ -33481,7 +33482,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>361</v>
       </c>
@@ -33567,7 +33568,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>361</v>
       </c>
@@ -33647,7 +33648,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>361</v>
       </c>
@@ -33737,7 +33738,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>361</v>
       </c>
@@ -33824,7 +33825,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>364</v>
       </c>
@@ -33913,7 +33914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>364</v>
       </c>
@@ -34002,7 +34003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>364</v>
       </c>
@@ -34079,7 +34080,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>364</v>
       </c>
@@ -34168,7 +34169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>364</v>
       </c>
@@ -34257,7 +34258,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>364</v>
       </c>
@@ -34343,7 +34344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>364</v>
       </c>
@@ -34432,7 +34433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>364</v>
       </c>
@@ -34518,7 +34519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>367</v>
       </c>
@@ -34604,7 +34605,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>367</v>
       </c>
@@ -34693,7 +34694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>367</v>
       </c>
@@ -34779,7 +34780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>367</v>
       </c>
@@ -34868,7 +34869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>367</v>
       </c>
@@ -34954,7 +34955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>367</v>
       </c>
@@ -35040,7 +35041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>369</v>
       </c>
@@ -35123,7 +35124,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>369</v>
       </c>
@@ -35206,7 +35207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>369</v>
       </c>
@@ -35283,7 +35284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>369</v>
       </c>
@@ -35372,7 +35373,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>369</v>
       </c>
@@ -35461,7 +35462,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>369</v>
       </c>
@@ -35547,7 +35548,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>369</v>
       </c>
@@ -35636,7 +35637,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>369</v>
       </c>
@@ -35722,7 +35723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>376</v>
       </c>
@@ -35812,7 +35813,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>376</v>
       </c>
@@ -35898,7 +35899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>376</v>
       </c>
@@ -35987,7 +35988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>376</v>
       </c>
@@ -36073,7 +36074,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>376</v>
       </c>
@@ -36162,7 +36163,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -36248,7 +36249,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -36337,7 +36338,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -37037,7 +37038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>379</v>
       </c>
@@ -37121,7 +37122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>379</v>
       </c>
@@ -37202,7 +37203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>379</v>
       </c>
@@ -37286,7 +37287,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>379</v>
       </c>
@@ -37370,7 +37371,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>379</v>
       </c>
@@ -37454,7 +37455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>379</v>
       </c>
@@ -37535,7 +37536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>379</v>
       </c>
@@ -37619,7 +37620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>379</v>
       </c>
@@ -37703,7 +37704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>379</v>
       </c>
@@ -37784,7 +37785,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>379</v>
       </c>
@@ -37868,7 +37869,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>379</v>
       </c>
@@ -37952,7 +37953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>379</v>
       </c>
@@ -38033,7 +38034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>379</v>
       </c>
@@ -38122,7 +38123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>379</v>
       </c>
@@ -38211,7 +38212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>379</v>
       </c>
@@ -38297,7 +38298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>379</v>
       </c>
@@ -38386,7 +38387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="428" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>379</v>
       </c>
@@ -38475,7 +38476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="429" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>379</v>
       </c>
@@ -38561,7 +38562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="430" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>379</v>
       </c>
@@ -38650,7 +38651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>379</v>
       </c>
@@ -38739,7 +38740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="432" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>379</v>
       </c>
@@ -38825,7 +38826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="433" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>379</v>
       </c>
@@ -38914,7 +38915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>379</v>
       </c>
@@ -38992,7 +38993,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="435" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>379</v>
       </c>
@@ -39076,7 +39077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="436" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>385</v>
       </c>
@@ -39165,7 +39166,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="437" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>385</v>
       </c>
@@ -39254,7 +39255,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>385</v>
       </c>
@@ -39343,7 +39344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>385</v>
       </c>
@@ -39432,7 +39433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>385</v>
       </c>
@@ -39521,7 +39522,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>385</v>
       </c>
@@ -39610,7 +39611,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="442" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>385</v>
       </c>
@@ -39693,7 +39694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="443" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>385</v>
       </c>
@@ -39767,7 +39768,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="444" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>386.1</v>
       </c>
@@ -39850,7 +39851,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="445" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>386.1</v>
       </c>
@@ -39933,7 +39934,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="446" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>386.1</v>
       </c>
@@ -40019,7 +40020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="447" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>386.1</v>
       </c>
@@ -40108,7 +40109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="448" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>386.1</v>
       </c>
@@ -40197,7 +40198,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="449" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>386.1</v>
       </c>
@@ -40283,7 +40284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="450" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>386.1</v>
       </c>
@@ -40366,7 +40367,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="451" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>386.1</v>
       </c>
@@ -40446,7 +40447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="452" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>386.2</v>
       </c>
@@ -40535,7 +40536,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>386.2</v>
       </c>
@@ -40624,7 +40625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>386.2</v>
       </c>
@@ -40710,7 +40711,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="455" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>386.2</v>
       </c>
@@ -40799,7 +40800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="456" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>386.2</v>
       </c>
@@ -40888,7 +40889,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="457" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>386.2</v>
       </c>
@@ -40974,7 +40975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="458" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>386.2</v>
       </c>
@@ -41057,7 +41058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>386.2</v>
       </c>
@@ -41137,7 +41138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="460" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>386.3</v>
       </c>
@@ -41226,7 +41227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>386.3</v>
       </c>
@@ -41315,7 +41316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="462" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>386.3</v>
       </c>
@@ -41401,7 +41402,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="463" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>386.3</v>
       </c>
@@ -41490,7 +41491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="464" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>386.3</v>
       </c>
@@ -41579,7 +41580,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="465" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>386.3</v>
       </c>
@@ -41665,7 +41666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="466" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>386.3</v>
       </c>
@@ -41748,7 +41749,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="467" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>386.3</v>
       </c>
@@ -41828,7 +41829,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="468" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>423</v>
       </c>
@@ -41911,7 +41912,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="469" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>423</v>
       </c>
@@ -41997,7 +41998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="470" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>423</v>
       </c>
@@ -42080,7 +42081,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>423</v>
       </c>
@@ -42166,7 +42167,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>423</v>
       </c>
@@ -42249,7 +42250,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>423</v>
       </c>
@@ -42335,7 +42336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>423</v>
       </c>
@@ -42421,7 +42422,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>424</v>
       </c>
@@ -42504,7 +42505,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>424</v>
       </c>
@@ -42590,7 +42591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="477" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>424</v>
       </c>
@@ -42673,7 +42674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>424</v>
       </c>
@@ -42759,7 +42760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="479" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>424</v>
       </c>
@@ -42842,7 +42843,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="480" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>424</v>
       </c>
@@ -42928,7 +42929,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>424</v>
       </c>
@@ -43014,7 +43015,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="482" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>460</v>
       </c>
@@ -43091,7 +43092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>460</v>
       </c>
@@ -43180,7 +43181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="484" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>460</v>
       </c>
@@ -43260,7 +43261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="485" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>460</v>
       </c>
@@ -43346,7 +43347,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>460</v>
       </c>
@@ -43432,7 +43433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="487" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>466</v>
       </c>
@@ -43518,7 +43519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="488" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>466</v>
       </c>
@@ -43604,7 +43605,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="489" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>466</v>
       </c>
@@ -43687,7 +43688,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="490" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>466</v>
       </c>
@@ -43770,7 +43771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="491" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>466</v>
       </c>
@@ -43856,7 +43857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>466</v>
       </c>
@@ -43942,7 +43943,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="493" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>203</v>
       </c>
@@ -44026,7 +44027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="494" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>203</v>
       </c>
@@ -44108,7 +44109,18 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC494" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC494" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="377"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="28">
+      <filters>
+        <filter val="Anual"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC492">
     <sortCondition ref="A2:A492"/>
     <sortCondition ref="F2:F492"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="931" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57EA6144-49B1-4345-B8B4-792ECD1771F2}"/>
+  <xr:revisionPtr revIDLastSave="1105" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E2E8C4-F466-48B9-A4FA-DF4DDD1B0CDD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Cierres_Original" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14038" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14138" uniqueCount="494">
   <si>
     <t>Id</t>
   </si>
@@ -1504,15 +1504,34 @@
   <si>
     <t>466-2025-12-31</t>
   </si>
+  <si>
+    <t>109-2025-12-31</t>
+  </si>
+  <si>
+    <t>386.2-2025-12-31</t>
+  </si>
+  <si>
+    <t>386.1-2025-12-31</t>
+  </si>
+  <si>
+    <t>386.1-2022-12-31</t>
+  </si>
+  <si>
+    <t>386.3-2025-12-31</t>
+  </si>
+  <si>
+    <t>386.3-2022-12-31</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1580,12 +1599,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1596,9 +1616,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E6474115-E034-47AA-AE39-934325146E0E}"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
@@ -1901,7 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC500"/>
+  <dimension ref="A1:AC505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -1909,8 +1931,10 @@
     <col min="6" max="6" width="10.33203125" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="71.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15651,6 +15675,24 @@
       <c r="J162">
         <v>2</v>
       </c>
+      <c r="K162">
+        <v>80</v>
+      </c>
+      <c r="L162">
+        <v>87.392767703668298</v>
+      </c>
+      <c r="M162">
+        <v>1.092409596295854</v>
+      </c>
+      <c r="N162">
+        <v>1.092409596295854</v>
+      </c>
+      <c r="O162" t="s">
+        <v>58</v>
+      </c>
+      <c r="P162" t="s">
+        <v>58</v>
+      </c>
       <c r="Q162" t="s">
         <v>98</v>
       </c>
@@ -15802,6 +15844,24 @@
       <c r="J164">
         <v>2</v>
       </c>
+      <c r="K164">
+        <v>80</v>
+      </c>
+      <c r="L164">
+        <v>85</v>
+      </c>
+      <c r="M164">
+        <v>1.0625</v>
+      </c>
+      <c r="N164">
+        <v>1.0625</v>
+      </c>
+      <c r="O164" t="s">
+        <v>58</v>
+      </c>
+      <c r="P164" t="s">
+        <v>58</v>
+      </c>
       <c r="Q164" t="s">
         <v>103</v>
       </c>
@@ -15939,25 +15999,26 @@
         <v>32</v>
       </c>
       <c r="F166" s="3">
-        <v>45838</v>
+        <v>46022</v>
       </c>
       <c r="G166">
         <v>2025</v>
       </c>
       <c r="H166" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I166" t="s">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="K166">
         <v>80</v>
       </c>
       <c r="L166">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="M166">
-        <v>1.0625</v>
+        <f>+L166/K166</f>
+        <v>1.175</v>
       </c>
       <c r="N166">
         <v>1.0625</v>
@@ -15969,7 +16030,7 @@
         <v>58</v>
       </c>
       <c r="Q166" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="R166">
         <v>0</v>
@@ -39210,18 +39271,15 @@
       <c r="I437" t="s">
         <v>45</v>
       </c>
+      <c r="J437">
+        <v>2</v>
+      </c>
       <c r="K437">
         <v>13361</v>
       </c>
       <c r="L437">
         <v>10035.311890999999</v>
       </c>
-      <c r="M437">
-        <v>0.75108988032332902</v>
-      </c>
-      <c r="N437">
-        <v>0.75108988032332902</v>
-      </c>
       <c r="O437" t="s">
         <v>143</v>
       </c>
@@ -39238,7 +39296,7 @@
         <v>0</v>
       </c>
       <c r="T437" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U437" t="s">
         <v>37</v>
@@ -39285,28 +39343,22 @@
         <v>32</v>
       </c>
       <c r="F438" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G438">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H438" t="s">
         <v>44</v>
       </c>
       <c r="I438" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K438">
-        <v>14097.721</v>
+        <v>13361</v>
       </c>
       <c r="L438">
-        <v>17697.080526999998</v>
-      </c>
-      <c r="M438">
-        <v>1.2553149921891629</v>
-      </c>
-      <c r="N438">
-        <v>1.2553149921891629</v>
+        <v>10035.311890999999</v>
       </c>
       <c r="O438" t="s">
         <v>143</v>
@@ -39315,7 +39367,7 @@
         <v>143</v>
       </c>
       <c r="Q438" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="R438">
         <v>0</v>
@@ -39371,28 +39423,25 @@
         <v>32</v>
       </c>
       <c r="F439" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G439">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H439" t="s">
         <v>44</v>
       </c>
       <c r="I439" t="s">
-        <v>53</v>
+        <v>49</v>
+      </c>
+      <c r="J439">
+        <v>2</v>
       </c>
       <c r="K439">
-        <v>15507.493100000003</v>
+        <v>14097.721</v>
       </c>
       <c r="L439">
-        <v>13243.138849000001</v>
-      </c>
-      <c r="M439">
-        <v>0.85398321724869886</v>
-      </c>
-      <c r="N439">
-        <v>0.85398321724869886</v>
+        <v>17697.080526999998</v>
       </c>
       <c r="O439" t="s">
         <v>143</v>
@@ -39401,7 +39450,7 @@
         <v>143</v>
       </c>
       <c r="Q439" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="R439">
         <v>0</v>
@@ -39410,7 +39459,7 @@
         <v>0</v>
       </c>
       <c r="T439" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U439" t="s">
         <v>37</v>
@@ -39457,28 +39506,22 @@
         <v>32</v>
       </c>
       <c r="F440" s="3">
-        <v>46022</v>
+        <v>45291</v>
       </c>
       <c r="G440">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H440" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I440" t="s">
-        <v>404</v>
+        <v>49</v>
       </c>
       <c r="K440">
-        <v>6845.8773119999996</v>
+        <v>14097.721</v>
       </c>
       <c r="L440">
-        <v>17058.242411318402</v>
-      </c>
-      <c r="M440">
-        <v>1.284122942663686</v>
-      </c>
-      <c r="N440">
-        <v>1.284122942663686</v>
+        <v>17697.080526999998</v>
       </c>
       <c r="O440" t="s">
         <v>143</v>
@@ -39487,7 +39530,7 @@
         <v>143</v>
       </c>
       <c r="Q440" t="s">
-        <v>486</v>
+        <v>317</v>
       </c>
       <c r="R440">
         <v>0</v>
@@ -39513,6 +39556,12 @@
       <c r="Y440" t="s">
         <v>314</v>
       </c>
+      <c r="Z440" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA440" t="s">
+        <v>148</v>
+      </c>
       <c r="AB440" t="s">
         <v>43</v>
       </c>
@@ -39522,10 +39571,10 @@
     </row>
     <row r="441" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A441">
-        <v>386.1</v>
+        <v>385</v>
       </c>
       <c r="B441" t="s">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="C441" t="s">
         <v>310</v>
@@ -39537,34 +39586,34 @@
         <v>32</v>
       </c>
       <c r="F441" s="3">
-        <v>45107</v>
+        <v>45657</v>
       </c>
       <c r="G441">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H441" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I441" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J441">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K441">
-        <v>240.869</v>
+        <v>15507.493100000003</v>
       </c>
       <c r="L441">
-        <v>883.81096500000001</v>
-      </c>
-      <c r="M441">
-        <v>1.3</v>
-      </c>
-      <c r="N441">
-        <v>3.6692599089131441</v>
+        <v>13243.138849000001</v>
+      </c>
+      <c r="O441" t="s">
+        <v>143</v>
+      </c>
+      <c r="P441" t="s">
+        <v>143</v>
       </c>
       <c r="Q441" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="R441">
         <v>0</v>
@@ -39597,7 +39646,7 @@
         <v>148</v>
       </c>
       <c r="AB441" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC441" t="s">
         <v>66</v>
@@ -39605,10 +39654,10 @@
     </row>
     <row r="442" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A442">
-        <v>386.1</v>
+        <v>385</v>
       </c>
       <c r="B442" t="s">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="C442" t="s">
         <v>310</v>
@@ -39620,34 +39669,31 @@
         <v>32</v>
       </c>
       <c r="F442" s="3">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G442">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H442" t="s">
         <v>44</v>
       </c>
       <c r="I442" t="s">
-        <v>49</v>
-      </c>
-      <c r="J442">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="K442">
-        <v>1116.9090000000001</v>
+        <v>15507.493100000003</v>
       </c>
       <c r="L442">
-        <v>2896.1173829999998</v>
-      </c>
-      <c r="M442">
-        <v>1.3</v>
-      </c>
-      <c r="N442">
-        <v>2.5929752405970401</v>
+        <v>13243.138849000001</v>
+      </c>
+      <c r="O442" t="s">
+        <v>143</v>
+      </c>
+      <c r="P442" t="s">
+        <v>143</v>
       </c>
       <c r="Q442" t="s">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="R442">
         <v>0</v>
@@ -39656,7 +39702,7 @@
         <v>0</v>
       </c>
       <c r="T442" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U442" t="s">
         <v>37</v>
@@ -39680,7 +39726,7 @@
         <v>148</v>
       </c>
       <c r="AB442" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC442" t="s">
         <v>66</v>
@@ -39688,10 +39734,10 @@
     </row>
     <row r="443" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A443">
-        <v>386.1</v>
+        <v>385</v>
       </c>
       <c r="B443" t="s">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c r="C443" t="s">
         <v>310</v>
@@ -39703,28 +39749,23 @@
         <v>32</v>
       </c>
       <c r="F443" s="3">
-        <v>45291</v>
+        <v>46022</v>
       </c>
       <c r="G443">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H443" t="s">
         <v>44</v>
       </c>
       <c r="I443" t="s">
-        <v>49</v>
-      </c>
-      <c r="K443">
-        <v>1357.778</v>
+        <v>465</v>
+      </c>
+      <c r="J443">
+        <v>2</v>
       </c>
       <c r="L443">
-        <v>3779.9283479999999</v>
-      </c>
-      <c r="M443">
-        <v>1.3</v>
-      </c>
-      <c r="N443">
-        <v>2.7839074929774972</v>
+        <f>17058242411/1000000</f>
+        <v>17058.242410999999</v>
       </c>
       <c r="O443" t="s">
         <v>143</v>
@@ -39733,7 +39774,7 @@
         <v>143</v>
       </c>
       <c r="Q443" t="s">
-        <v>379</v>
+        <v>486</v>
       </c>
       <c r="R443">
         <v>0</v>
@@ -39742,7 +39783,7 @@
         <v>0</v>
       </c>
       <c r="T443" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U443" t="s">
         <v>37</v>
@@ -39759,14 +39800,8 @@
       <c r="Y443" t="s">
         <v>314</v>
       </c>
-      <c r="Z443" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA443" t="s">
-        <v>148</v>
-      </c>
       <c r="AB443" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC443" t="s">
         <v>66</v>
@@ -39789,31 +39824,23 @@
         <v>32</v>
       </c>
       <c r="F444" s="3">
-        <v>45473</v>
+        <v>44926</v>
       </c>
       <c r="G444">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H444" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I444" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J444">
-        <v>1</v>
-      </c>
-      <c r="K444">
-        <v>817.70707000000004</v>
+        <v>2</v>
       </c>
       <c r="L444">
-        <v>1076.3764839999999</v>
-      </c>
-      <c r="M444">
-        <v>1.3</v>
-      </c>
-      <c r="N444">
-        <v>1.3163350587148519</v>
+        <f>894406923/1000000</f>
+        <v>894.40692300000001</v>
       </c>
       <c r="O444" t="s">
         <v>143</v>
@@ -39822,7 +39849,7 @@
         <v>143</v>
       </c>
       <c r="Q444" t="s">
-        <v>380</v>
+        <v>491</v>
       </c>
       <c r="R444">
         <v>0</v>
@@ -39878,31 +39905,20 @@
         <v>32</v>
       </c>
       <c r="F445" s="3">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="G445">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H445" t="s">
         <v>44</v>
       </c>
       <c r="I445" t="s">
-        <v>53</v>
-      </c>
-      <c r="J445">
-        <v>2</v>
-      </c>
-      <c r="K445">
-        <v>2606.5003262</v>
+        <v>45</v>
       </c>
       <c r="L445">
-        <v>3617.8366059999998</v>
-      </c>
-      <c r="M445">
-        <v>1.3</v>
-      </c>
-      <c r="N445">
-        <v>1.3880054299760709</v>
+        <f>894406923/1000000</f>
+        <v>894.40692300000001</v>
       </c>
       <c r="O445" t="s">
         <v>143</v>
@@ -39911,7 +39927,7 @@
         <v>143</v>
       </c>
       <c r="Q445" t="s">
-        <v>381</v>
+        <v>491</v>
       </c>
       <c r="R445">
         <v>0</v>
@@ -39920,7 +39936,7 @@
         <v>0</v>
       </c>
       <c r="T445" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U445" t="s">
         <v>37</v>
@@ -39967,28 +39983,22 @@
         <v>32</v>
       </c>
       <c r="F446" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G446">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H446" t="s">
         <v>44</v>
       </c>
       <c r="I446" t="s">
-        <v>53</v>
-      </c>
-      <c r="K446">
-        <v>3424.207396199999</v>
+        <v>49</v>
+      </c>
+      <c r="J446">
+        <v>2</v>
       </c>
       <c r="L446">
-        <v>4694.2130900000002</v>
-      </c>
-      <c r="M446">
-        <v>1.3</v>
-      </c>
-      <c r="N446">
-        <v>1.3708904125402519</v>
+        <v>3779.9283479999999</v>
       </c>
       <c r="O446" t="s">
         <v>143</v>
@@ -39997,7 +40007,7 @@
         <v>143</v>
       </c>
       <c r="Q446" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="R446">
         <v>0</v>
@@ -40006,7 +40016,7 @@
         <v>0</v>
       </c>
       <c r="T446" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U446" t="s">
         <v>37</v>
@@ -40053,31 +40063,19 @@
         <v>32</v>
       </c>
       <c r="F447" s="3">
-        <v>45838</v>
+        <v>45291</v>
       </c>
       <c r="G447">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H447" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I447" t="s">
-        <v>404</v>
-      </c>
-      <c r="J447">
-        <v>1</v>
-      </c>
-      <c r="K447">
-        <v>1392.56187</v>
+        <v>49</v>
       </c>
       <c r="L447">
-        <v>1610.582185</v>
-      </c>
-      <c r="M447">
-        <v>1.1565605950419999</v>
-      </c>
-      <c r="N447">
-        <v>1.1565605950419999</v>
+        <v>3779.9283479999999</v>
       </c>
       <c r="O447" t="s">
         <v>143</v>
@@ -40086,7 +40084,7 @@
         <v>143</v>
       </c>
       <c r="Q447" t="s">
-        <v>438</v>
+        <v>379</v>
       </c>
       <c r="R447">
         <v>0</v>
@@ -40095,7 +40093,7 @@
         <v>0</v>
       </c>
       <c r="T447" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U447" t="s">
         <v>37</v>
@@ -40111,6 +40109,12 @@
       </c>
       <c r="Y447" t="s">
         <v>314</v>
+      </c>
+      <c r="Z447" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA447" t="s">
+        <v>148</v>
       </c>
       <c r="AB447" t="s">
         <v>78</v>
@@ -40136,28 +40140,22 @@
         <v>32</v>
       </c>
       <c r="F448" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G448">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H448" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I448" t="s">
-        <v>404</v>
-      </c>
-      <c r="K448">
-        <v>1392.56187</v>
+        <v>53</v>
+      </c>
+      <c r="J448">
+        <v>2</v>
       </c>
       <c r="L448">
-        <v>1610.582185</v>
-      </c>
-      <c r="M448">
-        <v>1.1565605950419999</v>
-      </c>
-      <c r="N448">
-        <v>1.1565605950419999</v>
+        <v>4694.2130900000002</v>
       </c>
       <c r="O448" t="s">
         <v>143</v>
@@ -40166,7 +40164,7 @@
         <v>143</v>
       </c>
       <c r="Q448" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="R448">
         <v>0</v>
@@ -40175,7 +40173,7 @@
         <v>0</v>
       </c>
       <c r="T448" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U448" t="s">
         <v>37</v>
@@ -40192,6 +40190,12 @@
       <c r="Y448" t="s">
         <v>314</v>
       </c>
+      <c r="Z448" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA448" t="s">
+        <v>148</v>
+      </c>
       <c r="AB448" t="s">
         <v>78</v>
       </c>
@@ -40201,10 +40205,10 @@
     </row>
     <row r="449" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A449">
-        <v>386.2</v>
+        <v>386.1</v>
       </c>
       <c r="B449" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C449" t="s">
         <v>310</v>
@@ -40216,31 +40220,19 @@
         <v>32</v>
       </c>
       <c r="F449" s="3">
-        <v>45107</v>
+        <v>45657</v>
       </c>
       <c r="G449">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H449" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I449" t="s">
-        <v>47</v>
-      </c>
-      <c r="J449">
-        <v>1</v>
-      </c>
-      <c r="K449">
-        <v>2268.5070000000001</v>
+        <v>53</v>
       </c>
       <c r="L449">
-        <v>2406.8934370000002</v>
-      </c>
-      <c r="M449">
-        <v>1.0610033105474219</v>
-      </c>
-      <c r="N449">
-        <v>1.0610033105474219</v>
+        <v>4694.2130900000002</v>
       </c>
       <c r="O449" t="s">
         <v>143</v>
@@ -40249,7 +40241,7 @@
         <v>143</v>
       </c>
       <c r="Q449" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="R449">
         <v>0</v>
@@ -40258,7 +40250,7 @@
         <v>0</v>
       </c>
       <c r="T449" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U449" t="s">
         <v>37</v>
@@ -40290,10 +40282,10 @@
     </row>
     <row r="450" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A450">
-        <v>386.2</v>
+        <v>386.1</v>
       </c>
       <c r="B450" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C450" t="s">
         <v>310</v>
@@ -40305,31 +40297,23 @@
         <v>32</v>
       </c>
       <c r="F450" s="3">
-        <v>45291</v>
+        <v>46022</v>
       </c>
       <c r="G450">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H450" t="s">
         <v>44</v>
       </c>
       <c r="I450" t="s">
-        <v>49</v>
+        <v>465</v>
       </c>
       <c r="J450">
         <v>2</v>
       </c>
-      <c r="K450">
-        <v>4813.4959999999992</v>
-      </c>
       <c r="L450">
-        <v>7461.524879999999</v>
-      </c>
-      <c r="M450">
-        <v>1.3</v>
-      </c>
-      <c r="N450">
-        <v>1.5501259126422871</v>
+        <f>4042632396/1000000</f>
+        <v>4042.632396</v>
       </c>
       <c r="O450" t="s">
         <v>143</v>
@@ -40338,7 +40322,7 @@
         <v>143</v>
       </c>
       <c r="Q450" t="s">
-        <v>384</v>
+        <v>490</v>
       </c>
       <c r="R450">
         <v>0</v>
@@ -40363,12 +40347,6 @@
       </c>
       <c r="Y450" t="s">
         <v>314</v>
-      </c>
-      <c r="Z450" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA450" t="s">
-        <v>148</v>
       </c>
       <c r="AB450" t="s">
         <v>78</v>
@@ -40394,28 +40372,24 @@
         <v>32</v>
       </c>
       <c r="F451" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G451">
-        <v>2023</v>
+        <f>YEAR(F451)</f>
+        <v>2022</v>
       </c>
       <c r="H451" t="s">
         <v>44</v>
       </c>
       <c r="I451" t="s">
-        <v>49</v>
-      </c>
-      <c r="K451">
-        <v>7082.0029999999988</v>
+        <v>45</v>
+      </c>
+      <c r="J451">
+        <v>2</v>
       </c>
       <c r="L451">
-        <v>9868.4183169999997</v>
-      </c>
-      <c r="M451">
-        <v>1.3</v>
-      </c>
-      <c r="N451">
-        <v>1.393450174618678</v>
+        <f>5335242827/1000000</f>
+        <v>5335.242827</v>
       </c>
       <c r="O451" t="s">
         <v>143</v>
@@ -40433,7 +40407,7 @@
         <v>0</v>
       </c>
       <c r="T451" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U451" t="s">
         <v>37</v>
@@ -40480,31 +40454,21 @@
         <v>32</v>
       </c>
       <c r="F452" s="3">
-        <v>45473</v>
+        <v>44926</v>
       </c>
       <c r="G452">
-        <v>2024</v>
+        <f>YEAR(F452)</f>
+        <v>2022</v>
       </c>
       <c r="H452" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I452" t="s">
-        <v>51</v>
-      </c>
-      <c r="J452">
-        <v>1</v>
-      </c>
-      <c r="K452">
-        <v>2674.9657400000001</v>
+        <v>45</v>
       </c>
       <c r="L452">
-        <v>2915.5557789999998</v>
-      </c>
-      <c r="M452">
-        <v>1.089941353417109</v>
-      </c>
-      <c r="N452">
-        <v>1.089941353417109</v>
+        <f>5335242827/1000000</f>
+        <v>5335.242827</v>
       </c>
       <c r="O452" t="s">
         <v>143</v>
@@ -40513,7 +40477,7 @@
         <v>143</v>
       </c>
       <c r="Q452" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R452">
         <v>0</v>
@@ -40522,7 +40486,7 @@
         <v>0</v>
       </c>
       <c r="T452" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U452" t="s">
         <v>37</v>
@@ -40569,31 +40533,22 @@
         <v>32</v>
       </c>
       <c r="F453" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G453">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H453" t="s">
         <v>44</v>
       </c>
       <c r="I453" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J453">
         <v>2</v>
       </c>
-      <c r="K453">
-        <v>5036.1600211000004</v>
-      </c>
       <c r="L453">
-        <v>1255.13023</v>
-      </c>
-      <c r="M453">
-        <v>1.089941353417109</v>
-      </c>
-      <c r="N453">
-        <v>1.089941353417109</v>
+        <v>9868.4183169999997</v>
       </c>
       <c r="O453" t="s">
         <v>143</v>
@@ -40602,7 +40557,7 @@
         <v>143</v>
       </c>
       <c r="Q453" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R453">
         <v>0</v>
@@ -40658,28 +40613,19 @@
         <v>32</v>
       </c>
       <c r="F454" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G454">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H454" t="s">
         <v>44</v>
       </c>
       <c r="I454" t="s">
-        <v>53</v>
-      </c>
-      <c r="K454">
-        <v>7711.1257611000001</v>
+        <v>49</v>
       </c>
       <c r="L454">
-        <v>4170.686009</v>
-      </c>
-      <c r="M454">
-        <v>0.54086603411912804</v>
-      </c>
-      <c r="N454">
-        <v>0.54086603411912804</v>
+        <v>9868.4183169999997</v>
       </c>
       <c r="O454" t="s">
         <v>143</v>
@@ -40688,7 +40634,7 @@
         <v>143</v>
       </c>
       <c r="Q454" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R454">
         <v>0</v>
@@ -40744,31 +40690,22 @@
         <v>32</v>
       </c>
       <c r="F455" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G455">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H455" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I455" t="s">
-        <v>404</v>
+        <v>53</v>
       </c>
       <c r="J455">
-        <v>1</v>
-      </c>
-      <c r="K455">
-        <v>2655.6515559999998</v>
+        <v>2</v>
       </c>
       <c r="L455">
-        <v>3358.9061839999999</v>
-      </c>
-      <c r="M455">
-        <v>1.264814345244621</v>
-      </c>
-      <c r="N455">
-        <v>1.264814345244621</v>
+        <v>4170.686009</v>
       </c>
       <c r="O455" t="s">
         <v>143</v>
@@ -40777,7 +40714,7 @@
         <v>143</v>
       </c>
       <c r="Q455" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="R455">
         <v>0</v>
@@ -40802,6 +40739,12 @@
       </c>
       <c r="Y455" t="s">
         <v>314</v>
+      </c>
+      <c r="Z455" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA455" t="s">
+        <v>148</v>
       </c>
       <c r="AB455" t="s">
         <v>78</v>
@@ -40827,28 +40770,19 @@
         <v>32</v>
       </c>
       <c r="F456" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G456">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H456" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I456" t="s">
-        <v>404</v>
-      </c>
-      <c r="K456">
-        <v>2655.6515559999998</v>
+        <v>53</v>
       </c>
       <c r="L456">
-        <v>3358.9061839999999</v>
-      </c>
-      <c r="M456">
-        <v>1.264814345244621</v>
-      </c>
-      <c r="N456">
-        <v>1.264814345244621</v>
+        <v>4170.686009</v>
       </c>
       <c r="O456" t="s">
         <v>143</v>
@@ -40857,7 +40791,7 @@
         <v>143</v>
       </c>
       <c r="Q456" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="R456">
         <v>0</v>
@@ -40883,6 +40817,12 @@
       <c r="Y456" t="s">
         <v>314</v>
       </c>
+      <c r="Z456" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA456" t="s">
+        <v>148</v>
+      </c>
       <c r="AB456" t="s">
         <v>78</v>
       </c>
@@ -40892,10 +40832,10 @@
     </row>
     <row r="457" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A457">
-        <v>386.3</v>
+        <v>386.2</v>
       </c>
       <c r="B457" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C457" t="s">
         <v>310</v>
@@ -40907,31 +40847,23 @@
         <v>32</v>
       </c>
       <c r="F457" s="3">
-        <v>45107</v>
+        <v>46022</v>
       </c>
       <c r="G457">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H457" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I457" t="s">
-        <v>47</v>
+        <v>465</v>
       </c>
       <c r="J457">
-        <v>1</v>
-      </c>
-      <c r="K457">
-        <v>2805.83</v>
+        <v>2</v>
       </c>
       <c r="L457">
-        <v>2183.1533570000001</v>
-      </c>
-      <c r="M457">
-        <v>0.77807755886849883</v>
-      </c>
-      <c r="N457">
-        <v>0.77807755886849883</v>
+        <f>7446830696/1000000</f>
+        <v>7446.830696</v>
       </c>
       <c r="O457" t="s">
         <v>143</v>
@@ -40940,7 +40872,7 @@
         <v>143</v>
       </c>
       <c r="Q457" t="s">
-        <v>388</v>
+        <v>489</v>
       </c>
       <c r="R457">
         <v>0</v>
@@ -40966,12 +40898,6 @@
       <c r="Y457" t="s">
         <v>314</v>
       </c>
-      <c r="Z457" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA457" t="s">
-        <v>148</v>
-      </c>
       <c r="AB457" t="s">
         <v>78</v>
       </c>
@@ -40981,10 +40907,10 @@
     </row>
     <row r="458" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A458">
-        <v>386.3</v>
+        <v>386.2</v>
       </c>
       <c r="B458" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C458" t="s">
         <v>310</v>
@@ -40996,31 +40922,20 @@
         <v>32</v>
       </c>
       <c r="F458" s="3">
-        <v>45291</v>
+        <v>46022</v>
       </c>
       <c r="G458">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H458" t="s">
         <v>44</v>
       </c>
       <c r="I458" t="s">
-        <v>49</v>
-      </c>
-      <c r="J458">
-        <v>2</v>
-      </c>
-      <c r="K458">
-        <v>2852.11</v>
+        <v>465</v>
       </c>
       <c r="L458">
-        <v>1865.5805049999999</v>
-      </c>
-      <c r="M458">
-        <v>0.65410538338282886</v>
-      </c>
-      <c r="N458">
-        <v>0.65410538338282886</v>
+        <f>7446830696/1000000</f>
+        <v>7446.830696</v>
       </c>
       <c r="O458" t="s">
         <v>143</v>
@@ -41029,7 +40944,7 @@
         <v>143</v>
       </c>
       <c r="Q458" t="s">
-        <v>389</v>
+        <v>489</v>
       </c>
       <c r="R458">
         <v>0</v>
@@ -41038,7 +40953,7 @@
         <v>0</v>
       </c>
       <c r="T458" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U458" t="s">
         <v>37</v>
@@ -41054,12 +40969,6 @@
       </c>
       <c r="Y458" t="s">
         <v>314</v>
-      </c>
-      <c r="Z458" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA458" t="s">
-        <v>148</v>
       </c>
       <c r="AB458" t="s">
         <v>78</v>
@@ -41085,28 +40994,23 @@
         <v>32</v>
       </c>
       <c r="F459" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G459">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H459" t="s">
         <v>44</v>
       </c>
       <c r="I459" t="s">
-        <v>49</v>
-      </c>
-      <c r="K459">
-        <v>5657.94</v>
+        <v>45</v>
+      </c>
+      <c r="J459">
+        <v>2</v>
       </c>
       <c r="L459">
-        <v>4048.733862</v>
-      </c>
-      <c r="M459">
-        <v>0.71558444628256934</v>
-      </c>
-      <c r="N459">
-        <v>0.71558444628256934</v>
+        <f>3805662141/1000000</f>
+        <v>3805.6621409999998</v>
       </c>
       <c r="O459" t="s">
         <v>143</v>
@@ -41115,7 +41019,7 @@
         <v>143</v>
       </c>
       <c r="Q459" t="s">
-        <v>389</v>
+        <v>493</v>
       </c>
       <c r="R459">
         <v>0</v>
@@ -41124,7 +41028,7 @@
         <v>0</v>
       </c>
       <c r="T459" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U459" t="s">
         <v>37</v>
@@ -41171,31 +41075,20 @@
         <v>32</v>
       </c>
       <c r="F460" s="3">
-        <v>45473</v>
+        <v>44926</v>
       </c>
       <c r="G460">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H460" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I460" t="s">
-        <v>51</v>
-      </c>
-      <c r="J460">
-        <v>1</v>
-      </c>
-      <c r="K460">
-        <v>1948.7860350000001</v>
+        <v>45</v>
       </c>
       <c r="L460">
-        <v>2190.9297999999999</v>
-      </c>
-      <c r="M460">
-        <v>1.1242536433713719</v>
-      </c>
-      <c r="N460">
-        <v>1.1242536433713719</v>
+        <f>3805662141/1000000</f>
+        <v>3805.6621409999998</v>
       </c>
       <c r="O460" t="s">
         <v>143</v>
@@ -41204,7 +41097,7 @@
         <v>143</v>
       </c>
       <c r="Q460" t="s">
-        <v>390</v>
+        <v>493</v>
       </c>
       <c r="R460">
         <v>0</v>
@@ -41213,7 +41106,7 @@
         <v>0</v>
       </c>
       <c r="T460" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U460" t="s">
         <v>37</v>
@@ -41260,31 +41153,23 @@
         <v>32</v>
       </c>
       <c r="F461" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G461">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H461" t="s">
         <v>44</v>
       </c>
       <c r="I461" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J461">
         <v>2</v>
       </c>
-      <c r="K461">
-        <v>2423.3739076999991</v>
-      </c>
       <c r="L461">
-        <v>2187.3099499999998</v>
-      </c>
-      <c r="M461">
-        <v>1.1242536433713719</v>
-      </c>
-      <c r="N461">
-        <v>1.1242536433713719</v>
+        <f>4048733862/1000000</f>
+        <v>4048.733862</v>
       </c>
       <c r="O461" t="s">
         <v>143</v>
@@ -41293,7 +41178,7 @@
         <v>143</v>
       </c>
       <c r="Q461" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R461">
         <v>0</v>
@@ -41349,28 +41234,20 @@
         <v>32</v>
       </c>
       <c r="F462" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G462">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H462" t="s">
         <v>44</v>
       </c>
       <c r="I462" t="s">
-        <v>53</v>
-      </c>
-      <c r="K462">
-        <v>4372.1599426999992</v>
+        <v>49</v>
       </c>
       <c r="L462">
-        <v>4378.2397499999997</v>
-      </c>
-      <c r="M462">
-        <v>1.0013905729387029</v>
-      </c>
-      <c r="N462">
-        <v>1.0013905729387029</v>
+        <f>4048733862/1000000</f>
+        <v>4048.733862</v>
       </c>
       <c r="O462" t="s">
         <v>143</v>
@@ -41379,7 +41256,7 @@
         <v>143</v>
       </c>
       <c r="Q462" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="R462">
         <v>0</v>
@@ -41435,31 +41312,22 @@
         <v>32</v>
       </c>
       <c r="F463" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G463">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H463" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I463" t="s">
-        <v>404</v>
+        <v>53</v>
       </c>
       <c r="J463">
-        <v>1</v>
-      </c>
-      <c r="K463">
-        <v>2797.6638859999998</v>
+        <v>2</v>
       </c>
       <c r="L463">
-        <v>3821.45975</v>
-      </c>
-      <c r="M463">
-        <v>1.3</v>
-      </c>
-      <c r="N463">
-        <v>1.365946699002426</v>
+        <v>4378.2397499999997</v>
       </c>
       <c r="O463" t="s">
         <v>143</v>
@@ -41468,7 +41336,7 @@
         <v>143</v>
       </c>
       <c r="Q463" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="R463">
         <v>0</v>
@@ -41493,6 +41361,12 @@
       </c>
       <c r="Y463" t="s">
         <v>314</v>
+      </c>
+      <c r="Z463" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA463" t="s">
+        <v>148</v>
       </c>
       <c r="AB463" t="s">
         <v>78</v>
@@ -41518,28 +41392,19 @@
         <v>32</v>
       </c>
       <c r="F464" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G464">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H464" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I464" t="s">
-        <v>404</v>
-      </c>
-      <c r="K464">
-        <v>2797.6638859999998</v>
+        <v>53</v>
       </c>
       <c r="L464">
-        <v>3821.45975</v>
-      </c>
-      <c r="M464">
-        <v>1.365946699002426</v>
-      </c>
-      <c r="N464">
-        <v>1.365946699002426</v>
+        <v>4378.2397499999997</v>
       </c>
       <c r="O464" t="s">
         <v>143</v>
@@ -41548,7 +41413,7 @@
         <v>143</v>
       </c>
       <c r="Q464" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="R464">
         <v>0</v>
@@ -41574,6 +41439,12 @@
       <c r="Y464" t="s">
         <v>314</v>
       </c>
+      <c r="Z464" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA464" t="s">
+        <v>148</v>
+      </c>
       <c r="AB464" t="s">
         <v>78</v>
       </c>
@@ -41583,55 +41454,53 @@
     </row>
     <row r="465" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A465">
-        <v>423</v>
+        <v>386.3</v>
       </c>
       <c r="B465" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="C465" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="D465" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E465" t="s">
         <v>32</v>
       </c>
       <c r="F465" s="3">
-        <v>44926</v>
+        <v>46022</v>
       </c>
       <c r="G465">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="H465" t="s">
         <v>44</v>
       </c>
       <c r="I465" t="s">
-        <v>45</v>
+        <v>465</v>
       </c>
       <c r="J465">
         <v>2</v>
       </c>
-      <c r="K465">
-        <v>8.8000000000000007</v>
-      </c>
       <c r="L465">
-        <v>7.8</v>
-      </c>
-      <c r="M465">
-        <v>0.88636363636363624</v>
-      </c>
-      <c r="N465">
-        <v>0.88636363636363624</v>
+        <f>(5278611105+290168214)/1000000</f>
+        <v>5568.7793190000002</v>
+      </c>
+      <c r="O465" t="s">
+        <v>143</v>
+      </c>
+      <c r="P465" t="s">
+        <v>143</v>
       </c>
       <c r="Q465" t="s">
-        <v>321</v>
+        <v>492</v>
       </c>
       <c r="R465">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S465">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T465" t="s">
         <v>31</v>
@@ -41640,25 +41509,19 @@
         <v>37</v>
       </c>
       <c r="V465" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="W465" t="s">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="X465" t="s">
-        <v>39</v>
+        <v>313</v>
       </c>
       <c r="Y465" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z465" t="s">
-        <v>274</v>
-      </c>
-      <c r="AA465" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="AB465" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="AC465" t="s">
         <v>66</v>
@@ -41666,58 +41529,50 @@
     </row>
     <row r="466" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A466">
-        <v>423</v>
+        <v>386.3</v>
       </c>
       <c r="B466" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="C466" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="D466" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E466" t="s">
         <v>32</v>
       </c>
       <c r="F466" s="3">
-        <v>44926</v>
+        <v>46022</v>
       </c>
       <c r="G466">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="H466" t="s">
         <v>44</v>
       </c>
       <c r="I466" t="s">
-        <v>45</v>
-      </c>
-      <c r="K466">
-        <v>8.8000000000000007</v>
+        <v>465</v>
       </c>
       <c r="L466">
-        <v>7.8</v>
-      </c>
-      <c r="M466">
-        <v>0.88636363636363624</v>
-      </c>
-      <c r="N466">
-        <v>0.88636363636363624</v>
+        <f>(5278611105+290168214)/1000000</f>
+        <v>5568.7793190000002</v>
       </c>
       <c r="O466" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="P466" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="Q466" t="s">
-        <v>321</v>
+        <v>492</v>
       </c>
       <c r="R466">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S466">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T466" t="s">
         <v>443</v>
@@ -41726,25 +41581,19 @@
         <v>37</v>
       </c>
       <c r="V466" t="s">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="W466" t="s">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="X466" t="s">
-        <v>39</v>
+        <v>313</v>
       </c>
       <c r="Y466" t="s">
-        <v>322</v>
-      </c>
-      <c r="Z466" t="s">
-        <v>274</v>
-      </c>
-      <c r="AA466" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
       <c r="AB466" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="AC466" t="s">
         <v>66</v>
@@ -41767,34 +41616,34 @@
         <v>32</v>
       </c>
       <c r="F467" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G467">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H467" t="s">
         <v>44</v>
       </c>
       <c r="I467" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J467">
         <v>2</v>
       </c>
       <c r="K467">
-        <v>8.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L467">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M467">
-        <v>0.94047619047619047</v>
+        <v>0.88636363636363624</v>
       </c>
       <c r="N467">
-        <v>0.94047619047619047</v>
+        <v>0.88636363636363624</v>
       </c>
       <c r="Q467" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R467">
         <v>1</v>
@@ -41850,28 +41699,28 @@
         <v>32</v>
       </c>
       <c r="F468" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G468">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H468" t="s">
         <v>44</v>
       </c>
       <c r="I468" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K468">
-        <v>8.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L468">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M468">
-        <v>0.94047619047619047</v>
+        <v>0.88636363636363624</v>
       </c>
       <c r="N468">
-        <v>0.94047619047619047</v>
+        <v>0.88636363636363624</v>
       </c>
       <c r="O468" t="s">
         <v>245</v>
@@ -41880,7 +41729,7 @@
         <v>245</v>
       </c>
       <c r="Q468" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R468">
         <v>1</v>
@@ -41936,40 +41785,40 @@
         <v>32</v>
       </c>
       <c r="F469" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G469">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H469" t="s">
         <v>44</v>
       </c>
       <c r="I469" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J469">
         <v>2</v>
       </c>
       <c r="K469">
-        <v>8.3000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="L469">
-        <v>12.3</v>
+        <v>7.9</v>
       </c>
       <c r="M469">
-        <v>1.3</v>
+        <v>0.94047619047619047</v>
       </c>
       <c r="N469">
-        <v>1.481927710843373</v>
+        <v>0.94047619047619047</v>
       </c>
       <c r="Q469" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R469">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S469">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T469" t="s">
         <v>31</v>
@@ -42019,28 +41868,28 @@
         <v>32</v>
       </c>
       <c r="F470" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G470">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H470" t="s">
         <v>44</v>
       </c>
       <c r="I470" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K470">
-        <v>8.3000000000000007</v>
+        <v>8.4</v>
       </c>
       <c r="L470">
-        <v>12.3</v>
+        <v>7.9</v>
       </c>
       <c r="M470">
-        <v>1.3</v>
+        <v>0.94047619047619047</v>
       </c>
       <c r="N470">
-        <v>1.481927710843373</v>
+        <v>0.94047619047619047</v>
       </c>
       <c r="O470" t="s">
         <v>245</v>
@@ -42049,7 +41898,7 @@
         <v>245</v>
       </c>
       <c r="Q470" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R470">
         <v>1</v>
@@ -42105,16 +41954,19 @@
         <v>32</v>
       </c>
       <c r="F471" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G471">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H471" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I471" t="s">
-        <v>404</v>
+        <v>53</v>
+      </c>
+      <c r="J471">
+        <v>2</v>
       </c>
       <c r="K471">
         <v>8.3000000000000007</v>
@@ -42128,23 +41980,17 @@
       <c r="N471">
         <v>1.481927710843373</v>
       </c>
-      <c r="O471" t="s">
-        <v>245</v>
-      </c>
-      <c r="P471" t="s">
-        <v>245</v>
-      </c>
       <c r="Q471" t="s">
-        <v>455</v>
+        <v>324</v>
       </c>
       <c r="R471">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S471">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T471" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U471" t="s">
         <v>37</v>
@@ -42176,10 +42022,10 @@
     </row>
     <row r="472" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A472">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B472" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C472" t="s">
         <v>83</v>
@@ -42191,43 +42037,46 @@
         <v>32</v>
       </c>
       <c r="F472" s="3">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="G472">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H472" t="s">
         <v>44</v>
       </c>
       <c r="I472" t="s">
-        <v>45</v>
-      </c>
-      <c r="J472">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="K472">
-        <v>6.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="L472">
-        <v>5</v>
+        <v>12.3</v>
       </c>
       <c r="M472">
-        <v>0.76923076923076927</v>
+        <v>1.3</v>
       </c>
       <c r="N472">
-        <v>0.76923076923076927</v>
+        <v>1.481927710843373</v>
+      </c>
+      <c r="O472" t="s">
+        <v>245</v>
+      </c>
+      <c r="P472" t="s">
+        <v>245</v>
       </c>
       <c r="Q472" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="R472">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S472">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T472" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U472" t="s">
         <v>37</v>
@@ -42259,10 +42108,10 @@
     </row>
     <row r="473" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A473">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B473" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C473" t="s">
         <v>83</v>
@@ -42274,43 +42123,43 @@
         <v>32</v>
       </c>
       <c r="F473" s="3">
-        <v>44926</v>
+        <v>45838</v>
       </c>
       <c r="G473">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="H473" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I473" t="s">
-        <v>45</v>
+        <v>404</v>
       </c>
       <c r="K473">
-        <v>6.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="L473">
-        <v>5</v>
+        <v>12.3</v>
       </c>
       <c r="M473">
-        <v>0.76923076923076927</v>
+        <v>1.3</v>
       </c>
       <c r="N473">
-        <v>0.76923076923076927</v>
+        <v>1.481927710843373</v>
       </c>
       <c r="O473" t="s">
         <v>245</v>
       </c>
       <c r="P473" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="Q473" t="s">
-        <v>326</v>
+        <v>455</v>
       </c>
       <c r="R473">
         <v>1</v>
       </c>
       <c r="S473">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T473" t="s">
         <v>443</v>
@@ -42360,34 +42209,34 @@
         <v>32</v>
       </c>
       <c r="F474" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G474">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H474" t="s">
         <v>44</v>
       </c>
       <c r="I474" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J474">
         <v>2</v>
       </c>
       <c r="K474">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L474">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M474">
-        <v>1</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="N474">
-        <v>1</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="Q474" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R474">
         <v>0</v>
@@ -42443,40 +42292,40 @@
         <v>32</v>
       </c>
       <c r="F475" s="3">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="G475">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H475" t="s">
         <v>44</v>
       </c>
       <c r="I475" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K475">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="L475">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M475">
-        <v>1</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="N475">
-        <v>1</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="O475" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="P475" t="s">
         <v>35</v>
       </c>
       <c r="Q475" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R475">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S475">
         <v>0</v>
@@ -42529,34 +42378,34 @@
         <v>32</v>
       </c>
       <c r="F476" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G476">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H476" t="s">
         <v>44</v>
       </c>
       <c r="I476" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J476">
         <v>2</v>
       </c>
       <c r="K476">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L476">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M476">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="N476">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="Q476" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R476">
         <v>0</v>
@@ -42612,28 +42461,28 @@
         <v>32</v>
       </c>
       <c r="F477" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G477">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H477" t="s">
         <v>44</v>
       </c>
       <c r="I477" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K477">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L477">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M477">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="N477">
-        <v>1.285714285714286</v>
+        <v>1</v>
       </c>
       <c r="O477" t="s">
         <v>35</v>
@@ -42642,7 +42491,7 @@
         <v>35</v>
       </c>
       <c r="Q477" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R477">
         <v>0</v>
@@ -42698,16 +42547,19 @@
         <v>32</v>
       </c>
       <c r="F478" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G478">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H478" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I478" t="s">
-        <v>404</v>
+        <v>53</v>
+      </c>
+      <c r="J478">
+        <v>2</v>
       </c>
       <c r="K478">
         <v>7</v>
@@ -42721,14 +42573,8 @@
       <c r="N478">
         <v>1.285714285714286</v>
       </c>
-      <c r="O478" t="s">
-        <v>35</v>
-      </c>
-      <c r="P478" t="s">
-        <v>35</v>
-      </c>
       <c r="Q478" t="s">
-        <v>468</v>
+        <v>328</v>
       </c>
       <c r="R478">
         <v>0</v>
@@ -42737,7 +42583,7 @@
         <v>0</v>
       </c>
       <c r="T478" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U478" t="s">
         <v>37</v>
@@ -42769,13 +42615,13 @@
     </row>
     <row r="479" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A479">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="B479" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C479" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="D479" t="s">
         <v>66</v>
@@ -42784,28 +42630,37 @@
         <v>32</v>
       </c>
       <c r="F479" s="3">
-        <v>45291</v>
+        <v>45657</v>
       </c>
       <c r="G479">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H479" t="s">
         <v>44</v>
       </c>
       <c r="I479" t="s">
-        <v>49</v>
+        <v>53</v>
+      </c>
+      <c r="K479">
+        <v>7</v>
       </c>
       <c r="L479">
-        <v>94.85</v>
+        <v>9</v>
+      </c>
+      <c r="M479">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="N479">
+        <v>1.285714285714286</v>
       </c>
       <c r="O479" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
       <c r="P479" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="Q479" t="s">
-        <v>449</v>
+        <v>328</v>
       </c>
       <c r="R479">
         <v>0</v>
@@ -42820,22 +42675,22 @@
         <v>37</v>
       </c>
       <c r="V479" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="W479" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="X479" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="Y479" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Z479" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="AA479" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="AB479" t="s">
         <v>43</v>
@@ -42846,13 +42701,13 @@
     </row>
     <row r="480" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A480">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="B480" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C480" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="D480" t="s">
         <v>66</v>
@@ -42861,40 +42716,37 @@
         <v>32</v>
       </c>
       <c r="F480" s="3">
-        <v>45657</v>
+        <v>45838</v>
       </c>
       <c r="G480">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H480" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I480" t="s">
-        <v>53</v>
-      </c>
-      <c r="J480">
-        <v>2</v>
+        <v>404</v>
       </c>
       <c r="K480">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="L480">
-        <v>91.44</v>
+        <v>9</v>
       </c>
       <c r="M480">
-        <v>1.143</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="N480">
-        <v>1.143</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="O480" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="P480" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="Q480" t="s">
-        <v>330</v>
+        <v>468</v>
       </c>
       <c r="R480">
         <v>0</v>
@@ -42903,28 +42755,28 @@
         <v>0</v>
       </c>
       <c r="T480" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U480" t="s">
         <v>37</v>
       </c>
       <c r="V480" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="W480" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="X480" t="s">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="Y480" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="Z480" t="s">
-        <v>134</v>
+        <v>274</v>
       </c>
       <c r="AA480" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="AB480" t="s">
         <v>43</v>
@@ -42950,19 +42802,16 @@
         <v>32</v>
       </c>
       <c r="F481" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G481">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H481" t="s">
         <v>44</v>
       </c>
       <c r="I481" t="s">
-        <v>53</v>
-      </c>
-      <c r="J481">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="L481">
         <v>94.85</v>
@@ -42974,7 +42823,7 @@
         <v>58</v>
       </c>
       <c r="Q481" t="s">
-        <v>330</v>
+        <v>449</v>
       </c>
       <c r="R481">
         <v>0</v>
@@ -42983,7 +42832,7 @@
         <v>0</v>
       </c>
       <c r="T481" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U481" t="s">
         <v>37</v>
@@ -43041,6 +42890,9 @@
       <c r="I482" t="s">
         <v>53</v>
       </c>
+      <c r="J482">
+        <v>2</v>
+      </c>
       <c r="K482">
         <v>80</v>
       </c>
@@ -43066,10 +42918,10 @@
         <v>0</v>
       </c>
       <c r="S482">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T482" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U482" t="s">
         <v>37</v>
@@ -43116,46 +42968,40 @@
         <v>32</v>
       </c>
       <c r="F483" s="3">
-        <v>45838</v>
+        <v>45657</v>
       </c>
       <c r="G483">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H483" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I483" t="s">
-        <v>404</v>
-      </c>
-      <c r="K483">
-        <v>80</v>
+        <v>53</v>
+      </c>
+      <c r="J483">
+        <v>2</v>
       </c>
       <c r="L483">
-        <v>91.44</v>
-      </c>
-      <c r="M483">
-        <v>1.143</v>
-      </c>
-      <c r="N483">
-        <v>1.143</v>
+        <v>94.85</v>
       </c>
       <c r="O483" t="s">
-        <v>58</v>
+        <v>284</v>
       </c>
       <c r="P483" t="s">
         <v>58</v>
       </c>
       <c r="Q483" t="s">
-        <v>454</v>
+        <v>330</v>
       </c>
       <c r="R483">
         <v>0</v>
       </c>
       <c r="S483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T483" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U483" t="s">
         <v>37</v>
@@ -43187,85 +43033,82 @@
     </row>
     <row r="484" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A484">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B484" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C484" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D484" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E484" t="s">
         <v>32</v>
       </c>
       <c r="F484" s="3">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="G484">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H484" t="s">
         <v>44</v>
       </c>
       <c r="I484" t="s">
-        <v>45</v>
-      </c>
-      <c r="J484">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="K484">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="L484">
-        <v>43.56</v>
+        <v>91.44</v>
       </c>
       <c r="M484">
-        <v>1.3</v>
+        <v>1.143</v>
       </c>
       <c r="N484">
-        <v>1.7423999999999999</v>
+        <v>1.143</v>
       </c>
       <c r="O484" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="P484" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="Q484" t="s">
-        <v>451</v>
+        <v>330</v>
       </c>
       <c r="R484">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S484">
         <v>1</v>
       </c>
       <c r="T484" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U484" t="s">
         <v>37</v>
       </c>
       <c r="V484" t="s">
-        <v>342</v>
+        <v>130</v>
       </c>
       <c r="W484" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="X484" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="Y484" t="s">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="Z484" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="AA484" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="AB484" t="s">
         <v>43</v>
@@ -43276,85 +43119,82 @@
     </row>
     <row r="485" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A485">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B485" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C485" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D485" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E485" t="s">
         <v>32</v>
       </c>
       <c r="F485" s="3">
-        <v>45291</v>
+        <v>45838</v>
       </c>
       <c r="G485">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H485" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I485" t="s">
-        <v>49</v>
-      </c>
-      <c r="J485">
-        <v>2</v>
+        <v>404</v>
       </c>
       <c r="K485">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="L485">
-        <v>53.34</v>
+        <v>91.44</v>
       </c>
       <c r="M485">
-        <v>1.27</v>
+        <v>1.143</v>
       </c>
       <c r="N485">
-        <v>1.27</v>
+        <v>1.143</v>
       </c>
       <c r="O485" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="P485" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="Q485" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="R485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S485">
         <v>1</v>
       </c>
       <c r="T485" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U485" t="s">
         <v>37</v>
       </c>
       <c r="V485" t="s">
-        <v>342</v>
+        <v>130</v>
       </c>
       <c r="W485" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="X485" t="s">
-        <v>113</v>
+        <v>218</v>
       </c>
       <c r="Y485" t="s">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="Z485" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="AA485" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="AB485" t="s">
         <v>43</v>
@@ -43391,6 +43231,9 @@
       <c r="I486" t="s">
         <v>45</v>
       </c>
+      <c r="J486">
+        <v>2</v>
+      </c>
       <c r="K486">
         <v>25</v>
       </c>
@@ -43419,7 +43262,7 @@
         <v>1</v>
       </c>
       <c r="T486" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U486" t="s">
         <v>37</v>
@@ -43477,6 +43320,9 @@
       <c r="I487" t="s">
         <v>49</v>
       </c>
+      <c r="J487">
+        <v>2</v>
+      </c>
       <c r="K487">
         <v>42</v>
       </c>
@@ -43505,7 +43351,7 @@
         <v>1</v>
       </c>
       <c r="T487" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U487" t="s">
         <v>37</v>
@@ -43543,7 +43389,7 @@
         <v>341</v>
       </c>
       <c r="C488" t="s">
-        <v>342</v>
+        <v>30</v>
       </c>
       <c r="D488" t="s">
         <v>31</v>
@@ -43552,31 +43398,28 @@
         <v>32</v>
       </c>
       <c r="F488" s="3">
-        <v>45473</v>
+        <v>44926</v>
       </c>
       <c r="G488">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H488" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I488" t="s">
-        <v>51</v>
-      </c>
-      <c r="J488">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="K488">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L488">
-        <v>59.6</v>
+        <v>43.56</v>
       </c>
       <c r="M488">
-        <v>1.1919999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="N488">
-        <v>1.1919999999999999</v>
+        <v>1.7423999999999999</v>
       </c>
       <c r="O488" t="s">
         <v>35</v>
@@ -43585,16 +43428,16 @@
         <v>245</v>
       </c>
       <c r="Q488" t="s">
-        <v>343</v>
+        <v>451</v>
       </c>
       <c r="R488">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S488">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T488" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U488" t="s">
         <v>37</v>
@@ -43632,7 +43475,7 @@
         <v>341</v>
       </c>
       <c r="C489" t="s">
-        <v>342</v>
+        <v>30</v>
       </c>
       <c r="D489" t="s">
         <v>31</v>
@@ -43641,28 +43484,28 @@
         <v>32</v>
       </c>
       <c r="F489" s="3">
-        <v>45657</v>
+        <v>45291</v>
       </c>
       <c r="G489">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H489" t="s">
         <v>44</v>
       </c>
       <c r="I489" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="K489">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L489">
-        <v>53.8</v>
+        <v>53.34</v>
       </c>
       <c r="M489">
-        <v>1.0760000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="N489">
-        <v>1.0760000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="O489" t="s">
         <v>35</v>
@@ -43671,13 +43514,13 @@
         <v>245</v>
       </c>
       <c r="Q489" t="s">
-        <v>344</v>
+        <v>452</v>
       </c>
       <c r="R489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S489">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T489" t="s">
         <v>443</v>
@@ -43718,7 +43561,7 @@
         <v>341</v>
       </c>
       <c r="C490" t="s">
-        <v>30</v>
+        <v>342</v>
       </c>
       <c r="D490" t="s">
         <v>31</v>
@@ -43727,31 +43570,31 @@
         <v>32</v>
       </c>
       <c r="F490" s="3">
-        <v>45657</v>
+        <v>45473</v>
       </c>
       <c r="G490">
         <v>2024</v>
       </c>
       <c r="H490" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="I490" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J490">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K490">
         <v>50</v>
       </c>
       <c r="L490">
-        <v>53.8</v>
+        <v>59.6</v>
       </c>
       <c r="M490">
-        <v>1.0760000000000001</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="N490">
-        <v>1.0760000000000001</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="O490" t="s">
         <v>35</v>
@@ -43760,13 +43603,13 @@
         <v>245</v>
       </c>
       <c r="Q490" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T490" t="s">
         <v>31</v>
@@ -43807,7 +43650,7 @@
         <v>341</v>
       </c>
       <c r="C491" t="s">
-        <v>30</v>
+        <v>342</v>
       </c>
       <c r="D491" t="s">
         <v>31</v>
@@ -43816,29 +43659,25 @@
         <v>32</v>
       </c>
       <c r="F491" s="3">
-        <v>46022</v>
+        <v>45657</v>
       </c>
       <c r="G491">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H491" t="s">
         <v>44</v>
       </c>
       <c r="I491" t="s">
-        <v>465</v>
-      </c>
-      <c r="J491">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="K491">
         <v>50</v>
       </c>
       <c r="L491">
-        <v>58.6</v>
+        <v>53.8</v>
       </c>
       <c r="M491">
-        <f>+L491/K491</f>
-        <v>1.1719999999999999</v>
+        <v>1.0760000000000001</v>
       </c>
       <c r="N491">
         <v>1.0760000000000001</v>
@@ -43850,16 +43689,16 @@
         <v>245</v>
       </c>
       <c r="Q491" t="s">
-        <v>457</v>
+        <v>344</v>
       </c>
       <c r="R491">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S491">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T491" t="s">
-        <v>31</v>
+        <v>443</v>
       </c>
       <c r="U491" t="s">
         <v>37</v>
@@ -43891,13 +43730,13 @@
     </row>
     <row r="492" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A492">
-        <v>203</v>
+        <v>466</v>
       </c>
       <c r="B492" t="s">
-        <v>141</v>
+        <v>341</v>
       </c>
       <c r="C492" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="D492" t="s">
         <v>31</v>
@@ -43906,41 +43745,46 @@
         <v>32</v>
       </c>
       <c r="F492" s="3">
-        <v>46022</v>
+        <v>45657</v>
       </c>
       <c r="G492">
-        <f>YEAR(F492)</f>
-        <v>2025</v>
-      </c>
-      <c r="H492" t="str">
-        <f>PROPER(TEXT(F492,"mmmm"))</f>
-        <v>Diciembre</v>
-      </c>
-      <c r="I492" t="str">
-        <f>IF(H492="Junio",G492&amp;"-1",G492&amp;"-2")</f>
-        <v>2025-2</v>
+        <v>2024</v>
+      </c>
+      <c r="H492" t="s">
+        <v>44</v>
+      </c>
+      <c r="I492" t="s">
+        <v>53</v>
       </c>
       <c r="J492">
         <v>2</v>
       </c>
+      <c r="K492">
+        <v>50</v>
+      </c>
       <c r="L492">
-        <v>159354.82822823568</v>
+        <v>53.8</v>
+      </c>
+      <c r="M492">
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="N492">
+        <v>1.0760000000000001</v>
       </c>
       <c r="O492" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="P492" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q492" t="str">
-        <f>A492&amp;"-"&amp;TEXT(F492,"yyyy-mm-dd")</f>
-        <v>203-2025-12-31</v>
+        <v>245</v>
+      </c>
+      <c r="Q492" t="s">
+        <v>344</v>
       </c>
       <c r="R492">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S492">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T492" t="s">
         <v>31</v>
@@ -43949,25 +43793,25 @@
         <v>37</v>
       </c>
       <c r="V492" t="s">
-        <v>142</v>
+        <v>342</v>
       </c>
       <c r="W492" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="X492" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="Y492" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="Z492" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="AA492" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="AB492" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC492" t="s">
         <v>66</v>
@@ -43975,13 +43819,13 @@
     </row>
     <row r="493" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A493">
-        <v>203</v>
+        <v>466</v>
       </c>
       <c r="B493" t="s">
-        <v>141</v>
+        <v>341</v>
       </c>
       <c r="C493" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="D493" t="s">
         <v>31</v>
@@ -43993,62 +43837,71 @@
         <v>46022</v>
       </c>
       <c r="G493">
-        <f>YEAR(F493)</f>
         <v>2025</v>
       </c>
-      <c r="H493" t="str">
-        <f>PROPER(TEXT(F493,"mmmm"))</f>
-        <v>Diciembre</v>
-      </c>
-      <c r="I493" t="str">
-        <f>IF(H493="Junio",G493&amp;"-1",G493&amp;"-2")</f>
-        <v>2025-2</v>
+      <c r="H493" t="s">
+        <v>44</v>
+      </c>
+      <c r="I493" t="s">
+        <v>465</v>
+      </c>
+      <c r="J493">
+        <v>2</v>
+      </c>
+      <c r="K493">
+        <v>50</v>
       </c>
       <c r="L493">
-        <v>309304.69728996162</v>
+        <v>58.6</v>
+      </c>
+      <c r="M493">
+        <f>+L493/K493</f>
+        <v>1.1719999999999999</v>
+      </c>
+      <c r="N493">
+        <v>1.0760000000000001</v>
       </c>
       <c r="O493" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="P493" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q493" t="str">
-        <f>A493&amp;"-"&amp;TEXT(F493,"yyyy-mm-dd")</f>
-        <v>203-2025-12-31</v>
+        <v>245</v>
+      </c>
+      <c r="Q493" t="s">
+        <v>457</v>
       </c>
       <c r="R493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S493">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T493" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U493" t="s">
         <v>37</v>
       </c>
       <c r="V493" t="s">
-        <v>142</v>
+        <v>342</v>
       </c>
       <c r="W493" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="X493" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="Y493" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="Z493" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="AA493" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="AB493" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC493" t="s">
         <v>66</v>
@@ -44056,13 +43909,13 @@
     </row>
     <row r="494" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A494">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="B494" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="C494" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="D494" t="s">
         <v>31</v>
@@ -44074,43 +43927,38 @@
         <v>46022</v>
       </c>
       <c r="G494">
+        <f>YEAR(F494)</f>
         <v>2025</v>
       </c>
-      <c r="H494" t="s">
-        <v>44</v>
-      </c>
-      <c r="I494" t="s">
-        <v>465</v>
+      <c r="H494" t="str">
+        <f>PROPER(TEXT(F494,"mmmm"))</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="I494" t="str">
+        <f>IF(H494="Junio",G494&amp;"-1",G494&amp;"-2")</f>
+        <v>2025-2</v>
       </c>
       <c r="J494">
         <v>2</v>
       </c>
-      <c r="K494">
-        <v>5.2</v>
-      </c>
       <c r="L494">
-        <v>5.2</v>
-      </c>
-      <c r="M494">
-        <v>1.02</v>
-      </c>
-      <c r="N494">
-        <v>1.02</v>
+        <v>159354.82822823568</v>
       </c>
       <c r="O494" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="P494" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q494" t="s">
-        <v>406</v>
+        <v>143</v>
+      </c>
+      <c r="Q494" t="str">
+        <f>A494&amp;"-"&amp;TEXT(F494,"yyyy-mm-dd")</f>
+        <v>203-2025-12-31</v>
       </c>
       <c r="R494">
         <v>0</v>
       </c>
       <c r="S494">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T494" t="s">
         <v>31</v>
@@ -44119,39 +43967,39 @@
         <v>37</v>
       </c>
       <c r="V494" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="W494" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="X494" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="Y494" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="Z494" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="AA494" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="AB494" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="AC494" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
     </row>
     <row r="495" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A495">
-        <v>466</v>
+        <v>203</v>
       </c>
       <c r="B495" t="s">
-        <v>341</v>
+        <v>141</v>
       </c>
       <c r="C495" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D495" t="s">
         <v>31</v>
@@ -44163,41 +44011,35 @@
         <v>46022</v>
       </c>
       <c r="G495">
+        <f>YEAR(F495)</f>
         <v>2025</v>
       </c>
-      <c r="H495" t="s">
-        <v>44</v>
-      </c>
-      <c r="I495" t="s">
-        <v>465</v>
-      </c>
-      <c r="K495">
-        <v>55</v>
+      <c r="H495" t="str">
+        <f>PROPER(TEXT(F495,"mmmm"))</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="I495" t="str">
+        <f>IF(H495="Junio",G495&amp;"-1",G495&amp;"-2")</f>
+        <v>2025-2</v>
       </c>
       <c r="L495">
-        <v>58.6</v>
-      </c>
-      <c r="M495">
-        <f>+L495/K495</f>
-        <v>1.0654545454545454</v>
-      </c>
-      <c r="N495">
-        <v>1.0760000000000001</v>
+        <v>309304.69728996162</v>
       </c>
       <c r="O495" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="P495" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q495" t="s">
-        <v>487</v>
+        <v>143</v>
+      </c>
+      <c r="Q495" t="str">
+        <f>A495&amp;"-"&amp;TEXT(F495,"yyyy-mm-dd")</f>
+        <v>203-2025-12-31</v>
       </c>
       <c r="R495">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S495">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T495" t="s">
         <v>443</v>
@@ -44206,43 +44048,459 @@
         <v>37</v>
       </c>
       <c r="V495" t="s">
-        <v>342</v>
+        <v>142</v>
       </c>
       <c r="W495" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="X495" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="Y495" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="Z495" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="AA495" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="AB495" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="AC495" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="496" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="L496" s="8"/>
-    </row>
-    <row r="498" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L498" s="7"/>
-    </row>
-    <row r="500" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L500" s="7"/>
+      <c r="A496">
+        <v>148</v>
+      </c>
+      <c r="B496" t="s">
+        <v>104</v>
+      </c>
+      <c r="C496" t="s">
+        <v>105</v>
+      </c>
+      <c r="D496" t="s">
+        <v>31</v>
+      </c>
+      <c r="E496" t="s">
+        <v>32</v>
+      </c>
+      <c r="F496" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G496">
+        <v>2025</v>
+      </c>
+      <c r="H496" t="s">
+        <v>44</v>
+      </c>
+      <c r="I496" t="s">
+        <v>465</v>
+      </c>
+      <c r="J496">
+        <v>2</v>
+      </c>
+      <c r="K496">
+        <v>5.2</v>
+      </c>
+      <c r="L496">
+        <v>5.2</v>
+      </c>
+      <c r="M496">
+        <v>1.02</v>
+      </c>
+      <c r="N496">
+        <v>1.02</v>
+      </c>
+      <c r="O496" t="s">
+        <v>58</v>
+      </c>
+      <c r="P496" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q496" t="s">
+        <v>406</v>
+      </c>
+      <c r="R496">
+        <v>0</v>
+      </c>
+      <c r="S496">
+        <v>1</v>
+      </c>
+      <c r="T496" t="s">
+        <v>31</v>
+      </c>
+      <c r="U496" t="s">
+        <v>37</v>
+      </c>
+      <c r="V496" t="s">
+        <v>105</v>
+      </c>
+      <c r="W496" t="s">
+        <v>73</v>
+      </c>
+      <c r="X496" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y496" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z496" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA496" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB496" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC496" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="497" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A497">
+        <v>466</v>
+      </c>
+      <c r="B497" t="s">
+        <v>341</v>
+      </c>
+      <c r="C497" t="s">
+        <v>30</v>
+      </c>
+      <c r="D497" t="s">
+        <v>31</v>
+      </c>
+      <c r="E497" t="s">
+        <v>32</v>
+      </c>
+      <c r="F497" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G497">
+        <v>2025</v>
+      </c>
+      <c r="H497" t="s">
+        <v>44</v>
+      </c>
+      <c r="I497" t="s">
+        <v>465</v>
+      </c>
+      <c r="K497">
+        <v>55</v>
+      </c>
+      <c r="L497">
+        <v>58.6</v>
+      </c>
+      <c r="M497">
+        <f>+L497/K497</f>
+        <v>1.0654545454545454</v>
+      </c>
+      <c r="N497">
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="O497" t="s">
+        <v>35</v>
+      </c>
+      <c r="P497" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q497" t="s">
+        <v>487</v>
+      </c>
+      <c r="R497">
+        <v>1</v>
+      </c>
+      <c r="S497">
+        <v>1</v>
+      </c>
+      <c r="T497" t="s">
+        <v>443</v>
+      </c>
+      <c r="U497" t="s">
+        <v>37</v>
+      </c>
+      <c r="V497" t="s">
+        <v>342</v>
+      </c>
+      <c r="W497" t="s">
+        <v>112</v>
+      </c>
+      <c r="X497" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y497" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z497" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA497" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB497" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC497" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="498" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A498">
+        <v>109</v>
+      </c>
+      <c r="B498" t="s">
+        <v>96</v>
+      </c>
+      <c r="C498" t="s">
+        <v>99</v>
+      </c>
+      <c r="D498" t="s">
+        <v>66</v>
+      </c>
+      <c r="E498" t="s">
+        <v>32</v>
+      </c>
+      <c r="F498" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G498">
+        <v>2024</v>
+      </c>
+      <c r="H498" t="s">
+        <v>44</v>
+      </c>
+      <c r="I498" t="s">
+        <v>465</v>
+      </c>
+      <c r="J498">
+        <v>2</v>
+      </c>
+      <c r="K498">
+        <v>80</v>
+      </c>
+      <c r="L498">
+        <v>94</v>
+      </c>
+      <c r="M498">
+        <f>+L498/K498</f>
+        <v>1.175</v>
+      </c>
+      <c r="N498">
+        <v>1.0625</v>
+      </c>
+      <c r="O498" t="s">
+        <v>58</v>
+      </c>
+      <c r="P498" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q498" t="s">
+        <v>488</v>
+      </c>
+      <c r="R498">
+        <v>0</v>
+      </c>
+      <c r="S498">
+        <v>0</v>
+      </c>
+      <c r="T498" t="s">
+        <v>31</v>
+      </c>
+      <c r="U498" t="s">
+        <v>37</v>
+      </c>
+      <c r="V498" t="s">
+        <v>99</v>
+      </c>
+      <c r="W498" t="s">
+        <v>60</v>
+      </c>
+      <c r="X498" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z498" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA498" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB498" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC498" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="499" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A499">
+        <v>386.1</v>
+      </c>
+      <c r="B499" t="s">
+        <v>377</v>
+      </c>
+      <c r="C499" t="s">
+        <v>310</v>
+      </c>
+      <c r="D499" t="s">
+        <v>31</v>
+      </c>
+      <c r="E499" t="s">
+        <v>32</v>
+      </c>
+      <c r="F499" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G499">
+        <v>2025</v>
+      </c>
+      <c r="H499" t="s">
+        <v>44</v>
+      </c>
+      <c r="I499" t="s">
+        <v>465</v>
+      </c>
+      <c r="L499">
+        <f>4042632396/1000000</f>
+        <v>4042.632396</v>
+      </c>
+      <c r="O499" t="s">
+        <v>143</v>
+      </c>
+      <c r="P499" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q499" t="s">
+        <v>490</v>
+      </c>
+      <c r="R499">
+        <v>0</v>
+      </c>
+      <c r="S499">
+        <v>0</v>
+      </c>
+      <c r="T499" t="s">
+        <v>443</v>
+      </c>
+      <c r="U499" t="s">
+        <v>37</v>
+      </c>
+      <c r="V499" t="s">
+        <v>310</v>
+      </c>
+      <c r="W499" t="s">
+        <v>312</v>
+      </c>
+      <c r="X499" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y499" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB499" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC499" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="500" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A500">
+        <v>385</v>
+      </c>
+      <c r="B500" t="s">
+        <v>309</v>
+      </c>
+      <c r="C500" t="s">
+        <v>310</v>
+      </c>
+      <c r="D500" t="s">
+        <v>31</v>
+      </c>
+      <c r="E500" t="s">
+        <v>32</v>
+      </c>
+      <c r="F500" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G500">
+        <v>2025</v>
+      </c>
+      <c r="H500" t="s">
+        <v>44</v>
+      </c>
+      <c r="I500" t="s">
+        <v>465</v>
+      </c>
+      <c r="L500">
+        <f>17058242411/1000000</f>
+        <v>17058.242410999999</v>
+      </c>
+      <c r="O500" t="s">
+        <v>143</v>
+      </c>
+      <c r="P500" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q500" t="s">
+        <v>486</v>
+      </c>
+      <c r="R500">
+        <v>0</v>
+      </c>
+      <c r="S500">
+        <v>0</v>
+      </c>
+      <c r="T500" t="s">
+        <v>443</v>
+      </c>
+      <c r="U500" t="s">
+        <v>37</v>
+      </c>
+      <c r="V500" t="s">
+        <v>310</v>
+      </c>
+      <c r="W500" t="s">
+        <v>312</v>
+      </c>
+      <c r="X500" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y500" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB500" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC500" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="501" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="J501" s="8"/>
+    </row>
+    <row r="502" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="J502" s="8"/>
+      <c r="L502" s="7"/>
+    </row>
+    <row r="503" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="J503" s="8"/>
+      <c r="L503" s="9"/>
+    </row>
+    <row r="504" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="L504" s="9"/>
+    </row>
+    <row r="505" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="L505" s="9"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC491">
-    <sortCondition ref="A2:A491"/>
-    <sortCondition ref="F2:F491"/>
+  <autoFilter ref="A1:AC500" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC493">
+    <sortCondition ref="A2:A493"/>
+    <sortCondition ref="F2:F493"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1105" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56E2E8C4-F466-48B9-A4FA-DF4DDD1B0CDD}"/>
+  <xr:revisionPtr revIDLastSave="1149" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C33A5A-2A5B-4AC4-8258-3235DCA9A6EE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Cierres_Original" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$502</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14138" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14176" uniqueCount="496">
   <si>
     <t>Id</t>
   </si>
@@ -1522,6 +1522,12 @@
   <si>
     <t>386.3-2022-12-31</t>
   </si>
+  <si>
+    <t>423-2025-12-31</t>
+  </si>
+  <si>
+    <t>424-2025-12-31</t>
+  </si>
 </sst>
 </file>
 
@@ -1599,13 +1605,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1615,15 +1620,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Millares" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
+    <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E6474115-E034-47AA-AE39-934325146E0E}"/>
-    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -41972,7 +41975,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="L471">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="M471">
         <v>1.3</v>
@@ -41984,10 +41987,10 @@
         <v>324</v>
       </c>
       <c r="R471">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S471">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T471" t="s">
         <v>31</v>
@@ -42052,7 +42055,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="L472">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="M472">
         <v>1.3</v>
@@ -42123,28 +42126,25 @@
         <v>32</v>
       </c>
       <c r="F473" s="3">
-        <v>45838</v>
+        <v>46022</v>
       </c>
       <c r="G473">
         <v>2025</v>
       </c>
       <c r="H473" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I473" t="s">
-        <v>404</v>
+        <v>465</v>
+      </c>
+      <c r="J473">
+        <v>2</v>
       </c>
       <c r="K473">
-        <v>8.3000000000000007</v>
+        <v>12</v>
       </c>
       <c r="L473">
-        <v>12.3</v>
-      </c>
-      <c r="M473">
-        <v>1.3</v>
-      </c>
-      <c r="N473">
-        <v>1.481927710843373</v>
+        <v>15.1</v>
       </c>
       <c r="O473" t="s">
         <v>245</v>
@@ -42162,7 +42162,7 @@
         <v>1</v>
       </c>
       <c r="T473" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U473" t="s">
         <v>37</v>
@@ -42716,28 +42716,25 @@
         <v>32</v>
       </c>
       <c r="F480" s="3">
-        <v>45838</v>
+        <v>46022</v>
       </c>
       <c r="G480">
         <v>2025</v>
       </c>
       <c r="H480" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I480" t="s">
-        <v>404</v>
+        <v>465</v>
+      </c>
+      <c r="J480">
+        <v>2</v>
       </c>
       <c r="K480">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L480">
-        <v>9</v>
-      </c>
-      <c r="M480">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="N480">
-        <v>1.285714285714286</v>
+        <v>11</v>
       </c>
       <c r="O480" t="s">
         <v>35</v>
@@ -42746,7 +42743,7 @@
         <v>35</v>
       </c>
       <c r="Q480" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="R480">
         <v>0</v>
@@ -42755,7 +42752,7 @@
         <v>0</v>
       </c>
       <c r="T480" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="U480" t="s">
         <v>37</v>
@@ -44480,24 +44477,177 @@
       </c>
     </row>
     <row r="501" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="J501" s="8"/>
+      <c r="A501">
+        <v>423</v>
+      </c>
+      <c r="B501" t="s">
+        <v>320</v>
+      </c>
+      <c r="C501" t="s">
+        <v>83</v>
+      </c>
+      <c r="D501" t="s">
+        <v>66</v>
+      </c>
+      <c r="E501" t="s">
+        <v>32</v>
+      </c>
+      <c r="F501" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G501">
+        <v>2025</v>
+      </c>
+      <c r="H501" t="s">
+        <v>44</v>
+      </c>
+      <c r="I501" t="s">
+        <v>465</v>
+      </c>
+      <c r="K501">
+        <v>12</v>
+      </c>
+      <c r="L501">
+        <v>15.1</v>
+      </c>
+      <c r="O501" t="s">
+        <v>245</v>
+      </c>
+      <c r="P501" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q501" t="s">
+        <v>494</v>
+      </c>
+      <c r="R501">
+        <v>1</v>
+      </c>
+      <c r="S501">
+        <v>1</v>
+      </c>
+      <c r="T501" t="s">
+        <v>443</v>
+      </c>
+      <c r="U501" t="s">
+        <v>37</v>
+      </c>
+      <c r="V501" t="s">
+        <v>83</v>
+      </c>
+      <c r="W501" t="s">
+        <v>38</v>
+      </c>
+      <c r="X501" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y501" t="s">
+        <v>322</v>
+      </c>
+      <c r="Z501" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA501" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB501" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC501" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="502" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="J502" s="8"/>
-      <c r="L502" s="7"/>
+      <c r="A502">
+        <v>424</v>
+      </c>
+      <c r="B502" t="s">
+        <v>325</v>
+      </c>
+      <c r="C502" t="s">
+        <v>83</v>
+      </c>
+      <c r="D502" t="s">
+        <v>66</v>
+      </c>
+      <c r="E502" t="s">
+        <v>32</v>
+      </c>
+      <c r="F502" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G502">
+        <v>2025</v>
+      </c>
+      <c r="H502" t="s">
+        <v>44</v>
+      </c>
+      <c r="I502" t="s">
+        <v>465</v>
+      </c>
+      <c r="K502">
+        <v>9</v>
+      </c>
+      <c r="L502">
+        <v>11</v>
+      </c>
+      <c r="O502" t="s">
+        <v>35</v>
+      </c>
+      <c r="P502" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q502" t="s">
+        <v>495</v>
+      </c>
+      <c r="R502">
+        <v>0</v>
+      </c>
+      <c r="S502">
+        <v>0</v>
+      </c>
+      <c r="T502" t="s">
+        <v>443</v>
+      </c>
+      <c r="U502" t="s">
+        <v>37</v>
+      </c>
+      <c r="V502" t="s">
+        <v>83</v>
+      </c>
+      <c r="W502" t="s">
+        <v>38</v>
+      </c>
+      <c r="X502" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y502" t="s">
+        <v>322</v>
+      </c>
+      <c r="Z502" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA502" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB502" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC502" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="503" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="J503" s="8"/>
-      <c r="L503" s="9"/>
+      <c r="J503" s="7"/>
+      <c r="L503" s="8"/>
     </row>
     <row r="504" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="L504" s="9"/>
+      <c r="L504" s="8"/>
     </row>
     <row r="505" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="L505" s="9"/>
+      <c r="L505" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC500" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC502" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC493">
     <sortCondition ref="A2:A493"/>
     <sortCondition ref="F2:F493"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1149" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C33A5A-2A5B-4AC4-8258-3235DCA9A6EE}"/>
+  <xr:revisionPtr revIDLastSave="1161" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAA6815-7C13-49E8-A97F-D11CF39680D5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1926,6 +1926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2030,7 +2031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2196,7 +2197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2277,7 +2278,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2361,7 +2362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2610,7 +2611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2694,7 +2695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -3113,7 +3114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3288,7 +3289,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>14</v>
       </c>
@@ -3466,7 +3467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>14</v>
       </c>
@@ -3552,7 +3553,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>14</v>
       </c>
@@ -3641,7 +3642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>14</v>
       </c>
@@ -3730,7 +3731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>14</v>
       </c>
@@ -3816,7 +3817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>14</v>
       </c>
@@ -3905,7 +3906,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>14</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>14</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>14.1</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14.1</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>14.1</v>
       </c>
@@ -4317,7 +4318,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>14.1</v>
       </c>
@@ -4401,7 +4402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>14.1</v>
       </c>
@@ -4485,7 +4486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>14.1</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>14.1</v>
       </c>
@@ -4650,7 +4651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>14.1</v>
       </c>
@@ -4734,7 +4735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>14.1</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>14.1</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>14.1</v>
       </c>
@@ -4983,7 +4984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>14.1</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>14.1</v>
       </c>
@@ -5153,7 +5154,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>14.1</v>
       </c>
@@ -5242,7 +5243,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>14.1</v>
       </c>
@@ -5328,7 +5329,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>14.1</v>
       </c>
@@ -5417,7 +5418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>14.1</v>
       </c>
@@ -5506,7 +5507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>14.1</v>
       </c>
@@ -5592,7 +5593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14.1</v>
       </c>
@@ -5681,7 +5682,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14.1</v>
       </c>
@@ -5770,7 +5771,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14.1</v>
       </c>
@@ -5856,7 +5857,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14.1</v>
       </c>
@@ -5945,7 +5946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14.1</v>
       </c>
@@ -6025,7 +6026,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>14.1</v>
       </c>
@@ -6108,7 +6109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>14.2</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>14.2</v>
       </c>
@@ -6276,7 +6277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>14.2</v>
       </c>
@@ -6357,7 +6358,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>14.2</v>
       </c>
@@ -6441,7 +6442,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>14.2</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>14.2</v>
       </c>
@@ -6606,7 +6607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>14.2</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>14.2</v>
       </c>
@@ -6774,7 +6775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>14.2</v>
       </c>
@@ -6855,7 +6856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>14.2</v>
       </c>
@@ -6939,7 +6940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>14.2</v>
       </c>
@@ -7023,7 +7024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>14.2</v>
       </c>
@@ -7104,7 +7105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>14.2</v>
       </c>
@@ -7193,7 +7194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>14.2</v>
       </c>
@@ -7282,7 +7283,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>14.2</v>
       </c>
@@ -7368,7 +7369,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>14.2</v>
       </c>
@@ -7457,7 +7458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>14.2</v>
       </c>
@@ -7546,7 +7547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>14.2</v>
       </c>
@@ -7632,7 +7633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>14.2</v>
       </c>
@@ -7721,7 +7722,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>14.2</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>14.2</v>
       </c>
@@ -7896,7 +7897,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>14.2</v>
       </c>
@@ -7985,7 +7986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>14.2</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>14.2</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>14.3</v>
       </c>
@@ -8226,7 +8227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>14.3</v>
       </c>
@@ -8310,7 +8311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>14.3</v>
       </c>
@@ -8391,7 +8392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14.3</v>
       </c>
@@ -8475,7 +8476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14.3</v>
       </c>
@@ -8559,7 +8560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14.3</v>
       </c>
@@ -8640,7 +8641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>14.3</v>
       </c>
@@ -8724,7 +8725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>14.3</v>
       </c>
@@ -8808,7 +8809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>14.3</v>
       </c>
@@ -8889,7 +8890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>14.3</v>
       </c>
@@ -8973,7 +8974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>14.3</v>
       </c>
@@ -9057,7 +9058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>14.3</v>
       </c>
@@ -9138,7 +9139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>14.3</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>14.3</v>
       </c>
@@ -9316,7 +9317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>14.3</v>
       </c>
@@ -9402,7 +9403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>14.3</v>
       </c>
@@ -9491,7 +9492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>14.3</v>
       </c>
@@ -9580,7 +9581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>14.3</v>
       </c>
@@ -9666,7 +9667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>14.3</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>14.3</v>
       </c>
@@ -9844,7 +9845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>14.3</v>
       </c>
@@ -9930,7 +9931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>14.3</v>
       </c>
@@ -10019,7 +10020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>14.3</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>14.3</v>
       </c>
@@ -10185,7 +10186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>14.4</v>
       </c>
@@ -10269,7 +10270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>14.4</v>
       </c>
@@ -10353,7 +10354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>14.4</v>
       </c>
@@ -10434,7 +10435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>14.4</v>
       </c>
@@ -10518,7 +10519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>14.4</v>
       </c>
@@ -10602,7 +10603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>14.4</v>
       </c>
@@ -10683,7 +10684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>14.4</v>
       </c>
@@ -10767,7 +10768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>14.4</v>
       </c>
@@ -10851,7 +10852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>14.4</v>
       </c>
@@ -10932,7 +10933,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>14.4</v>
       </c>
@@ -11016,7 +11017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>14.4</v>
       </c>
@@ -11100,7 +11101,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>14.4</v>
       </c>
@@ -11181,7 +11182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>14.4</v>
       </c>
@@ -11270,7 +11271,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>14.4</v>
       </c>
@@ -11359,7 +11360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>14.4</v>
       </c>
@@ -11445,7 +11446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>14.4</v>
       </c>
@@ -11534,7 +11535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>14.4</v>
       </c>
@@ -11623,7 +11624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>14.4</v>
       </c>
@@ -11709,7 +11710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>14.4</v>
       </c>
@@ -11798,7 +11799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>14.4</v>
       </c>
@@ -11887,7 +11888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>14.4</v>
       </c>
@@ -11973,7 +11974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>14.4</v>
       </c>
@@ -12062,7 +12063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.4</v>
       </c>
@@ -12151,7 +12152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>14.4</v>
       </c>
@@ -13195,7 +13196,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>96</v>
       </c>
@@ -13284,7 +13285,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>96</v>
       </c>
@@ -13370,7 +13371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>96</v>
       </c>
@@ -13459,7 +13460,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>96</v>
       </c>
@@ -13548,7 +13549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>96</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>96</v>
       </c>
@@ -13723,7 +13724,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>96</v>
       </c>
@@ -13812,7 +13813,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>96</v>
       </c>
@@ -13898,7 +13899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>97</v>
       </c>
@@ -13987,7 +13988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>97</v>
       </c>
@@ -14070,7 +14071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>97</v>
       </c>
@@ -14156,7 +14157,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>97</v>
       </c>
@@ -14233,7 +14234,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>97</v>
       </c>
@@ -14310,7 +14311,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>97</v>
       </c>
@@ -14390,7 +14391,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>97</v>
       </c>
@@ -14467,7 +14468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>97</v>
       </c>
@@ -14544,7 +14545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>97</v>
       </c>
@@ -14624,7 +14625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>97</v>
       </c>
@@ -14704,7 +14705,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>98</v>
       </c>
@@ -14787,7 +14788,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>98</v>
       </c>
@@ -14876,7 +14877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>98</v>
       </c>
@@ -14962,7 +14963,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>98</v>
       </c>
@@ -15045,7 +15046,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>98</v>
       </c>
@@ -15134,7 +15135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>98</v>
       </c>
@@ -15220,7 +15221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>98</v>
       </c>
@@ -15297,7 +15298,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>98</v>
       </c>
@@ -15386,7 +15387,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>98</v>
       </c>
@@ -15472,7 +15473,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>98</v>
       </c>
@@ -15561,7 +15562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>98</v>
       </c>
@@ -16069,7 +16070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>148</v>
       </c>
@@ -16155,7 +16156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>148</v>
       </c>
@@ -16244,7 +16245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>148</v>
       </c>
@@ -16333,7 +16334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>148</v>
       </c>
@@ -16419,7 +16420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>148</v>
       </c>
@@ -16508,7 +16509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>148</v>
       </c>
@@ -16597,7 +16598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>148</v>
       </c>
@@ -16683,7 +16684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>148</v>
       </c>
@@ -16772,7 +16773,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>148</v>
       </c>
@@ -16858,7 +16859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>193</v>
       </c>
@@ -16947,7 +16948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>193</v>
       </c>
@@ -17036,7 +17037,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>193</v>
       </c>
@@ -17122,7 +17123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>193</v>
       </c>
@@ -17211,7 +17212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>193</v>
       </c>
@@ -17300,7 +17301,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>193</v>
       </c>
@@ -17386,7 +17387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>193</v>
       </c>
@@ -17475,7 +17476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>193</v>
       </c>
@@ -17564,7 +17565,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>193</v>
       </c>
@@ -17650,7 +17651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>193</v>
       </c>
@@ -17739,7 +17740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>193</v>
       </c>
@@ -17825,7 +17826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>194</v>
       </c>
@@ -17914,7 +17915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>194</v>
       </c>
@@ -18003,7 +18004,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>194</v>
       </c>
@@ -18089,7 +18090,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>194</v>
       </c>
@@ -18178,7 +18179,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>194</v>
       </c>
@@ -18267,7 +18268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>194</v>
       </c>
@@ -18353,7 +18354,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>194</v>
       </c>
@@ -18442,7 +18443,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>194</v>
       </c>
@@ -18531,7 +18532,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -18617,7 +18618,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18706,7 +18707,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>194</v>
       </c>
@@ -20049,7 +20050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>203</v>
       </c>
@@ -20138,7 +20139,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>203</v>
       </c>
@@ -20227,7 +20228,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>203</v>
       </c>
@@ -20313,7 +20314,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>203</v>
       </c>
@@ -20402,7 +20403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>203</v>
       </c>
@@ -20491,7 +20492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>203</v>
       </c>
@@ -20577,7 +20578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>203</v>
       </c>
@@ -20666,7 +20667,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>203</v>
       </c>
@@ -20755,7 +20756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>203</v>
       </c>
@@ -20841,7 +20842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>203</v>
       </c>
@@ -20930,7 +20931,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>204</v>
       </c>
@@ -21019,7 +21020,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>204</v>
       </c>
@@ -21108,7 +21109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>204</v>
       </c>
@@ -21182,7 +21183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>204</v>
       </c>
@@ -21271,7 +21272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>204</v>
       </c>
@@ -21360,7 +21361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>204</v>
       </c>
@@ -21446,7 +21447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>204</v>
       </c>
@@ -21535,7 +21536,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>204</v>
       </c>
@@ -21624,7 +21625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>204</v>
       </c>
@@ -21710,7 +21711,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>204</v>
       </c>
@@ -21799,7 +21800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>204</v>
       </c>
@@ -21885,7 +21886,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>205</v>
       </c>
@@ -21974,7 +21975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>205</v>
       </c>
@@ -22063,7 +22064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>205</v>
       </c>
@@ -22149,7 +22150,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>205</v>
       </c>
@@ -22238,7 +22239,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>205</v>
       </c>
@@ -22327,7 +22328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>205</v>
       </c>
@@ -22413,7 +22414,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>205</v>
       </c>
@@ -22502,7 +22503,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>205</v>
       </c>
@@ -22588,7 +22589,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>207</v>
       </c>
@@ -22677,7 +22678,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>207</v>
       </c>
@@ -22766,7 +22767,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>207</v>
       </c>
@@ -22852,7 +22853,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>207</v>
       </c>
@@ -22941,7 +22942,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>207</v>
       </c>
@@ -23030,7 +23031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>207</v>
       </c>
@@ -23116,7 +23117,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>207</v>
       </c>
@@ -23205,7 +23206,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>207</v>
       </c>
@@ -23291,7 +23292,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>228</v>
       </c>
@@ -23374,7 +23375,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>228</v>
       </c>
@@ -23460,7 +23461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>228</v>
       </c>
@@ -23546,7 +23547,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>228</v>
       </c>
@@ -23617,7 +23618,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>228</v>
       </c>
@@ -23703,7 +23704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>228</v>
       </c>
@@ -23789,7 +23790,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>244</v>
       </c>
@@ -23875,7 +23876,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>244</v>
       </c>
@@ -23958,7 +23959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>244</v>
       </c>
@@ -24044,7 +24045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>244</v>
       </c>
@@ -24127,7 +24128,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>244</v>
       </c>
@@ -24213,7 +24214,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>244</v>
       </c>
@@ -24299,7 +24300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>245</v>
       </c>
@@ -24388,7 +24389,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>245</v>
       </c>
@@ -24477,7 +24478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>245</v>
       </c>
@@ -24563,7 +24564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>245</v>
       </c>
@@ -24652,7 +24653,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>245</v>
       </c>
@@ -24741,7 +24742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>245</v>
       </c>
@@ -24827,7 +24828,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>245</v>
       </c>
@@ -24916,7 +24917,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>245</v>
       </c>
@@ -24999,7 +25000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>245</v>
       </c>
@@ -25085,7 +25086,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>245</v>
       </c>
@@ -25174,7 +25175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>245</v>
       </c>
@@ -25260,7 +25261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>274</v>
       </c>
@@ -25344,7 +25345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>274</v>
       </c>
@@ -25428,7 +25429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -25509,7 +25510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>274</v>
       </c>
@@ -25593,7 +25594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25677,7 +25678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25758,7 +25759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -25842,7 +25843,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>274</v>
       </c>
@@ -25926,7 +25927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>274</v>
       </c>
@@ -26007,7 +26008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>274</v>
       </c>
@@ -26091,7 +26092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -26175,7 +26176,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>274</v>
       </c>
@@ -26256,7 +26257,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>274</v>
       </c>
@@ -26345,7 +26346,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>274</v>
       </c>
@@ -26434,7 +26435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>274</v>
       </c>
@@ -26520,7 +26521,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>274</v>
       </c>
@@ -26609,7 +26610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>274</v>
       </c>
@@ -26698,7 +26699,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>274</v>
       </c>
@@ -26784,7 +26785,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>274</v>
       </c>
@@ -26873,7 +26874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>274</v>
       </c>
@@ -26962,7 +26963,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>274</v>
       </c>
@@ -27048,7 +27049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>274</v>
       </c>
@@ -27137,7 +27138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>274</v>
       </c>
@@ -27224,7 +27225,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>274</v>
       </c>
@@ -27308,7 +27309,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>276</v>
       </c>
@@ -27391,7 +27392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>276</v>
       </c>
@@ -27474,7 +27475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>276</v>
       </c>
@@ -27560,7 +27561,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>276</v>
       </c>
@@ -27643,7 +27644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>276</v>
       </c>
@@ -27726,7 +27727,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>276</v>
       </c>
@@ -27812,7 +27813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>276</v>
       </c>
@@ -27895,7 +27896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>276</v>
       </c>
@@ -27978,7 +27979,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>276</v>
       </c>
@@ -28064,7 +28065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>276</v>
       </c>
@@ -28153,7 +28154,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>276</v>
       </c>
@@ -28239,7 +28240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>277</v>
       </c>
@@ -28319,7 +28320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>277</v>
       </c>
@@ -28399,7 +28400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>277</v>
       </c>
@@ -28482,7 +28483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>277</v>
       </c>
@@ -28562,7 +28563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>277</v>
       </c>
@@ -28642,7 +28643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>277</v>
       </c>
@@ -28725,7 +28726,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>277</v>
       </c>
@@ -28811,7 +28812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>277</v>
       </c>
@@ -28894,7 +28895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>323</v>
       </c>
@@ -28977,7 +28978,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>323</v>
       </c>
@@ -29063,7 +29064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>323</v>
       </c>
@@ -29146,7 +29147,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>323</v>
       </c>
@@ -29229,7 +29230,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>323</v>
       </c>
@@ -29315,7 +29316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>323</v>
       </c>
@@ -29398,7 +29399,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>323</v>
       </c>
@@ -29475,7 +29476,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -29561,7 +29562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -29650,7 +29651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>323</v>
       </c>
@@ -29736,7 +29737,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -29825,7 +29826,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>325</v>
       </c>
@@ -29914,7 +29915,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>325</v>
       </c>
@@ -30000,7 +30001,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>325</v>
       </c>
@@ -30089,7 +30090,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>325</v>
       </c>
@@ -30166,7 +30167,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>325</v>
       </c>
@@ -30252,7 +30253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>325</v>
       </c>
@@ -30341,7 +30342,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>325</v>
       </c>
@@ -30430,7 +30431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>325</v>
       </c>
@@ -30516,7 +30517,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>325</v>
       </c>
@@ -30605,7 +30606,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>325</v>
       </c>
@@ -30691,7 +30692,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>331</v>
       </c>
@@ -30774,7 +30775,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>331</v>
       </c>
@@ -30851,7 +30852,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>331</v>
       </c>
@@ -30934,7 +30935,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>331</v>
       </c>
@@ -31011,7 +31012,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>331</v>
       </c>
@@ -31091,7 +31092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>331</v>
       </c>
@@ -33036,7 +33037,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>339</v>
       </c>
@@ -33125,7 +33126,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>339</v>
       </c>
@@ -33211,7 +33212,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>339</v>
       </c>
@@ -33300,7 +33301,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>339</v>
       </c>
@@ -33386,7 +33387,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>339</v>
       </c>
@@ -33475,7 +33476,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>339</v>
       </c>
@@ -33561,7 +33562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>361</v>
       </c>
@@ -33642,7 +33643,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>361</v>
       </c>
@@ -33731,7 +33732,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>361</v>
       </c>
@@ -33817,7 +33818,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>361</v>
       </c>
@@ -33907,7 +33908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>361</v>
       </c>
@@ -33994,7 +33995,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>364</v>
       </c>
@@ -34083,7 +34084,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>364</v>
       </c>
@@ -34172,7 +34173,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>364</v>
       </c>
@@ -34249,7 +34250,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>364</v>
       </c>
@@ -34338,7 +34339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>364</v>
       </c>
@@ -34427,7 +34428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>364</v>
       </c>
@@ -34513,7 +34514,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>364</v>
       </c>
@@ -34602,7 +34603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>364</v>
       </c>
@@ -34688,7 +34689,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>367</v>
       </c>
@@ -34774,7 +34775,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>367</v>
       </c>
@@ -34863,7 +34864,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>367</v>
       </c>
@@ -34949,7 +34950,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>367</v>
       </c>
@@ -35038,7 +35039,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>367</v>
       </c>
@@ -35124,7 +35125,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>367</v>
       </c>
@@ -35210,7 +35211,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>369</v>
       </c>
@@ -35293,7 +35294,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>369</v>
       </c>
@@ -35376,7 +35377,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>369</v>
       </c>
@@ -35453,7 +35454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>369</v>
       </c>
@@ -35542,7 +35543,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>369</v>
       </c>
@@ -35631,7 +35632,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>369</v>
       </c>
@@ -35717,7 +35718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>369</v>
       </c>
@@ -35806,7 +35807,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>369</v>
       </c>
@@ -35892,7 +35893,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>376</v>
       </c>
@@ -35982,7 +35983,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>376</v>
       </c>
@@ -36068,7 +36069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>376</v>
       </c>
@@ -36157,7 +36158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>376</v>
       </c>
@@ -36243,7 +36244,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -36332,7 +36333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -36418,7 +36419,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -36507,7 +36508,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>376</v>
       </c>
@@ -36593,7 +36594,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="406" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>377</v>
       </c>
@@ -36682,7 +36683,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="407" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>377</v>
       </c>
@@ -36771,7 +36772,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="408" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>377</v>
       </c>
@@ -36857,7 +36858,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="409" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>377</v>
       </c>
@@ -36946,7 +36947,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="410" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>377</v>
       </c>
@@ -37035,7 +37036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="411" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>377</v>
       </c>
@@ -37121,7 +37122,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>377</v>
       </c>
@@ -37207,7 +37208,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>379</v>
       </c>
@@ -37291,7 +37292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>379</v>
       </c>
@@ -37372,7 +37373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>379</v>
       </c>
@@ -37456,7 +37457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>379</v>
       </c>
@@ -37540,7 +37541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>379</v>
       </c>
@@ -37624,7 +37625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>379</v>
       </c>
@@ -37705,7 +37706,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>379</v>
       </c>
@@ -37789,7 +37790,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>379</v>
       </c>
@@ -37873,7 +37874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>379</v>
       </c>
@@ -37954,7 +37955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>379</v>
       </c>
@@ -38038,7 +38039,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>379</v>
       </c>
@@ -38122,7 +38123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>379</v>
       </c>
@@ -38203,7 +38204,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>379</v>
       </c>
@@ -38292,7 +38293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>379</v>
       </c>
@@ -38381,7 +38382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>379</v>
       </c>
@@ -38467,7 +38468,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="428" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>379</v>
       </c>
@@ -38556,7 +38557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="429" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>379</v>
       </c>
@@ -38645,7 +38646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="430" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>379</v>
       </c>
@@ -38731,7 +38732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>379</v>
       </c>
@@ -38820,7 +38821,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="432" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>379</v>
       </c>
@@ -38909,7 +38910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="433" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>379</v>
       </c>
@@ -38995,7 +38996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>379</v>
       </c>
@@ -39084,7 +39085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="435" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>379</v>
       </c>
@@ -39162,7 +39163,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="436" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>379</v>
       </c>
@@ -39246,7 +39247,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="437" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>385</v>
       </c>
@@ -39329,7 +39330,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>385</v>
       </c>
@@ -39409,7 +39410,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>385</v>
       </c>
@@ -39492,7 +39493,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>385</v>
       </c>
@@ -39572,7 +39573,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>385</v>
       </c>
@@ -39655,7 +39656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="442" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>385</v>
       </c>
@@ -39735,7 +39736,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="443" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>385</v>
       </c>
@@ -39810,7 +39811,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="444" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>386.1</v>
       </c>
@@ -39891,7 +39892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="445" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>386.1</v>
       </c>
@@ -39969,7 +39970,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="446" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>386.1</v>
       </c>
@@ -40049,7 +40050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="447" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>386.1</v>
       </c>
@@ -40126,7 +40127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="448" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>386.1</v>
       </c>
@@ -40206,7 +40207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="449" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>386.1</v>
       </c>
@@ -40283,7 +40284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="450" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>386.1</v>
       </c>
@@ -40358,7 +40359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="451" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>386.2</v>
       </c>
@@ -40440,7 +40441,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="452" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>386.2</v>
       </c>
@@ -40519,7 +40520,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>386.2</v>
       </c>
@@ -40599,7 +40600,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>386.2</v>
       </c>
@@ -40676,7 +40677,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="455" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>386.2</v>
       </c>
@@ -40756,7 +40757,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="456" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>386.2</v>
       </c>
@@ -40833,7 +40834,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="457" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>386.2</v>
       </c>
@@ -40908,7 +40909,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="458" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>386.2</v>
       </c>
@@ -40980,7 +40981,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>386.3</v>
       </c>
@@ -41061,7 +41062,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="460" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>386.3</v>
       </c>
@@ -41139,7 +41140,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>386.3</v>
       </c>
@@ -41220,7 +41221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="462" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>386.3</v>
       </c>
@@ -41298,7 +41299,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="463" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>386.3</v>
       </c>
@@ -41378,7 +41379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="464" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>386.3</v>
       </c>
@@ -41455,7 +41456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="465" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>386.3</v>
       </c>
@@ -41530,7 +41531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="466" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>386.3</v>
       </c>
@@ -41602,7 +41603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="467" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>423</v>
       </c>
@@ -41685,7 +41686,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="468" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>423</v>
       </c>
@@ -41771,7 +41772,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="469" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>423</v>
       </c>
@@ -41854,7 +41855,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="470" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>423</v>
       </c>
@@ -41940,7 +41941,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>423</v>
       </c>
@@ -42023,7 +42024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>423</v>
       </c>
@@ -42109,7 +42110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>423</v>
       </c>
@@ -42192,7 +42193,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>424</v>
       </c>
@@ -42275,7 +42276,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>424</v>
       </c>
@@ -42361,7 +42362,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>424</v>
       </c>
@@ -42444,7 +42445,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="477" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>424</v>
       </c>
@@ -42530,7 +42531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>424</v>
       </c>
@@ -42613,7 +42614,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="479" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>424</v>
       </c>
@@ -42699,7 +42700,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="480" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>424</v>
       </c>
@@ -42782,7 +42783,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>460</v>
       </c>
@@ -42859,7 +42860,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="482" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>460</v>
       </c>
@@ -42948,7 +42949,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>460</v>
       </c>
@@ -43028,7 +43029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="484" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>460</v>
       </c>
@@ -43114,7 +43115,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="485" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>460</v>
       </c>
@@ -43200,7 +43201,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>466</v>
       </c>
@@ -43289,7 +43290,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="487" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>466</v>
       </c>
@@ -43378,7 +43379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="488" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>466</v>
       </c>
@@ -43464,7 +43465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="489" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>466</v>
       </c>
@@ -43550,7 +43551,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="490" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>466</v>
       </c>
@@ -43639,7 +43640,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="491" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>466</v>
       </c>
@@ -43725,7 +43726,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>466</v>
       </c>
@@ -43814,7 +43815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="493" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>466</v>
       </c>
@@ -43904,7 +43905,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="494" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>203</v>
       </c>
@@ -43988,7 +43989,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="495" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>203</v>
       </c>
@@ -44069,7 +44070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="496" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>148</v>
       </c>
@@ -44158,7 +44159,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="497" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>466</v>
       </c>
@@ -44332,7 +44333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="499" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>386.1</v>
       </c>
@@ -44404,7 +44405,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="500" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>385</v>
       </c>
@@ -44476,7 +44477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="501" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>423</v>
       </c>
@@ -44556,7 +44557,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="502" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>424</v>
       </c>
@@ -44647,7 +44648,13 @@
       <c r="L505" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC502" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC502" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="22">
+      <filters>
+        <filter val="Transformación_Organizacional"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC493">
     <sortCondition ref="A2:A493"/>
     <sortCondition ref="F2:F493"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1161" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAA6815-7C13-49E8-A97F-D11CF39680D5}"/>
+  <xr:revisionPtr revIDLastSave="1163" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F8C5E80-CC12-4614-ABA6-A7E53C5E1C60}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1926,7 +1926,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2031,7 +2030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2114,7 +2113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2197,7 +2196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2362,7 +2361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2695,7 +2694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2776,7 +2775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -2860,7 +2859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14</v>
       </c>
@@ -2944,7 +2943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
@@ -3025,7 +3024,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -3114,7 +3113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3289,7 +3288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3378,7 +3377,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>14</v>
       </c>
@@ -3467,7 +3466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>14</v>
       </c>
@@ -3553,7 +3552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>14</v>
       </c>
@@ -3642,7 +3641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>14</v>
       </c>
@@ -3731,7 +3730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>14</v>
       </c>
@@ -3817,7 +3816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>14</v>
       </c>
@@ -3906,7 +3905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>14</v>
       </c>
@@ -3986,7 +3985,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>14</v>
       </c>
@@ -4069,7 +4068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>14.1</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14.1</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>14.1</v>
       </c>
@@ -4318,7 +4317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>14.1</v>
       </c>
@@ -4402,7 +4401,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>14.1</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>14.1</v>
       </c>
@@ -4567,7 +4566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>14.1</v>
       </c>
@@ -4651,7 +4650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>14.1</v>
       </c>
@@ -4735,7 +4734,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>14.1</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>14.1</v>
       </c>
@@ -4900,7 +4899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>14.1</v>
       </c>
@@ -4984,7 +4983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>14.1</v>
       </c>
@@ -5065,7 +5064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>14.1</v>
       </c>
@@ -5154,7 +5153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>14.1</v>
       </c>
@@ -5243,7 +5242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>14.1</v>
       </c>
@@ -5329,7 +5328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>14.1</v>
       </c>
@@ -5418,7 +5417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>14.1</v>
       </c>
@@ -5507,7 +5506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>14.1</v>
       </c>
@@ -5593,7 +5592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14.1</v>
       </c>
@@ -5682,7 +5681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14.1</v>
       </c>
@@ -5771,7 +5770,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14.1</v>
       </c>
@@ -5857,7 +5856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14.1</v>
       </c>
@@ -5946,7 +5945,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14.1</v>
       </c>
@@ -6026,7 +6025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>14.1</v>
       </c>
@@ -6109,7 +6108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>14.2</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>14.2</v>
       </c>
@@ -6277,7 +6276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>14.2</v>
       </c>
@@ -6358,7 +6357,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>14.2</v>
       </c>
@@ -6442,7 +6441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>14.2</v>
       </c>
@@ -6526,7 +6525,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>14.2</v>
       </c>
@@ -6607,7 +6606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>14.2</v>
       </c>
@@ -6691,7 +6690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>14.2</v>
       </c>
@@ -6775,7 +6774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>14.2</v>
       </c>
@@ -6856,7 +6855,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>14.2</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>14.2</v>
       </c>
@@ -7024,7 +7023,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>14.2</v>
       </c>
@@ -7105,7 +7104,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>14.2</v>
       </c>
@@ -7194,7 +7193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>14.2</v>
       </c>
@@ -7283,7 +7282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>14.2</v>
       </c>
@@ -7369,7 +7368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>14.2</v>
       </c>
@@ -7458,7 +7457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>14.2</v>
       </c>
@@ -7547,7 +7546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>14.2</v>
       </c>
@@ -7633,7 +7632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>14.2</v>
       </c>
@@ -7722,7 +7721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>14.2</v>
       </c>
@@ -7811,7 +7810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>14.2</v>
       </c>
@@ -7897,7 +7896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>14.2</v>
       </c>
@@ -7986,7 +7985,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>14.2</v>
       </c>
@@ -8066,7 +8065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>14.2</v>
       </c>
@@ -8143,7 +8142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>14.3</v>
       </c>
@@ -8227,7 +8226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>14.3</v>
       </c>
@@ -8311,7 +8310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>14.3</v>
       </c>
@@ -8392,7 +8391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14.3</v>
       </c>
@@ -8476,7 +8475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14.3</v>
       </c>
@@ -8560,7 +8559,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14.3</v>
       </c>
@@ -8641,7 +8640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>14.3</v>
       </c>
@@ -8725,7 +8724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>14.3</v>
       </c>
@@ -8809,7 +8808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>14.3</v>
       </c>
@@ -8890,7 +8889,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>14.3</v>
       </c>
@@ -8974,7 +8973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>14.3</v>
       </c>
@@ -9058,7 +9057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>14.3</v>
       </c>
@@ -9139,7 +9138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>14.3</v>
       </c>
@@ -9228,7 +9227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>14.3</v>
       </c>
@@ -9317,7 +9316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>14.3</v>
       </c>
@@ -9403,7 +9402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>14.3</v>
       </c>
@@ -9492,7 +9491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>14.3</v>
       </c>
@@ -9581,7 +9580,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>14.3</v>
       </c>
@@ -9667,7 +9666,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>14.3</v>
       </c>
@@ -9756,7 +9755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>14.3</v>
       </c>
@@ -9845,7 +9844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>14.3</v>
       </c>
@@ -9931,7 +9930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>14.3</v>
       </c>
@@ -10020,7 +10019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>14.3</v>
       </c>
@@ -10109,7 +10108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>14.3</v>
       </c>
@@ -10186,7 +10185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>14.4</v>
       </c>
@@ -10270,7 +10269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>14.4</v>
       </c>
@@ -10354,7 +10353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>14.4</v>
       </c>
@@ -10435,7 +10434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>14.4</v>
       </c>
@@ -10519,7 +10518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>14.4</v>
       </c>
@@ -10603,7 +10602,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>14.4</v>
       </c>
@@ -10684,7 +10683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>14.4</v>
       </c>
@@ -10768,7 +10767,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>14.4</v>
       </c>
@@ -10852,7 +10851,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>14.4</v>
       </c>
@@ -10933,7 +10932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>14.4</v>
       </c>
@@ -11017,7 +11016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>14.4</v>
       </c>
@@ -11101,7 +11100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>14.4</v>
       </c>
@@ -11182,7 +11181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>14.4</v>
       </c>
@@ -11271,7 +11270,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>14.4</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>14.4</v>
       </c>
@@ -11446,7 +11445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>14.4</v>
       </c>
@@ -11535,7 +11534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>14.4</v>
       </c>
@@ -11624,7 +11623,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>14.4</v>
       </c>
@@ -11710,7 +11709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>14.4</v>
       </c>
@@ -11799,7 +11798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>14.4</v>
       </c>
@@ -11888,7 +11887,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>14.4</v>
       </c>
@@ -11974,7 +11973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>14.4</v>
       </c>
@@ -12063,7 +12062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.4</v>
       </c>
@@ -12152,7 +12151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>14.4</v>
       </c>
@@ -13196,7 +13195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>96</v>
       </c>
@@ -13285,7 +13284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>96</v>
       </c>
@@ -13371,7 +13370,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>96</v>
       </c>
@@ -13460,7 +13459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>96</v>
       </c>
@@ -13549,7 +13548,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>96</v>
       </c>
@@ -13635,7 +13634,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>96</v>
       </c>
@@ -13724,7 +13723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>96</v>
       </c>
@@ -13813,7 +13812,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>96</v>
       </c>
@@ -13899,7 +13898,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>97</v>
       </c>
@@ -13988,7 +13987,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>97</v>
       </c>
@@ -14071,7 +14070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>97</v>
       </c>
@@ -14157,7 +14156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>97</v>
       </c>
@@ -14234,7 +14233,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>97</v>
       </c>
@@ -14311,7 +14310,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>97</v>
       </c>
@@ -14391,7 +14390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>97</v>
       </c>
@@ -14468,7 +14467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>97</v>
       </c>
@@ -14545,7 +14544,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>97</v>
       </c>
@@ -14625,7 +14624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>97</v>
       </c>
@@ -14705,7 +14704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>98</v>
       </c>
@@ -14788,7 +14787,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>98</v>
       </c>
@@ -14877,7 +14876,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>98</v>
       </c>
@@ -14963,7 +14962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>98</v>
       </c>
@@ -15046,7 +15045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>98</v>
       </c>
@@ -15135,7 +15134,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>98</v>
       </c>
@@ -15221,7 +15220,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>98</v>
       </c>
@@ -15298,7 +15297,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>98</v>
       </c>
@@ -15387,7 +15386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>98</v>
       </c>
@@ -15473,7 +15472,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>98</v>
       </c>
@@ -15562,7 +15561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>98</v>
       </c>
@@ -16070,7 +16069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>148</v>
       </c>
@@ -16156,7 +16155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>148</v>
       </c>
@@ -16245,7 +16244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>148</v>
       </c>
@@ -16334,7 +16333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>148</v>
       </c>
@@ -16420,7 +16419,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>148</v>
       </c>
@@ -16509,7 +16508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>148</v>
       </c>
@@ -16598,7 +16597,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>148</v>
       </c>
@@ -16684,7 +16683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>148</v>
       </c>
@@ -16773,7 +16772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>148</v>
       </c>
@@ -16859,7 +16858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>193</v>
       </c>
@@ -16948,7 +16947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>193</v>
       </c>
@@ -17037,7 +17036,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>193</v>
       </c>
@@ -17123,7 +17122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>193</v>
       </c>
@@ -17212,7 +17211,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>193</v>
       </c>
@@ -17301,7 +17300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>193</v>
       </c>
@@ -17387,7 +17386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>193</v>
       </c>
@@ -17476,7 +17475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>193</v>
       </c>
@@ -17565,7 +17564,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>193</v>
       </c>
@@ -17651,7 +17650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>193</v>
       </c>
@@ -17740,7 +17739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>193</v>
       </c>
@@ -17826,7 +17825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>194</v>
       </c>
@@ -17915,7 +17914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>194</v>
       </c>
@@ -18004,7 +18003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>194</v>
       </c>
@@ -18090,7 +18089,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>194</v>
       </c>
@@ -18179,7 +18178,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>194</v>
       </c>
@@ -18268,7 +18267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>194</v>
       </c>
@@ -18354,7 +18353,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>194</v>
       </c>
@@ -18443,7 +18442,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>194</v>
       </c>
@@ -18532,7 +18531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -18618,7 +18617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -18707,7 +18706,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>194</v>
       </c>
@@ -20050,7 +20049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>203</v>
       </c>
@@ -20139,7 +20138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>203</v>
       </c>
@@ -20228,7 +20227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>203</v>
       </c>
@@ -20314,7 +20313,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>203</v>
       </c>
@@ -20403,7 +20402,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>203</v>
       </c>
@@ -20492,7 +20491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>203</v>
       </c>
@@ -20578,7 +20577,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>203</v>
       </c>
@@ -20667,7 +20666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>203</v>
       </c>
@@ -20756,7 +20755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>203</v>
       </c>
@@ -20842,7 +20841,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>203</v>
       </c>
@@ -20931,7 +20930,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>204</v>
       </c>
@@ -21020,7 +21019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>204</v>
       </c>
@@ -21109,7 +21108,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>204</v>
       </c>
@@ -21183,7 +21182,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>204</v>
       </c>
@@ -21272,7 +21271,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>204</v>
       </c>
@@ -21361,7 +21360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>204</v>
       </c>
@@ -21447,7 +21446,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>204</v>
       </c>
@@ -21536,7 +21535,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>204</v>
       </c>
@@ -21625,7 +21624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>204</v>
       </c>
@@ -21711,7 +21710,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>204</v>
       </c>
@@ -21800,7 +21799,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>204</v>
       </c>
@@ -21886,7 +21885,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>205</v>
       </c>
@@ -21975,7 +21974,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>205</v>
       </c>
@@ -22064,7 +22063,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>205</v>
       </c>
@@ -22150,7 +22149,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>205</v>
       </c>
@@ -22239,7 +22238,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>205</v>
       </c>
@@ -22328,7 +22327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>205</v>
       </c>
@@ -22414,7 +22413,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>205</v>
       </c>
@@ -22503,7 +22502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>205</v>
       </c>
@@ -22589,7 +22588,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>207</v>
       </c>
@@ -22678,7 +22677,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>207</v>
       </c>
@@ -22767,7 +22766,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>207</v>
       </c>
@@ -22853,7 +22852,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>207</v>
       </c>
@@ -22942,7 +22941,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>207</v>
       </c>
@@ -23031,7 +23030,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>207</v>
       </c>
@@ -23117,7 +23116,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>207</v>
       </c>
@@ -23206,7 +23205,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>207</v>
       </c>
@@ -23292,7 +23291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>228</v>
       </c>
@@ -23375,7 +23374,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>228</v>
       </c>
@@ -23461,7 +23460,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>228</v>
       </c>
@@ -23547,7 +23546,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>228</v>
       </c>
@@ -23618,7 +23617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>228</v>
       </c>
@@ -23704,7 +23703,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>228</v>
       </c>
@@ -23790,7 +23789,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>244</v>
       </c>
@@ -23876,7 +23875,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>244</v>
       </c>
@@ -23959,7 +23958,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>244</v>
       </c>
@@ -24045,7 +24044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>244</v>
       </c>
@@ -24128,7 +24127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>244</v>
       </c>
@@ -24214,7 +24213,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>244</v>
       </c>
@@ -24300,7 +24299,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>245</v>
       </c>
@@ -24389,7 +24388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>245</v>
       </c>
@@ -24478,7 +24477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>245</v>
       </c>
@@ -24564,7 +24563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>245</v>
       </c>
@@ -24653,7 +24652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>245</v>
       </c>
@@ -24742,7 +24741,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>245</v>
       </c>
@@ -24828,7 +24827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>245</v>
       </c>
@@ -24917,7 +24916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>245</v>
       </c>
@@ -25000,7 +24999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>245</v>
       </c>
@@ -25086,7 +25085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>245</v>
       </c>
@@ -25175,7 +25174,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>245</v>
       </c>
@@ -25261,7 +25260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>274</v>
       </c>
@@ -25345,7 +25344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>274</v>
       </c>
@@ -25429,7 +25428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -25510,7 +25509,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>274</v>
       </c>
@@ -25594,7 +25593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25678,7 +25677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25759,7 +25758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -25843,7 +25842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>274</v>
       </c>
@@ -25927,7 +25926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>274</v>
       </c>
@@ -26008,7 +26007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>274</v>
       </c>
@@ -26092,7 +26091,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -26176,7 +26175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>274</v>
       </c>
@@ -26257,7 +26256,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>274</v>
       </c>
@@ -26346,7 +26345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>274</v>
       </c>
@@ -26435,7 +26434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>274</v>
       </c>
@@ -26521,7 +26520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>274</v>
       </c>
@@ -26610,7 +26609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>274</v>
       </c>
@@ -26699,7 +26698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>274</v>
       </c>
@@ -26785,7 +26784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>274</v>
       </c>
@@ -26874,7 +26873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>274</v>
       </c>
@@ -26963,7 +26962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>274</v>
       </c>
@@ -27049,7 +27048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>274</v>
       </c>
@@ -27138,7 +27137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>274</v>
       </c>
@@ -27225,7 +27224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>274</v>
       </c>
@@ -27309,7 +27308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>276</v>
       </c>
@@ -27392,7 +27391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>276</v>
       </c>
@@ -27475,7 +27474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>276</v>
       </c>
@@ -27561,7 +27560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>276</v>
       </c>
@@ -27644,7 +27643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>276</v>
       </c>
@@ -27727,7 +27726,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>276</v>
       </c>
@@ -27813,7 +27812,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>276</v>
       </c>
@@ -27896,7 +27895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>276</v>
       </c>
@@ -27979,7 +27978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>276</v>
       </c>
@@ -28065,7 +28064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>276</v>
       </c>
@@ -28154,7 +28153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>276</v>
       </c>
@@ -28240,7 +28239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>277</v>
       </c>
@@ -28320,7 +28319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>277</v>
       </c>
@@ -28400,7 +28399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>277</v>
       </c>
@@ -28483,7 +28482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>277</v>
       </c>
@@ -28563,7 +28562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>277</v>
       </c>
@@ -28643,7 +28642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>277</v>
       </c>
@@ -28726,7 +28725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>277</v>
       </c>
@@ -28812,7 +28811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>277</v>
       </c>
@@ -28895,7 +28894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>323</v>
       </c>
@@ -28978,7 +28977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>323</v>
       </c>
@@ -29064,7 +29063,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>323</v>
       </c>
@@ -29147,7 +29146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>323</v>
       </c>
@@ -29230,7 +29229,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>323</v>
       </c>
@@ -29316,7 +29315,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>323</v>
       </c>
@@ -29399,7 +29398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>323</v>
       </c>
@@ -29476,7 +29475,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>323</v>
       </c>
@@ -29562,7 +29561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -29651,7 +29650,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>323</v>
       </c>
@@ -29737,7 +29736,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -29826,7 +29825,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>325</v>
       </c>
@@ -29915,7 +29914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>325</v>
       </c>
@@ -30001,7 +30000,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>325</v>
       </c>
@@ -30090,7 +30089,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>325</v>
       </c>
@@ -30167,7 +30166,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>325</v>
       </c>
@@ -30253,7 +30252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>325</v>
       </c>
@@ -30342,7 +30341,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>325</v>
       </c>
@@ -30431,7 +30430,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>325</v>
       </c>
@@ -30517,7 +30516,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>325</v>
       </c>
@@ -30606,7 +30605,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>325</v>
       </c>
@@ -30692,7 +30691,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>331</v>
       </c>
@@ -30775,7 +30774,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>331</v>
       </c>
@@ -30852,7 +30851,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>331</v>
       </c>
@@ -30935,7 +30934,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>331</v>
       </c>
@@ -31012,7 +31011,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>331</v>
       </c>
@@ -31092,7 +31091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>331</v>
       </c>
@@ -33037,7 +33036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>339</v>
       </c>
@@ -33126,7 +33125,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>339</v>
       </c>
@@ -33212,7 +33211,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>339</v>
       </c>
@@ -33301,7 +33300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>339</v>
       </c>
@@ -33387,7 +33386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>339</v>
       </c>
@@ -33476,7 +33475,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>339</v>
       </c>
@@ -33562,7 +33561,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>361</v>
       </c>
@@ -33643,7 +33642,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>361</v>
       </c>
@@ -33732,7 +33731,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>361</v>
       </c>
@@ -33818,7 +33817,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>361</v>
       </c>
@@ -33908,7 +33907,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>361</v>
       </c>
@@ -33995,7 +33994,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>364</v>
       </c>
@@ -34084,7 +34083,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>364</v>
       </c>
@@ -34173,7 +34172,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>364</v>
       </c>
@@ -34250,7 +34249,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>364</v>
       </c>
@@ -34339,7 +34338,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>364</v>
       </c>
@@ -34428,7 +34427,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>364</v>
       </c>
@@ -34514,7 +34513,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>364</v>
       </c>
@@ -34603,7 +34602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>364</v>
       </c>
@@ -34689,7 +34688,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>367</v>
       </c>
@@ -34775,7 +34774,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>367</v>
       </c>
@@ -34864,7 +34863,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>367</v>
       </c>
@@ -34950,7 +34949,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>367</v>
       </c>
@@ -35039,7 +35038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>367</v>
       </c>
@@ -35125,7 +35124,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>367</v>
       </c>
@@ -35211,7 +35210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>369</v>
       </c>
@@ -35294,7 +35293,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>369</v>
       </c>
@@ -35377,7 +35376,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>369</v>
       </c>
@@ -35454,7 +35453,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>369</v>
       </c>
@@ -35543,7 +35542,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>369</v>
       </c>
@@ -35632,7 +35631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>369</v>
       </c>
@@ -35718,7 +35717,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>369</v>
       </c>
@@ -35807,7 +35806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>369</v>
       </c>
@@ -35893,7 +35892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>376</v>
       </c>
@@ -35983,7 +35982,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>376</v>
       </c>
@@ -36069,7 +36068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>376</v>
       </c>
@@ -36158,7 +36157,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>376</v>
       </c>
@@ -36244,7 +36243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>376</v>
       </c>
@@ -36333,7 +36332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>376</v>
       </c>
@@ -36419,7 +36418,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>376</v>
       </c>
@@ -36508,7 +36507,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>376</v>
       </c>
@@ -36594,7 +36593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="406" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>377</v>
       </c>
@@ -36683,7 +36682,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="407" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>377</v>
       </c>
@@ -36772,7 +36771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="408" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>377</v>
       </c>
@@ -36858,7 +36857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="409" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>377</v>
       </c>
@@ -36947,7 +36946,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="410" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>377</v>
       </c>
@@ -37036,7 +37035,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="411" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>377</v>
       </c>
@@ -37122,7 +37121,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>377</v>
       </c>
@@ -37208,7 +37207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>379</v>
       </c>
@@ -37292,7 +37291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>379</v>
       </c>
@@ -37373,7 +37372,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>379</v>
       </c>
@@ -37457,7 +37456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>379</v>
       </c>
@@ -37541,7 +37540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>379</v>
       </c>
@@ -37625,7 +37624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>379</v>
       </c>
@@ -37706,7 +37705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>379</v>
       </c>
@@ -37790,7 +37789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>379</v>
       </c>
@@ -37874,7 +37873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>379</v>
       </c>
@@ -37955,7 +37954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>379</v>
       </c>
@@ -38039,7 +38038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>379</v>
       </c>
@@ -38123,7 +38122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>379</v>
       </c>
@@ -38204,7 +38203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>379</v>
       </c>
@@ -38293,7 +38292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>379</v>
       </c>
@@ -38382,7 +38381,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>379</v>
       </c>
@@ -38468,7 +38467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="428" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>379</v>
       </c>
@@ -38557,7 +38556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="429" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>379</v>
       </c>
@@ -38646,7 +38645,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="430" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>379</v>
       </c>
@@ -38732,7 +38731,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="431" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>379</v>
       </c>
@@ -38821,7 +38820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="432" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>379</v>
       </c>
@@ -38910,7 +38909,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="433" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>379</v>
       </c>
@@ -38996,7 +38995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="434" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>379</v>
       </c>
@@ -39085,7 +39084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="435" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>379</v>
       </c>
@@ -39163,7 +39162,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="436" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>379</v>
       </c>
@@ -39247,7 +39246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="437" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>385</v>
       </c>
@@ -39330,7 +39329,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>385</v>
       </c>
@@ -39410,7 +39409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>385</v>
       </c>
@@ -39493,7 +39492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>385</v>
       </c>
@@ -39573,7 +39572,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>385</v>
       </c>
@@ -39656,7 +39655,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="442" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>385</v>
       </c>
@@ -39736,7 +39735,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="443" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>385</v>
       </c>
@@ -39811,7 +39810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="444" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>386.1</v>
       </c>
@@ -39892,7 +39891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="445" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>386.1</v>
       </c>
@@ -39970,7 +39969,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="446" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>386.1</v>
       </c>
@@ -40050,7 +40049,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="447" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>386.1</v>
       </c>
@@ -40127,7 +40126,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="448" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>386.1</v>
       </c>
@@ -40207,7 +40206,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="449" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>386.1</v>
       </c>
@@ -40284,7 +40283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="450" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>386.1</v>
       </c>
@@ -40359,7 +40358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="451" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>386.2</v>
       </c>
@@ -40441,7 +40440,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="452" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>386.2</v>
       </c>
@@ -40520,7 +40519,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>386.2</v>
       </c>
@@ -40600,7 +40599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>386.2</v>
       </c>
@@ -40677,7 +40676,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="455" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>386.2</v>
       </c>
@@ -40757,7 +40756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="456" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>386.2</v>
       </c>
@@ -40834,7 +40833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="457" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>386.2</v>
       </c>
@@ -40909,7 +40908,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="458" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>386.2</v>
       </c>
@@ -40981,7 +40980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>386.3</v>
       </c>
@@ -41062,7 +41061,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="460" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>386.3</v>
       </c>
@@ -41140,7 +41139,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>386.3</v>
       </c>
@@ -41221,7 +41220,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="462" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>386.3</v>
       </c>
@@ -41299,7 +41298,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="463" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>386.3</v>
       </c>
@@ -41379,7 +41378,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="464" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>386.3</v>
       </c>
@@ -41456,7 +41455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="465" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>386.3</v>
       </c>
@@ -41531,7 +41530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="466" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>386.3</v>
       </c>
@@ -41603,7 +41602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="467" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>423</v>
       </c>
@@ -41686,7 +41685,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="468" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>423</v>
       </c>
@@ -41772,7 +41771,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="469" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>423</v>
       </c>
@@ -41855,7 +41854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="470" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>423</v>
       </c>
@@ -41941,7 +41940,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>423</v>
       </c>
@@ -42024,7 +42023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>423</v>
       </c>
@@ -42110,7 +42109,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>423</v>
       </c>
@@ -42193,7 +42192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>424</v>
       </c>
@@ -42276,7 +42275,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>424</v>
       </c>
@@ -42362,7 +42361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>424</v>
       </c>
@@ -42445,7 +42444,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="477" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>424</v>
       </c>
@@ -42531,7 +42530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>424</v>
       </c>
@@ -42614,7 +42613,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="479" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>424</v>
       </c>
@@ -42700,7 +42699,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="480" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>424</v>
       </c>
@@ -42783,7 +42782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>460</v>
       </c>
@@ -42860,7 +42859,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="482" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>460</v>
       </c>
@@ -42949,7 +42948,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>460</v>
       </c>
@@ -43029,7 +43028,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="484" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>460</v>
       </c>
@@ -43115,7 +43114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="485" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>460</v>
       </c>
@@ -43201,7 +43200,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>466</v>
       </c>
@@ -43290,7 +43289,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="487" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>466</v>
       </c>
@@ -43379,7 +43378,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="488" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>466</v>
       </c>
@@ -43465,7 +43464,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="489" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>466</v>
       </c>
@@ -43551,7 +43550,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="490" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>466</v>
       </c>
@@ -43640,7 +43639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="491" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>466</v>
       </c>
@@ -43726,7 +43725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>466</v>
       </c>
@@ -43815,7 +43814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="493" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>466</v>
       </c>
@@ -43905,7 +43904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="494" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>203</v>
       </c>
@@ -43989,7 +43988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="495" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>203</v>
       </c>
@@ -44070,7 +44069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="496" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>148</v>
       </c>
@@ -44159,7 +44158,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="497" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>466</v>
       </c>
@@ -44333,7 +44332,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="499" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>386.1</v>
       </c>
@@ -44405,7 +44404,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="500" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>385</v>
       </c>
@@ -44477,7 +44476,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="501" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>423</v>
       </c>
@@ -44557,7 +44556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="502" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>424</v>
       </c>
@@ -44648,13 +44647,7 @@
       <c r="L505" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC502" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="22">
-      <filters>
-        <filter val="Transformación_Organizacional"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AC502" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC493">
     <sortCondition ref="A2:A493"/>
     <sortCondition ref="F2:F493"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1337" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9317C94A-2322-43D4-A624-061C03E66349}"/>
+  <xr:revisionPtr revIDLastSave="1350" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2519E97C-F21B-4734-9548-E26F88DD5F05}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Cierres_Original" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Unificado!$A$1:$AC$504</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14195" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14214" uniqueCount="509">
   <si>
     <t>Id</t>
   </si>
@@ -1564,6 +1564,9 @@
   <si>
     <t>339-2022-12-31</t>
   </si>
+  <si>
+    <t>96-2025-12-31</t>
+  </si>
 </sst>
 </file>
 
@@ -1636,7 +1639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1646,7 +1649,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1950,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC503"/>
+  <dimension ref="A1:AC504"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -33428,7 +33430,7 @@
       <c r="K369">
         <v>30</v>
       </c>
-      <c r="L369" s="7">
+      <c r="L369">
         <v>33.299999999999997</v>
       </c>
       <c r="M369">
@@ -44697,6 +44699,83 @@
         <v>43</v>
       </c>
       <c r="AC503" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="504" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A504">
+        <v>96</v>
+      </c>
+      <c r="B504" t="s">
+        <v>70</v>
+      </c>
+      <c r="C504" t="s">
+        <v>71</v>
+      </c>
+      <c r="D504" t="s">
+        <v>66</v>
+      </c>
+      <c r="E504" t="s">
+        <v>32</v>
+      </c>
+      <c r="F504" s="3">
+        <v>46022</v>
+      </c>
+      <c r="G504">
+        <v>2025</v>
+      </c>
+      <c r="H504" t="s">
+        <v>44</v>
+      </c>
+      <c r="I504" t="s">
+        <v>465</v>
+      </c>
+      <c r="L504">
+        <v>740</v>
+      </c>
+      <c r="O504" t="s">
+        <v>35</v>
+      </c>
+      <c r="P504" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q504" t="s">
+        <v>508</v>
+      </c>
+      <c r="R504">
+        <v>0</v>
+      </c>
+      <c r="S504">
+        <v>0</v>
+      </c>
+      <c r="T504" t="s">
+        <v>443</v>
+      </c>
+      <c r="U504" t="s">
+        <v>37</v>
+      </c>
+      <c r="V504" t="s">
+        <v>71</v>
+      </c>
+      <c r="W504" t="s">
+        <v>73</v>
+      </c>
+      <c r="X504" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y504" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z504" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA504" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB504" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC504" t="s">
         <v>66</v>
       </c>
     </row>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1358" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D0C5291-0C01-4993-9D13-33B747A09DDC}"/>
+  <xr:revisionPtr revIDLastSave="1360" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC546522-844A-44C1-BD9F-2B317E16A401}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1952,7 +1952,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC494"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2057,7 +2056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>14</v>
       </c>
@@ -2140,7 +2139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>14</v>
       </c>
@@ -2223,7 +2222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>14</v>
       </c>
@@ -2304,7 +2303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>14</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>14</v>
       </c>
@@ -2472,7 +2471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>14</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2637,7 +2636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2721,7 +2720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2802,7 +2801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>14</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
@@ -3051,7 +3050,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3315,7 +3314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -3404,7 +3403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>14</v>
       </c>
@@ -3493,7 +3492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>14</v>
       </c>
@@ -3579,7 +3578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>14</v>
       </c>
@@ -3668,7 +3667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>14</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>14</v>
       </c>
@@ -3843,7 +3842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>14</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>14</v>
       </c>
@@ -4012,7 +4011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>14</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>14.1</v>
       </c>
@@ -4179,7 +4178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>14.1</v>
       </c>
@@ -4263,7 +4262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>14.1</v>
       </c>
@@ -4344,7 +4343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>14.1</v>
       </c>
@@ -4428,7 +4427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>14.1</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>14.1</v>
       </c>
@@ -4593,7 +4592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>14.1</v>
       </c>
@@ -4677,7 +4676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>14.1</v>
       </c>
@@ -4761,7 +4760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>14.1</v>
       </c>
@@ -4842,7 +4841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>14.1</v>
       </c>
@@ -4926,7 +4925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>14.1</v>
       </c>
@@ -5010,7 +5009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>14.1</v>
       </c>
@@ -5091,7 +5090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>14.1</v>
       </c>
@@ -5180,7 +5179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>14.1</v>
       </c>
@@ -5269,7 +5268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>14.1</v>
       </c>
@@ -5355,7 +5354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>14.1</v>
       </c>
@@ -5444,7 +5443,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>14.1</v>
       </c>
@@ -5533,7 +5532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>14.1</v>
       </c>
@@ -5619,7 +5618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>14.1</v>
       </c>
@@ -5708,7 +5707,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>14.1</v>
       </c>
@@ -5797,7 +5796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>14.1</v>
       </c>
@@ -5883,7 +5882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>14.1</v>
       </c>
@@ -5972,7 +5971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>14.1</v>
       </c>
@@ -6052,7 +6051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>14.1</v>
       </c>
@@ -6135,7 +6134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>14.2</v>
       </c>
@@ -6219,7 +6218,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>14.2</v>
       </c>
@@ -6303,7 +6302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>14.2</v>
       </c>
@@ -6384,7 +6383,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>14.2</v>
       </c>
@@ -6468,7 +6467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>14.2</v>
       </c>
@@ -6552,7 +6551,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>14.2</v>
       </c>
@@ -6633,7 +6632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>14.2</v>
       </c>
@@ -6717,7 +6716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>14.2</v>
       </c>
@@ -6801,7 +6800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>14.2</v>
       </c>
@@ -6882,7 +6881,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>14.2</v>
       </c>
@@ -6966,7 +6965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>14.2</v>
       </c>
@@ -7050,7 +7049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>14.2</v>
       </c>
@@ -7131,7 +7130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>14.2</v>
       </c>
@@ -7220,7 +7219,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>14.2</v>
       </c>
@@ -7309,7 +7308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>14.2</v>
       </c>
@@ -7395,7 +7394,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>14.2</v>
       </c>
@@ -7484,7 +7483,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>14.2</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>14.2</v>
       </c>
@@ -7659,7 +7658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>14.2</v>
       </c>
@@ -7748,7 +7747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>14.2</v>
       </c>
@@ -7837,7 +7836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>14.2</v>
       </c>
@@ -7923,7 +7922,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>14.2</v>
       </c>
@@ -8012,7 +8011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>14.2</v>
       </c>
@@ -8092,7 +8091,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>14.2</v>
       </c>
@@ -8169,7 +8168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>14.3</v>
       </c>
@@ -8253,7 +8252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>14.3</v>
       </c>
@@ -8337,7 +8336,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>14.3</v>
       </c>
@@ -8418,7 +8417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>14.3</v>
       </c>
@@ -8502,7 +8501,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>14.3</v>
       </c>
@@ -8586,7 +8585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>14.3</v>
       </c>
@@ -8667,7 +8666,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>14.3</v>
       </c>
@@ -8751,7 +8750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>14.3</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>14.3</v>
       </c>
@@ -8916,7 +8915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>14.3</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>14.3</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>14.3</v>
       </c>
@@ -9165,7 +9164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>14.3</v>
       </c>
@@ -9254,7 +9253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>14.3</v>
       </c>
@@ -9343,7 +9342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>14.3</v>
       </c>
@@ -9429,7 +9428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>14.3</v>
       </c>
@@ -9518,7 +9517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>14.3</v>
       </c>
@@ -9607,7 +9606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>14.3</v>
       </c>
@@ -9693,7 +9692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>14.3</v>
       </c>
@@ -9782,7 +9781,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>14.3</v>
       </c>
@@ -9871,7 +9870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>14.3</v>
       </c>
@@ -9957,7 +9956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>14.3</v>
       </c>
@@ -10046,7 +10045,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>14.3</v>
       </c>
@@ -10135,7 +10134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>14.3</v>
       </c>
@@ -10212,7 +10211,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>14.4</v>
       </c>
@@ -10296,7 +10295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>14.4</v>
       </c>
@@ -10380,7 +10379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>14.4</v>
       </c>
@@ -10461,7 +10460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>14.4</v>
       </c>
@@ -10545,7 +10544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>14.4</v>
       </c>
@@ -10629,7 +10628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>14.4</v>
       </c>
@@ -10710,7 +10709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>14.4</v>
       </c>
@@ -10794,7 +10793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>14.4</v>
       </c>
@@ -10878,7 +10877,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>14.4</v>
       </c>
@@ -10959,7 +10958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>14.4</v>
       </c>
@@ -11043,7 +11042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>14.4</v>
       </c>
@@ -11127,7 +11126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>14.4</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>14.4</v>
       </c>
@@ -11297,7 +11296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>14.4</v>
       </c>
@@ -11386,7 +11385,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>14.4</v>
       </c>
@@ -11472,7 +11471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>14.4</v>
       </c>
@@ -11561,7 +11560,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>14.4</v>
       </c>
@@ -11650,7 +11649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>14.4</v>
       </c>
@@ -11736,7 +11735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>14.4</v>
       </c>
@@ -11825,7 +11824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>14.4</v>
       </c>
@@ -11914,7 +11913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>14.4</v>
       </c>
@@ -12000,7 +11999,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>14.4</v>
       </c>
@@ -12089,7 +12088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>14.4</v>
       </c>
@@ -12178,7 +12177,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>14.4</v>
       </c>
@@ -12255,7 +12254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>77</v>
       </c>
@@ -12344,7 +12343,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>77</v>
       </c>
@@ -12433,7 +12432,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>77</v>
       </c>
@@ -12519,7 +12518,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>77</v>
       </c>
@@ -12608,7 +12607,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>77</v>
       </c>
@@ -12697,7 +12696,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>77</v>
       </c>
@@ -12783,7 +12782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>77</v>
       </c>
@@ -12872,7 +12871,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>77</v>
       </c>
@@ -12961,7 +12960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>77</v>
       </c>
@@ -13047,7 +13046,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>77</v>
       </c>
@@ -13136,7 +13135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>77</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>96</v>
       </c>
@@ -13313,7 +13312,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>96</v>
       </c>
@@ -13399,7 +13398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>96</v>
       </c>
@@ -13488,7 +13487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>96</v>
       </c>
@@ -13577,7 +13576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>96</v>
       </c>
@@ -13663,7 +13662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>96</v>
       </c>
@@ -13752,7 +13751,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>96</v>
       </c>
@@ -13841,7 +13840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>96</v>
       </c>
@@ -14099,7 +14098,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>98</v>
       </c>
@@ -14357,7 +14356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>98</v>
       </c>
@@ -14609,7 +14608,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>98</v>
       </c>
@@ -14784,7 +14783,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>98</v>
       </c>
@@ -14870,7 +14869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>109</v>
       </c>
@@ -14956,7 +14955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>109</v>
       </c>
@@ -15039,7 +15038,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>109</v>
       </c>
@@ -15125,7 +15124,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>109</v>
       </c>
@@ -15208,7 +15207,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>109</v>
       </c>
@@ -15292,7 +15291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>148</v>
       </c>
@@ -15378,7 +15377,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>148</v>
       </c>
@@ -15467,7 +15466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>148</v>
       </c>
@@ -15556,7 +15555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>148</v>
       </c>
@@ -15642,7 +15641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>148</v>
       </c>
@@ -15731,7 +15730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>148</v>
       </c>
@@ -15820,7 +15819,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>148</v>
       </c>
@@ -15906,7 +15905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>148</v>
       </c>
@@ -15995,7 +15994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>148</v>
       </c>
@@ -16081,7 +16080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>193</v>
       </c>
@@ -16170,7 +16169,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>193</v>
       </c>
@@ -16259,7 +16258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>193</v>
       </c>
@@ -16345,7 +16344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>193</v>
       </c>
@@ -16434,7 +16433,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>193</v>
       </c>
@@ -16523,7 +16522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>193</v>
       </c>
@@ -16609,7 +16608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>193</v>
       </c>
@@ -16698,7 +16697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>193</v>
       </c>
@@ -16787,7 +16786,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>193</v>
       </c>
@@ -16873,7 +16872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>193</v>
       </c>
@@ -16962,7 +16961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>193</v>
       </c>
@@ -17048,7 +17047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>194</v>
       </c>
@@ -17137,7 +17136,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>194</v>
       </c>
@@ -17226,7 +17225,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>194</v>
       </c>
@@ -17312,7 +17311,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>194</v>
       </c>
@@ -17401,7 +17400,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>194</v>
       </c>
@@ -17490,7 +17489,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>194</v>
       </c>
@@ -17576,7 +17575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>194</v>
       </c>
@@ -17665,7 +17664,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>194</v>
       </c>
@@ -17754,7 +17753,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>194</v>
       </c>
@@ -17840,7 +17839,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>194</v>
       </c>
@@ -17929,7 +17928,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>194</v>
       </c>
@@ -18015,7 +18014,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>200</v>
       </c>
@@ -18095,7 +18094,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>200</v>
       </c>
@@ -18172,7 +18171,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>200</v>
       </c>
@@ -18255,7 +18254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>200</v>
       </c>
@@ -18341,7 +18340,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>200</v>
       </c>
@@ -18427,7 +18426,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>202</v>
       </c>
@@ -18508,7 +18507,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>202</v>
       </c>
@@ -18592,7 +18591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>202</v>
       </c>
@@ -18676,7 +18675,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>202</v>
       </c>
@@ -18757,7 +18756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>202</v>
       </c>
@@ -18841,7 +18840,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>202</v>
       </c>
@@ -18922,7 +18921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>202</v>
       </c>
@@ -19011,7 +19010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>202</v>
       </c>
@@ -19097,7 +19096,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>202</v>
       </c>
@@ -19186,7 +19185,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>202</v>
       </c>
@@ -19272,7 +19271,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>203</v>
       </c>
@@ -19361,7 +19360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -19450,7 +19449,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>203</v>
       </c>
@@ -19536,7 +19535,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>203</v>
       </c>
@@ -19625,7 +19624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>203</v>
       </c>
@@ -19714,7 +19713,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>203</v>
       </c>
@@ -19800,7 +19799,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>203</v>
       </c>
@@ -19889,7 +19888,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>203</v>
       </c>
@@ -19978,7 +19977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>203</v>
       </c>
@@ -20064,7 +20063,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>203</v>
       </c>
@@ -20153,7 +20152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>204</v>
       </c>
@@ -20242,7 +20241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>204</v>
       </c>
@@ -20328,7 +20327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="215" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>204</v>
       </c>
@@ -20417,7 +20416,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>204</v>
       </c>
@@ -20503,7 +20502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="217" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>204</v>
       </c>
@@ -20584,7 +20583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>204</v>
       </c>
@@ -20662,7 +20661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>205</v>
       </c>
@@ -20748,7 +20747,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>205</v>
       </c>
@@ -20831,7 +20830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>205</v>
       </c>
@@ -20920,7 +20919,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>205</v>
       </c>
@@ -21009,7 +21008,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>205</v>
       </c>
@@ -21095,7 +21094,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>205</v>
       </c>
@@ -21184,7 +21183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>205</v>
       </c>
@@ -21273,7 +21272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>205</v>
       </c>
@@ -21359,7 +21358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>205</v>
       </c>
@@ -21448,7 +21447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>205</v>
       </c>
@@ -21531,7 +21530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>207</v>
       </c>
@@ -21620,7 +21619,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>207</v>
       </c>
@@ -21709,7 +21708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>207</v>
       </c>
@@ -21795,7 +21794,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>207</v>
       </c>
@@ -21884,7 +21883,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>207</v>
       </c>
@@ -21973,7 +21972,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>207</v>
       </c>
@@ -22059,7 +22058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>207</v>
       </c>
@@ -22148,7 +22147,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>207</v>
       </c>
@@ -22225,7 +22224,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>228</v>
       </c>
@@ -22308,7 +22307,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>228</v>
       </c>
@@ -22394,7 +22393,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>228</v>
       </c>
@@ -22480,7 +22479,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>228</v>
       </c>
@@ -22551,7 +22550,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>228</v>
       </c>
@@ -22637,7 +22636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>228</v>
       </c>
@@ -22723,7 +22722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>244</v>
       </c>
@@ -22809,7 +22808,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>244</v>
       </c>
@@ -22892,7 +22891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -22978,7 +22977,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>244</v>
       </c>
@@ -23061,7 +23060,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>244</v>
       </c>
@@ -23147,7 +23146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>244</v>
       </c>
@@ -23236,7 +23235,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>245</v>
       </c>
@@ -23325,7 +23324,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>245</v>
       </c>
@@ -23414,7 +23413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>245</v>
       </c>
@@ -23500,7 +23499,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>245</v>
       </c>
@@ -23589,7 +23588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>245</v>
       </c>
@@ -23678,7 +23677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>245</v>
       </c>
@@ -23764,7 +23763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>245</v>
       </c>
@@ -23853,7 +23852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>245</v>
       </c>
@@ -23936,7 +23935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>245</v>
       </c>
@@ -24022,7 +24021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>245</v>
       </c>
@@ -24111,7 +24110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>245</v>
       </c>
@@ -24197,7 +24196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>274</v>
       </c>
@@ -24281,7 +24280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>274</v>
       </c>
@@ -24365,7 +24364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>274</v>
       </c>
@@ -24446,7 +24445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>274</v>
       </c>
@@ -24530,7 +24529,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>274</v>
       </c>
@@ -24614,7 +24613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>274</v>
       </c>
@@ -24695,7 +24694,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>274</v>
       </c>
@@ -24779,7 +24778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>274</v>
       </c>
@@ -24863,7 +24862,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>274</v>
       </c>
@@ -24944,7 +24943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>274</v>
       </c>
@@ -25028,7 +25027,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>274</v>
       </c>
@@ -25112,7 +25111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>274</v>
       </c>
@@ -25193,7 +25192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>274</v>
       </c>
@@ -25282,7 +25281,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>274</v>
       </c>
@@ -25371,7 +25370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>274</v>
       </c>
@@ -25457,7 +25456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -25546,7 +25545,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>274</v>
       </c>
@@ -25635,7 +25634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>274</v>
       </c>
@@ -25721,7 +25720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>274</v>
       </c>
@@ -25810,7 +25809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>274</v>
       </c>
@@ -25899,7 +25898,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>274</v>
       </c>
@@ -25985,7 +25984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>274</v>
       </c>
@@ -26074,7 +26073,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>274</v>
       </c>
@@ -26161,7 +26160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>274</v>
       </c>
@@ -26245,7 +26244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>276</v>
       </c>
@@ -26328,7 +26327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>276</v>
       </c>
@@ -26411,7 +26410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>276</v>
       </c>
@@ -26497,7 +26496,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>276</v>
       </c>
@@ -26580,7 +26579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>276</v>
       </c>
@@ -26663,7 +26662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>276</v>
       </c>
@@ -26749,7 +26748,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>276</v>
       </c>
@@ -26832,7 +26831,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>276</v>
       </c>
@@ -26915,7 +26914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>276</v>
       </c>
@@ -27001,7 +27000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>276</v>
       </c>
@@ -27090,7 +27089,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>276</v>
       </c>
@@ -27176,7 +27175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>277</v>
       </c>
@@ -27256,7 +27255,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>277</v>
       </c>
@@ -27336,7 +27335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>277</v>
       </c>
@@ -27419,7 +27418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>277</v>
       </c>
@@ -27499,7 +27498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>277</v>
       </c>
@@ -27579,7 +27578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>277</v>
       </c>
@@ -27662,7 +27661,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>277</v>
       </c>
@@ -27748,7 +27747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>277</v>
       </c>
@@ -27831,7 +27830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>323</v>
       </c>
@@ -27914,7 +27913,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>323</v>
       </c>
@@ -28000,7 +27999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>323</v>
       </c>
@@ -28083,7 +28082,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>323</v>
       </c>
@@ -28166,7 +28165,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>323</v>
       </c>
@@ -28252,7 +28251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>323</v>
       </c>
@@ -28335,7 +28334,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>323</v>
       </c>
@@ -28412,7 +28411,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>323</v>
       </c>
@@ -28498,7 +28497,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>323</v>
       </c>
@@ -28587,7 +28586,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>323</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>325</v>
       </c>
@@ -28762,7 +28761,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>325</v>
       </c>
@@ -28851,7 +28850,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>325</v>
       </c>
@@ -28937,7 +28936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>325</v>
       </c>
@@ -29026,7 +29025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>325</v>
       </c>
@@ -29103,7 +29102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>325</v>
       </c>
@@ -29189,7 +29188,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>325</v>
       </c>
@@ -29278,7 +29277,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>325</v>
       </c>
@@ -29367,7 +29366,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>325</v>
       </c>
@@ -29453,7 +29452,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>325</v>
       </c>
@@ -29542,7 +29541,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>325</v>
       </c>
@@ -29628,7 +29627,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>331</v>
       </c>
@@ -29711,7 +29710,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>331</v>
       </c>
@@ -29788,7 +29787,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>331</v>
       </c>
@@ -29871,7 +29870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>331</v>
       </c>
@@ -29948,7 +29947,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>331</v>
       </c>
@@ -30028,7 +30027,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>331</v>
       </c>
@@ -30105,7 +30104,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>332</v>
       </c>
@@ -30188,7 +30187,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>332</v>
       </c>
@@ -30271,7 +30270,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>332</v>
       </c>
@@ -30357,7 +30356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -30440,7 +30439,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>332</v>
       </c>
@@ -30523,7 +30522,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>332</v>
       </c>
@@ -30609,7 +30608,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>332</v>
       </c>
@@ -30698,7 +30697,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>332</v>
       </c>
@@ -30781,7 +30780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>332</v>
       </c>
@@ -30867,7 +30866,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>332</v>
       </c>
@@ -30956,7 +30955,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>332</v>
       </c>
@@ -31042,7 +31041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>334</v>
       </c>
@@ -31128,7 +31127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>334</v>
       </c>
@@ -31211,7 +31210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>334</v>
       </c>
@@ -31297,7 +31296,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>334</v>
       </c>
@@ -31380,7 +31379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>334</v>
       </c>
@@ -31466,7 +31465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>334</v>
       </c>
@@ -31555,7 +31554,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>335</v>
       </c>
@@ -31641,7 +31640,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>335</v>
       </c>
@@ -31724,7 +31723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>335</v>
       </c>
@@ -31810,7 +31809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>335</v>
       </c>
@@ -31893,7 +31892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>335</v>
       </c>
@@ -31976,7 +31975,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>339</v>
       </c>
@@ -32067,7 +32066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>339</v>
       </c>
@@ -32155,7 +32154,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>339</v>
       </c>
@@ -32244,7 +32243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>339</v>
       </c>
@@ -32330,7 +32329,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>339</v>
       </c>
@@ -32419,7 +32418,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>339</v>
       </c>
@@ -32505,7 +32504,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>339</v>
       </c>
@@ -32594,7 +32593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>339</v>
       </c>
@@ -32680,7 +32679,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>361</v>
       </c>
@@ -32761,7 +32760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>361</v>
       </c>
@@ -32850,7 +32849,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -32936,7 +32935,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>361</v>
       </c>
@@ -33026,7 +33025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>361</v>
       </c>
@@ -33113,7 +33112,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -33202,7 +33201,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>364</v>
       </c>
@@ -33291,7 +33290,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>364</v>
       </c>
@@ -33368,7 +33367,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>364</v>
       </c>
@@ -33457,7 +33456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>364</v>
       </c>
@@ -33546,7 +33545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>364</v>
       </c>
@@ -33632,7 +33631,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>364</v>
       </c>
@@ -33721,7 +33720,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>364</v>
       </c>
@@ -33807,7 +33806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>367</v>
       </c>
@@ -33893,7 +33892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>367</v>
       </c>
@@ -33982,7 +33981,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>367</v>
       </c>
@@ -34068,7 +34067,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>367</v>
       </c>
@@ -34157,7 +34156,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>367</v>
       </c>
@@ -34243,7 +34242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>367</v>
       </c>
@@ -34326,7 +34325,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>369</v>
       </c>
@@ -34409,7 +34408,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>369</v>
       </c>
@@ -34492,7 +34491,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>369</v>
       </c>
@@ -34569,7 +34568,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>369</v>
       </c>
@@ -34658,7 +34657,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>369</v>
       </c>
@@ -34747,7 +34746,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>369</v>
       </c>
@@ -34833,7 +34832,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>369</v>
       </c>
@@ -34922,7 +34921,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>369</v>
       </c>
@@ -35008,7 +35007,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>376</v>
       </c>
@@ -35098,7 +35097,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>376</v>
       </c>
@@ -35184,7 +35183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>376</v>
       </c>
@@ -35273,7 +35272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>376</v>
       </c>
@@ -35359,7 +35358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>376</v>
       </c>
@@ -35448,7 +35447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>376</v>
       </c>
@@ -35534,7 +35533,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>376</v>
       </c>
@@ -35623,7 +35622,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>376</v>
       </c>
@@ -35709,7 +35708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>377</v>
       </c>
@@ -35798,7 +35797,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>377</v>
       </c>
@@ -35884,7 +35883,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>377</v>
       </c>
@@ -35973,7 +35972,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>377</v>
       </c>
@@ -36059,7 +36058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>377</v>
       </c>
@@ -36139,7 +36138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>379</v>
       </c>
@@ -36223,7 +36222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>379</v>
       </c>
@@ -36304,7 +36303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>379</v>
       </c>
@@ -36388,7 +36387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>379</v>
       </c>
@@ -36472,7 +36471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>379</v>
       </c>
@@ -36556,7 +36555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>379</v>
       </c>
@@ -36637,7 +36636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="406" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>379</v>
       </c>
@@ -36721,7 +36720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="407" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>379</v>
       </c>
@@ -36805,7 +36804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="408" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>379</v>
       </c>
@@ -36886,7 +36885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="409" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>379</v>
       </c>
@@ -36970,7 +36969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="410" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>379</v>
       </c>
@@ -37054,7 +37053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="411" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>379</v>
       </c>
@@ -37135,7 +37134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>379</v>
       </c>
@@ -37224,7 +37223,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>379</v>
       </c>
@@ -37313,7 +37312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>379</v>
       </c>
@@ -37399,7 +37398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>379</v>
       </c>
@@ -37488,7 +37487,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>379</v>
       </c>
@@ -37577,7 +37576,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>379</v>
       </c>
@@ -37663,7 +37662,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>379</v>
       </c>
@@ -37752,7 +37751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>379</v>
       </c>
@@ -37841,7 +37840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>379</v>
       </c>
@@ -37927,7 +37926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>379</v>
       </c>
@@ -38016,7 +38015,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>379</v>
       </c>
@@ -38094,7 +38093,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>379</v>
       </c>
@@ -38178,7 +38177,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="424" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>385</v>
       </c>
@@ -38261,7 +38260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>385</v>
       </c>
@@ -38341,7 +38340,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>385</v>
       </c>
@@ -38424,7 +38423,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>385</v>
       </c>
@@ -38504,7 +38503,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="428" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>385</v>
       </c>
@@ -38587,7 +38586,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="429" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>385</v>
       </c>
@@ -38667,7 +38666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="430" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>385</v>
       </c>
@@ -38742,7 +38741,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="431" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>386.1</v>
       </c>
@@ -38823,7 +38822,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="432" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>386.1</v>
       </c>
@@ -38901,7 +38900,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="433" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>386.1</v>
       </c>
@@ -38981,7 +38980,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="434" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>386.1</v>
       </c>
@@ -39058,7 +39057,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="435" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>386.1</v>
       </c>
@@ -39138,7 +39137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="436" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>386.1</v>
       </c>
@@ -39215,7 +39214,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="437" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>386.1</v>
       </c>
@@ -39290,7 +39289,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>386.2</v>
       </c>
@@ -39372,7 +39371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>386.2</v>
       </c>
@@ -39451,7 +39450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>386.2</v>
       </c>
@@ -39531,7 +39530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>386.2</v>
       </c>
@@ -39608,7 +39607,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="442" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>386.2</v>
       </c>
@@ -39688,7 +39687,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="443" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>386.2</v>
       </c>
@@ -39765,7 +39764,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="444" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>386.2</v>
       </c>
@@ -39840,7 +39839,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="445" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>386.2</v>
       </c>
@@ -39912,7 +39911,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="446" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>386.3</v>
       </c>
@@ -39993,7 +39992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="447" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>386.3</v>
       </c>
@@ -40071,7 +40070,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="448" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>386.3</v>
       </c>
@@ -40152,7 +40151,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="449" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>386.3</v>
       </c>
@@ -40230,7 +40229,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="450" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>386.3</v>
       </c>
@@ -40310,7 +40309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="451" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>386.3</v>
       </c>
@@ -40387,7 +40386,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="452" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>386.3</v>
       </c>
@@ -40462,7 +40461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>386.3</v>
       </c>
@@ -40534,7 +40533,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>423</v>
       </c>
@@ -40617,7 +40616,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="455" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>423</v>
       </c>
@@ -40703,7 +40702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="456" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>423</v>
       </c>
@@ -40786,7 +40785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="457" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>423</v>
       </c>
@@ -40872,7 +40871,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="458" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>423</v>
       </c>
@@ -40955,7 +40954,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>423</v>
       </c>
@@ -41041,7 +41040,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="460" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>423</v>
       </c>
@@ -41124,7 +41123,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>424</v>
       </c>
@@ -41207,7 +41206,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="462" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>424</v>
       </c>
@@ -41293,7 +41292,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="463" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>424</v>
       </c>
@@ -41376,7 +41375,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="464" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>424</v>
       </c>
@@ -41462,7 +41461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="465" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>424</v>
       </c>
@@ -41545,7 +41544,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="466" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>424</v>
       </c>
@@ -41631,7 +41630,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="467" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>424</v>
       </c>
@@ -41714,7 +41713,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="468" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>460</v>
       </c>
@@ -41791,7 +41790,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="469" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>460</v>
       </c>
@@ -41880,7 +41879,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="470" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>460</v>
       </c>
@@ -41960,7 +41959,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>460</v>
       </c>
@@ -42046,7 +42045,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>460</v>
       </c>
@@ -42132,7 +42131,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>466</v>
       </c>
@@ -42221,7 +42220,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>466</v>
       </c>
@@ -42310,7 +42309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>466</v>
       </c>
@@ -42396,7 +42395,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>466</v>
       </c>
@@ -42482,7 +42481,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="477" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>466</v>
       </c>
@@ -42571,7 +42570,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>466</v>
       </c>
@@ -42657,7 +42656,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="479" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>466</v>
       </c>
@@ -42746,7 +42745,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="480" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>466</v>
       </c>
@@ -42836,7 +42835,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>203</v>
       </c>
@@ -42920,7 +42919,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="482" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>203</v>
       </c>
@@ -43001,7 +43000,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>148</v>
       </c>
@@ -43090,7 +43089,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="484" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>466</v>
       </c>
@@ -43177,7 +43176,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="485" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>109</v>
       </c>
@@ -43264,7 +43263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>386.1</v>
       </c>
@@ -43336,7 +43335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="487" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>385</v>
       </c>
@@ -43408,7 +43407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="488" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>423</v>
       </c>
@@ -43488,7 +43487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="489" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>424</v>
       </c>
@@ -43568,7 +43567,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="490" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>377</v>
       </c>
@@ -43645,7 +43644,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="491" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>367</v>
       </c>
@@ -43725,7 +43724,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>244</v>
       </c>
@@ -43811,7 +43810,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="493" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>334</v>
       </c>
@@ -43897,7 +43896,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="494" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>96</v>
       </c>
@@ -43975,18 +43974,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC494" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Lanzamiento de nuevos programas virtual"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AC494" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC480">
     <sortCondition ref="A2:A480"/>
     <sortCondition ref="F2:F480"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1360" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC546522-844A-44C1-BD9F-2B317E16A401}"/>
+  <xr:revisionPtr revIDLastSave="1367" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEAB8B40-8F77-4468-864B-6EFE92D92A01}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43974,7 +43974,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC494" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC480">
     <sortCondition ref="A2:A480"/>
     <sortCondition ref="F2:F480"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Indicadores/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1367" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEAB8B40-8F77-4468-864B-6EFE92D92A01}"/>
+  <xr:revisionPtr revIDLastSave="1370" documentId="11_C54DB9D477E07092D1C9E253F65DD242EE9209D1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC4E1B31-F2FA-4057-9F79-BA07D36222A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB13218-3AF6-4A56-AB91-C59000667156}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34F4CC89-DCD1-43E7-889A-30452BB6AE13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44837,15 +44837,15 @@
         <v>739</v>
       </c>
       <c r="L492">
-        <v>159</v>
+        <v>739</v>
       </c>
       <c r="M492">
         <f>+L492/K492</f>
-        <v>0.21515561569688768</v>
+        <v>1</v>
       </c>
       <c r="N492">
         <f>+L492/K492</f>
-        <v>0.21515561569688768</v>
+        <v>1</v>
       </c>
       <c r="O492" t="s">
         <v>35</v>
@@ -44925,15 +44925,15 @@
         <v>739</v>
       </c>
       <c r="L493">
-        <v>159</v>
+        <v>739</v>
       </c>
       <c r="M493">
         <f>+L493/K493</f>
-        <v>0.21515561569688768</v>
+        <v>1</v>
       </c>
       <c r="N493">
         <f>+L493/K493</f>
-        <v>0.21515561569688768</v>
+        <v>1</v>
       </c>
       <c r="O493" t="s">
         <v>35</v>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="446" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38C7AD91-46F2-4337-B350-9143CE8B224B}"/>
+  <xr:revisionPtr revIDLastSave="457" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7DB59C-6878-490F-97EA-2D84D70CF822}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21070,7 +21070,7 @@
         <v>148</v>
       </c>
       <c r="AB215" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC215" s="3" t="s">
         <v>66</v>
@@ -21153,7 +21153,7 @@
         <v>148</v>
       </c>
       <c r="AB216" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC216" s="3" t="s">
         <v>66</v>
@@ -21244,7 +21244,7 @@
         <v>148</v>
       </c>
       <c r="AB217" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC217" s="3" t="s">
         <v>66</v>
@@ -21333,7 +21333,7 @@
         <v>148</v>
       </c>
       <c r="AB218" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC218" s="3" t="s">
         <v>66</v>
@@ -21424,7 +21424,7 @@
         <v>148</v>
       </c>
       <c r="AB219" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC219" s="3" t="s">
         <v>66</v>
@@ -21513,7 +21513,7 @@
         <v>148</v>
       </c>
       <c r="AB220" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC220" s="3" t="s">
         <v>66</v>
@@ -21606,7 +21606,7 @@
         <v>148</v>
       </c>
       <c r="AB221" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC221" s="3" t="s">
         <v>66</v>
@@ -46718,13 +46718,14 @@
         <v>148</v>
       </c>
       <c r="AB503" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="AC503" s="3" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC503" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC469">
     <sortCondition ref="A2:A469"/>
     <sortCondition ref="F2:F469"/>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Prospectiva/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="457" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7DB59C-6878-490F-97EA-2D84D70CF822}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9785E104-D4CE-4036-A871-490B49092295}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14264" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14424" uniqueCount="530">
   <si>
     <t>Id</t>
   </si>
@@ -1613,6 +1613,24 @@
   <si>
     <t>205-2025-12-31</t>
   </si>
+  <si>
+    <t>Prov-1</t>
+  </si>
+  <si>
+    <t>Total Programas</t>
+  </si>
+  <si>
+    <t>Prov-1-2022-12-31</t>
+  </si>
+  <si>
+    <t>Prov-1-2023-12-31</t>
+  </si>
+  <si>
+    <t>Prov-1-2024-12-31</t>
+  </si>
+  <si>
+    <t>Prov-1-20225-12-31</t>
+  </si>
 </sst>
 </file>
 
@@ -1701,7 +1719,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1712,6 +1730,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{2B248724-A66E-415B-8BBA-BBCDE8553B51}"/>
@@ -2017,7 +2036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC503"/>
+  <dimension ref="A1:AC511"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -46721,6 +46740,694 @@
         <v>43</v>
       </c>
       <c r="AC503" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="504" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A504" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B504" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D504" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E504" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F504" s="5">
+        <v>44926</v>
+      </c>
+      <c r="G504" s="3">
+        <v>2022</v>
+      </c>
+      <c r="H504" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I504" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J504" s="3">
+        <v>2</v>
+      </c>
+      <c r="K504" s="3"/>
+      <c r="L504" s="8">
+        <v>98</v>
+      </c>
+      <c r="M504" s="3">
+        <v>1</v>
+      </c>
+      <c r="N504" s="3">
+        <v>1</v>
+      </c>
+      <c r="O504" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P504" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q504" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="R504" s="3">
+        <v>0</v>
+      </c>
+      <c r="S504" s="3">
+        <v>0</v>
+      </c>
+      <c r="T504" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U504" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V504" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W504" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X504" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y504" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z504" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA504" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB504" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC504" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="505" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A505" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B505" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D505" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E505" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F505" s="5">
+        <v>45291</v>
+      </c>
+      <c r="G505" s="3">
+        <v>2023</v>
+      </c>
+      <c r="H505" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I505" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J505" s="3">
+        <v>2</v>
+      </c>
+      <c r="K505" s="3"/>
+      <c r="L505" s="8">
+        <v>92</v>
+      </c>
+      <c r="M505" s="3">
+        <v>1</v>
+      </c>
+      <c r="N505" s="3">
+        <v>1</v>
+      </c>
+      <c r="O505" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P505" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q505" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="R505" s="3">
+        <v>0</v>
+      </c>
+      <c r="S505" s="3">
+        <v>0</v>
+      </c>
+      <c r="T505" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U505" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V505" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W505" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X505" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y505" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z505" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA505" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB505" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC505" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="506" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A506" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B506" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D506" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E506" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F506" s="5">
+        <v>45657</v>
+      </c>
+      <c r="G506" s="3">
+        <v>2024</v>
+      </c>
+      <c r="H506" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I506" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J506" s="3">
+        <v>2</v>
+      </c>
+      <c r="K506" s="3"/>
+      <c r="L506" s="8">
+        <v>95</v>
+      </c>
+      <c r="M506" s="3">
+        <v>1</v>
+      </c>
+      <c r="N506" s="3">
+        <v>1</v>
+      </c>
+      <c r="O506" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P506" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q506" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="R506" s="3">
+        <v>0</v>
+      </c>
+      <c r="S506" s="3">
+        <v>0</v>
+      </c>
+      <c r="T506" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U506" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V506" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W506" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X506" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y506" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z506" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA506" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB506" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC506" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="507" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A507" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B507" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D507" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E507" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F507" s="5">
+        <v>46022</v>
+      </c>
+      <c r="G507" s="3">
+        <v>2025</v>
+      </c>
+      <c r="H507" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I507" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J507" s="3">
+        <v>2</v>
+      </c>
+      <c r="K507" s="3"/>
+      <c r="L507" s="8">
+        <v>104</v>
+      </c>
+      <c r="M507" s="3">
+        <v>1</v>
+      </c>
+      <c r="N507" s="3">
+        <v>1</v>
+      </c>
+      <c r="O507" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P507" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q507" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="R507" s="3">
+        <v>0</v>
+      </c>
+      <c r="S507" s="3">
+        <v>0</v>
+      </c>
+      <c r="T507" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U507" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V507" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W507" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X507" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y507" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z507" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA507" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB507" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC507" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="508" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A508" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B508" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D508" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E508" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F508" s="5">
+        <v>44926</v>
+      </c>
+      <c r="G508" s="3">
+        <v>2022</v>
+      </c>
+      <c r="H508" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I508" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J508" s="3"/>
+      <c r="K508" s="3"/>
+      <c r="L508" s="8">
+        <v>98</v>
+      </c>
+      <c r="M508" s="3">
+        <v>1</v>
+      </c>
+      <c r="N508" s="3">
+        <v>1</v>
+      </c>
+      <c r="O508" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P508" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q508" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="R508" s="3">
+        <v>0</v>
+      </c>
+      <c r="S508" s="3">
+        <v>0</v>
+      </c>
+      <c r="T508" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="U508" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V508" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W508" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X508" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y508" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z508" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA508" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB508" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC508" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="509" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A509" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B509" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D509" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E509" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F509" s="5">
+        <v>45291</v>
+      </c>
+      <c r="G509" s="3">
+        <v>2023</v>
+      </c>
+      <c r="H509" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I509" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J509" s="3"/>
+      <c r="K509" s="3"/>
+      <c r="L509" s="8">
+        <v>92</v>
+      </c>
+      <c r="M509" s="3">
+        <v>1</v>
+      </c>
+      <c r="N509" s="3">
+        <v>1</v>
+      </c>
+      <c r="O509" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P509" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q509" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="R509" s="3">
+        <v>0</v>
+      </c>
+      <c r="S509" s="3">
+        <v>0</v>
+      </c>
+      <c r="T509" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="U509" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V509" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W509" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X509" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y509" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z509" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA509" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB509" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC509" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="510" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A510" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B510" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C510" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D510" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E510" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F510" s="5">
+        <v>45657</v>
+      </c>
+      <c r="G510" s="3">
+        <v>2024</v>
+      </c>
+      <c r="H510" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I510" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J510" s="3"/>
+      <c r="K510" s="3"/>
+      <c r="L510" s="8">
+        <v>95</v>
+      </c>
+      <c r="M510" s="3">
+        <v>1</v>
+      </c>
+      <c r="N510" s="3">
+        <v>1</v>
+      </c>
+      <c r="O510" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P510" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q510" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="R510" s="3">
+        <v>0</v>
+      </c>
+      <c r="S510" s="3">
+        <v>0</v>
+      </c>
+      <c r="T510" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="U510" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V510" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W510" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X510" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y510" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z510" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA510" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB510" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC510" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="511" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A511" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B511" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D511" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E511" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F511" s="5">
+        <v>46022</v>
+      </c>
+      <c r="G511" s="3">
+        <v>2025</v>
+      </c>
+      <c r="H511" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I511" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J511" s="3"/>
+      <c r="K511" s="3"/>
+      <c r="L511" s="8">
+        <v>104</v>
+      </c>
+      <c r="M511" s="3">
+        <v>1</v>
+      </c>
+      <c r="N511" s="3">
+        <v>1</v>
+      </c>
+      <c r="O511" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P511" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q511" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="R511" s="3">
+        <v>0</v>
+      </c>
+      <c r="S511" s="3">
+        <v>0</v>
+      </c>
+      <c r="T511" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="U511" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V511" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="W511" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="X511" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y511" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z511" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA511" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB511" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC511" s="3" t="s">
         <v>66</v>
       </c>
     </row>

--- a/Data/Dataset_Unificado.xlsx
+++ b/Data/Dataset_Unificado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Imágenes/Proyectos/Modelo_Prospectivo/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87619B33-ACE9-4934-8C47-9C90E5CDF4BA}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="13_ncr:1_{1F4801C9-ED16-400C-AD37-A33B0E67B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF33899-46E3-4C9F-A751-684D70FAA38C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2014,6 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC508"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2118,7 +2119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>14</v>
       </c>
@@ -2204,7 +2205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>14</v>
       </c>
@@ -2290,7 +2291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>14</v>
       </c>
@@ -2375,7 +2376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>14</v>
       </c>
@@ -2462,7 +2463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>14</v>
       </c>
@@ -2549,7 +2550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>14</v>
       </c>
@@ -2634,7 +2635,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>14</v>
       </c>
@@ -2721,7 +2722,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>14</v>
       </c>
@@ -2808,7 +2809,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>14</v>
       </c>
@@ -2893,7 +2894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>14</v>
       </c>
@@ -2980,7 +2981,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>14</v>
       </c>
@@ -3067,7 +3068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>14</v>
       </c>
@@ -3152,7 +3153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>14</v>
       </c>
@@ -3241,7 +3242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3330,7 +3331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3417,7 +3418,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3506,7 +3507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>14</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>14</v>
       </c>
@@ -3682,7 +3683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>14</v>
       </c>
@@ -3771,7 +3772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>14</v>
       </c>
@@ -3947,7 +3948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>14</v>
       </c>
@@ -4036,7 +4037,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>14</v>
       </c>
@@ -4216,7 +4217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>14.1</v>
       </c>
@@ -4303,7 +4304,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>14.1</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>14.1</v>
       </c>
@@ -4475,7 +4476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>14.1</v>
       </c>
@@ -4562,7 +4563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>14.1</v>
       </c>
@@ -4649,7 +4650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>14.1</v>
       </c>
@@ -4734,7 +4735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>14.1</v>
       </c>
@@ -4821,7 +4822,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>14.1</v>
       </c>
@@ -4908,7 +4909,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>14.1</v>
       </c>
@@ -4993,7 +4994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>14.1</v>
       </c>
@@ -5080,7 +5081,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>14.1</v>
       </c>
@@ -5167,7 +5168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>14.1</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>14.1</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>14.1</v>
       </c>
@@ -5434,7 +5435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>14.1</v>
       </c>
@@ -5523,7 +5524,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>14.1</v>
       </c>
@@ -5614,7 +5615,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>14.1</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>14.1</v>
       </c>
@@ -5794,7 +5795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>14.1</v>
       </c>
@@ -5885,7 +5886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>14.1</v>
       </c>
@@ -5976,7 +5977,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>14.1</v>
       </c>
@@ -6065,7 +6066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>14.1</v>
       </c>
@@ -6156,7 +6157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>14.1</v>
       </c>
@@ -6247,7 +6248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>14.1</v>
       </c>
@@ -6336,7 +6337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>14.2</v>
       </c>
@@ -6423,7 +6424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>14.2</v>
       </c>
@@ -6510,7 +6511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>14.2</v>
       </c>
@@ -6595,7 +6596,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>14.2</v>
       </c>
@@ -6682,7 +6683,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>14.2</v>
       </c>
@@ -6769,7 +6770,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>14.2</v>
       </c>
@@ -6854,7 +6855,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>14.2</v>
       </c>
@@ -6941,7 +6942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>14.2</v>
       </c>
@@ -7028,7 +7029,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>14.2</v>
       </c>
@@ -7113,7 +7114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>14.2</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>14.2</v>
       </c>
@@ -7287,7 +7288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>14.2</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>14.2</v>
       </c>
@@ -7463,7 +7464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>14.2</v>
       </c>
@@ -7554,7 +7555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>14.2</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>14.2</v>
       </c>
@@ -7734,7 +7735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>14.2</v>
       </c>
@@ -7825,7 +7826,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>14.2</v>
       </c>
@@ -7914,7 +7915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>14.2</v>
       </c>
@@ -8005,7 +8006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>14.2</v>
       </c>
@@ -8096,7 +8097,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>14.2</v>
       </c>
@@ -8185,7 +8186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>14.2</v>
       </c>
@@ -8276,7 +8277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>14.2</v>
       </c>
@@ -8367,7 +8368,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>14.2</v>
       </c>
@@ -8456,7 +8457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>14.3</v>
       </c>
@@ -8543,7 +8544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>14.3</v>
       </c>
@@ -8630,7 +8631,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>14.3</v>
       </c>
@@ -8715,7 +8716,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>14.3</v>
       </c>
@@ -8802,7 +8803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>14.3</v>
       </c>
@@ -8889,7 +8890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>14.3</v>
       </c>
@@ -8974,7 +8975,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>14.3</v>
       </c>
@@ -9061,7 +9062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>14.3</v>
       </c>
@@ -9148,7 +9149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>14.3</v>
       </c>
@@ -9233,7 +9234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>14.3</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>14.3</v>
       </c>
@@ -9407,7 +9408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>14.3</v>
       </c>
@@ -9492,7 +9493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>14.3</v>
       </c>
@@ -9583,7 +9584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>14.3</v>
       </c>
@@ -9674,7 +9675,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>14.3</v>
       </c>
@@ -9763,7 +9764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>14.3</v>
       </c>
@@ -9854,7 +9855,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>14.3</v>
       </c>
@@ -9945,7 +9946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>14.3</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>14.3</v>
       </c>
@@ -10125,7 +10126,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>14.3</v>
       </c>
@@ -10216,7 +10217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>14.3</v>
       </c>
@@ -10305,7 +10306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>14.3</v>
       </c>
@@ -10396,7 +10397,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>14.3</v>
       </c>
@@ -10487,7 +10488,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>14.3</v>
       </c>
@@ -10576,7 +10577,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>14.4</v>
       </c>
@@ -10663,7 +10664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>14.4</v>
       </c>
@@ -10750,7 +10751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>14.4</v>
       </c>
@@ -10835,7 +10836,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>14.4</v>
       </c>
@@ -10922,7 +10923,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>14.4</v>
       </c>
@@ -11009,7 +11010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>14.4</v>
       </c>
@@ -11094,7 +11095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>14.4</v>
       </c>
@@ -11181,7 +11182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>14.4</v>
       </c>
@@ -11268,7 +11269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>14.4</v>
       </c>
@@ -11353,7 +11354,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>14.4</v>
       </c>
@@ -11440,7 +11441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>14.4</v>
       </c>
@@ -11527,7 +11528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>14.4</v>
       </c>
@@ -11612,7 +11613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>14.4</v>
       </c>
@@ -11703,7 +11704,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>14.4</v>
       </c>
@@ -11794,7 +11795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>14.4</v>
       </c>
@@ -11883,7 +11884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>14.4</v>
       </c>
@@ -11974,7 +11975,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>14.4</v>
       </c>
@@ -12065,7 +12066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>14.4</v>
       </c>
@@ -12154,7 +12155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>14.4</v>
       </c>
@@ -12245,7 +12246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>14.4</v>
       </c>
@@ -12336,7 +12337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>14.4</v>
       </c>
@@ -12425,7 +12426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>14.4</v>
       </c>
@@ -12516,7 +12517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>14.4</v>
       </c>
@@ -12607,7 +12608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>14.4</v>
       </c>
@@ -12696,7 +12697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>77</v>
       </c>
@@ -12785,7 +12786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>77</v>
       </c>
@@ -12874,7 +12875,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>77</v>
       </c>
@@ -12961,7 +12962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>77</v>
       </c>
@@ -13050,7 +13051,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>77</v>
       </c>
@@ -13139,7 +13140,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>77</v>
       </c>
@@ -13226,7 +13227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>77</v>
       </c>
@@ -13317,7 +13318,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>77</v>
       </c>
@@ -13408,7 +13409,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>77</v>
       </c>
@@ -13497,7 +13498,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>77</v>
       </c>
@@ -13588,7 +13589,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>77</v>
       </c>
@@ -13679,7 +13680,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>96</v>
       </c>
@@ -13768,7 +13769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>96</v>
       </c>
@@ -13855,7 +13856,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>96</v>
       </c>
@@ -13946,7 +13947,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>96</v>
       </c>
@@ -14035,7 +14036,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>96</v>
       </c>
@@ -14126,7 +14127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>96</v>
       </c>
@@ -14215,7 +14216,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>98</v>
       </c>
@@ -14300,7 +14301,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>98</v>
       </c>
@@ -14389,7 +14390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>98</v>
       </c>
@@ -14476,7 +14477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>98</v>
       </c>
@@ -14561,7 +14562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>98</v>
       </c>
@@ -14650,7 +14651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>98</v>
       </c>
@@ -14737,7 +14738,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>98</v>
       </c>
@@ -14818,7 +14819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>98</v>
       </c>
@@ -14909,7 +14910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>98</v>
       </c>
@@ -14998,7 +14999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>98</v>
       </c>
@@ -15089,7 +15090,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>98</v>
       </c>
@@ -15180,7 +15181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>109</v>
       </c>
@@ -15267,7 +15268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>109</v>
       </c>
@@ -15352,7 +15353,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>109</v>
       </c>
@@ -15439,7 +15440,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>109</v>
       </c>
@@ -15524,7 +15525,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>148</v>
       </c>
@@ -15613,7 +15614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>148</v>
       </c>
@@ -15704,7 +15705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>148</v>
       </c>
@@ -15795,7 +15796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>148</v>
       </c>
@@ -15884,7 +15885,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>148</v>
       </c>
@@ -15975,7 +15976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>148</v>
       </c>
@@ -16066,7 +16067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>148</v>
       </c>
@@ -16155,7 +16156,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>148</v>
       </c>
@@ -16246,7 +16247,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>148</v>
       </c>
@@ -16337,7 +16338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>193</v>
       </c>
@@ -16428,7 +16429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>193</v>
       </c>
@@ -16519,7 +16520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>193</v>
       </c>
@@ -16608,7 +16609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>193</v>
       </c>
@@ -16699,7 +16700,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>193</v>
       </c>
@@ -16790,7 +16791,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>193</v>
       </c>
@@ -16879,7 +16880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>193</v>
       </c>
@@ -16970,7 +16971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>193</v>
       </c>
@@ -17061,7 +17062,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>193</v>
       </c>
@@ -17150,7 +17151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>193</v>
       </c>
@@ -17241,7 +17242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>193</v>
       </c>
@@ -17332,7 +17333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>194</v>
       </c>
@@ -17423,7 +17424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>194</v>
       </c>
@@ -17514,7 +17515,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>194</v>
       </c>
@@ -17603,7 +17604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>194</v>
       </c>
@@ -17694,7 +17695,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>194</v>
       </c>
@@ -17785,7 +17786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>194</v>
       </c>
@@ -17874,7 +17875,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>194</v>
       </c>
@@ -17965,7 +17966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>194</v>
       </c>
@@ -18056,7 +18057,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>194</v>
       </c>
@@ -18145,7 +18146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>194</v>
       </c>
@@ -18236,7 +18237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>194</v>
       </c>
@@ -18327,7 +18328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>200</v>
       </c>
@@ -18410,7 +18411,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>200</v>
       </c>
@@ -18491,7 +18492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>200</v>
       </c>
@@ -18582,7 +18583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>200</v>
       </c>
@@ -18671,7 +18672,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>202</v>
       </c>
@@ -18756,7 +18757,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>202</v>
       </c>
@@ -18843,7 +18844,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>202</v>
       </c>
@@ -18930,7 +18931,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>202</v>
       </c>
@@ -19015,7 +19016,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>202</v>
       </c>
@@ -19102,7 +19103,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>202</v>
       </c>
@@ -19187,7 +19188,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>202</v>
       </c>
@@ -19278,7 +19279,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>202</v>
       </c>
@@ -19367,7 +19368,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>202</v>
       </c>
@@ -19458,7 +19459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>202</v>
       </c>
@@ -19547,7 +19548,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>203</v>
       </c>
@@ -19638,7 +19639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>203</v>
       </c>
@@ -19729,7 +19730,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>203</v>
       </c>
@@ -19818,7 +19819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>203</v>
       </c>
@@ -19909,7 +19910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>203</v>
       </c>
@@ -20000,7 +20001,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -20089,7 +20090,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>203</v>
       </c>
@@ -20180,7 +20181,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -20271,7 +20272,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>203</v>
       </c>
@@ -20360,7 +20361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>203</v>
       </c>
@@ -20451,7 +20452,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>204</v>
       </c>
@@ -20541,7 +20542,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>204</v>
       </c>
@@ -20628,7 +20629,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>204</v>
       </c>
@@ -20718,7 +20719,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>204</v>
       </c>
@@ -20806,7 +20807,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>204</v>
       </c>
@@ -20898,7 +20899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>204</v>
       </c>
@@ -21880,7 +21881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>207</v>
       </c>
@@ -21971,7 +21972,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>207</v>
       </c>
@@ -22062,7 +22063,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>207</v>
       </c>
@@ -22151,7 +22152,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>207</v>
       </c>
@@ -22242,7 +22243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>207</v>
       </c>
@@ -22333,7 +22334,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>207</v>
       </c>
@@ -22422,7 +22423,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>207</v>
       </c>
@@ -22513,7 +22514,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>207</v>
       </c>
@@ -22605,7 +22606,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>228</v>
       </c>
@@ -22696,7 +22697,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>228</v>
       </c>
@@ -22785,7 +22786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>228</v>
       </c>
@@ -22876,7 +22877,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>228</v>
       </c>
@@ -22965,7 +22966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>228</v>
       </c>
@@ -23056,7 +23057,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>228</v>
       </c>
@@ -23145,7 +23146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>244</v>
       </c>
@@ -23236,7 +23237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>244</v>
       </c>
@@ -23325,7 +23326,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>244</v>
       </c>
@@ -23416,7 +23417,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>244</v>
       </c>
@@ -23505,7 +23506,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>244</v>
       </c>
@@ -23596,7 +23597,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>244</v>
       </c>
@@ -23685,7 +23686,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -23776,7 +23777,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -23867,7 +23868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>245</v>
       </c>
@@ -23958,7 +23959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -24047,7 +24048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>245</v>
       </c>
@@ -24138,7 +24139,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>245</v>
       </c>
@@ -24229,7 +24230,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>245</v>
       </c>
@@ -24318,7 +24319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>245</v>
       </c>
@@ -24409,7 +24410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>245</v>
       </c>
@@ -24500,7 +24501,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>245</v>
       </c>
@@ -24589,7 +24590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>245</v>
       </c>
@@ -24680,7 +24681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>245</v>
       </c>
@@ -24771,7 +24772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>274</v>
       </c>
@@ -24858,7 +24859,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>274</v>
       </c>
@@ -24945,7 +24946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>274</v>
       </c>
@@ -25030,7 +25031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>274</v>
       </c>
@@ -25117,7 +25118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>274</v>
       </c>
@@ -25204,7 +25205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>274</v>
       </c>
@@ -25289,7 +25290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>274</v>
       </c>
@@ -25376,7 +25377,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>274</v>
       </c>
@@ -25463,7 +25464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>274</v>
       </c>
@@ -25548,7 +25549,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>274</v>
       </c>
@@ -25635,7 +25636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>274</v>
       </c>
@@ -25722,7 +25723,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>274</v>
       </c>
@@ -25807,7 +25808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>274</v>
       </c>
@@ -25898,7 +25899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>274</v>
       </c>
@@ -25989,7 +25990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>274</v>
       </c>
@@ -26078,7 +26079,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>274</v>
       </c>
@@ -26169,7 +26170,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>274</v>
       </c>
@@ -26260,7 +26261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>274</v>
       </c>
@@ -26349,7 +26350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>274</v>
       </c>
@@ -26440,7 +26441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>274</v>
       </c>
@@ -26531,7 +26532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -26620,7 +26621,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>274</v>
       </c>
@@ -26711,7 +26712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>274</v>
       </c>
@@ -26803,7 +26804,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>274</v>
       </c>
@@ -26896,7 +26897,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>276</v>
       </c>
@@ -26987,7 +26988,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>276</v>
       </c>
@@ -27078,7 +27079,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>276</v>
       </c>
@@ -27167,7 +27168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>276</v>
       </c>
@@ -27258,7 +27259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>276</v>
       </c>
@@ -27349,7 +27350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>276</v>
       </c>
@@ -27438,7 +27439,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>276</v>
       </c>
@@ -27529,7 +27530,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>276</v>
       </c>
@@ -27620,7 +27621,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>276</v>
       </c>
@@ -27709,7 +27710,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>276</v>
       </c>
@@ -27800,7 +27801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>276</v>
       </c>
@@ -27891,7 +27892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>277</v>
       </c>
@@ -27980,7 +27981,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>277</v>
       </c>
@@ -28069,7 +28070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>277</v>
       </c>
@@ -28156,7 +28157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>277</v>
       </c>
@@ -28245,7 +28246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>277</v>
       </c>
@@ -28334,7 +28335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>277</v>
       </c>
@@ -28421,7 +28422,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>277</v>
       </c>
@@ -28510,7 +28511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>277</v>
       </c>
@@ -28599,7 +28600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>323</v>
       </c>
@@ -28684,7 +28685,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>323</v>
       </c>
@@ -28771,7 +28772,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="302" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>323</v>
       </c>
@@ -28856,7 +28857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>323</v>
       </c>
@@ -28941,7 +28942,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="304" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>323</v>
       </c>
@@ -29028,7 +29029,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="305" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>323</v>
       </c>
@@ -29113,7 +29114,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="306" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>323</v>
       </c>
@@ -29194,7 +29195,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="307" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>323</v>
       </c>
@@ -29281,7 +29282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="308" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>323</v>
       </c>
@@ -29370,7 +29371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="309" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>323</v>
       </c>
@@ -29459,7 +29460,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>325</v>
       </c>
@@ -29548,7 +29549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="311" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>325</v>
       </c>
@@ -29637,7 +29638,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="312" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>325</v>
       </c>
@@ -29724,7 +29725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="313" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>325</v>
       </c>
@@ -29813,7 +29814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="314" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>325</v>
       </c>
@@ -29894,7 +29895,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="315" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>325</v>
       </c>
@@ -29981,7 +29982,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="316" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>325</v>
       </c>
@@ -30070,7 +30071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="317" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>325</v>
       </c>
@@ -30159,7 +30160,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="318" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>325</v>
       </c>
@@ -30246,7 +30247,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="319" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>325</v>
       </c>
@@ -30335,7 +30336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="320" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>325</v>
       </c>
@@ -30424,7 +30425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="321" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>331</v>
       </c>
@@ -30509,7 +30510,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="322" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>331</v>
       </c>
@@ -30590,7 +30591,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="323" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>331</v>
       </c>
@@ -30675,7 +30676,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="324" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>331</v>
       </c>
@@ -30756,7 +30757,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="325" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>331</v>
       </c>
@@ -30841,7 +30842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="326" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>332</v>
       </c>
@@ -30931,7 +30932,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="327" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>332</v>
       </c>
@@ -31021,7 +31022,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="328" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>332</v>
       </c>
@@ -31109,7 +31110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="329" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>332</v>
       </c>
@@ -31199,7 +31200,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="330" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>332</v>
       </c>
@@ -31290,7 +31291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="331" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>332</v>
       </c>
@@ -31379,7 +31380,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="332" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>332</v>
       </c>
@@ -31470,7 +31471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="333" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>332</v>
       </c>
@@ -31561,7 +31562,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="334" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>332</v>
       </c>
@@ -31650,7 +31651,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="335" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>332</v>
       </c>
@@ -31741,7 +31742,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>332</v>
       </c>
@@ -31832,7 +31833,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="337" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>332</v>
       </c>
@@ -31921,7 +31922,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="338" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>334</v>
       </c>
@@ -32010,7 +32011,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="339" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>334</v>
       </c>
@@ -32101,7 +32102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="340" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>334</v>
       </c>
@@ -32190,7 +32191,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="341" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>334</v>
       </c>
@@ -32281,7 +32282,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="342" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>334</v>
       </c>
@@ -32370,7 +32371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="343" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>334</v>
       </c>
@@ -32461,7 +32462,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="344" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>335</v>
       </c>
@@ -32548,7 +32549,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="345" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>335</v>
       </c>
@@ -32633,7 +32634,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="346" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>335</v>
       </c>
@@ -32720,7 +32721,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="347" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>335</v>
       </c>
@@ -32805,7 +32806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="348" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>335</v>
       </c>
@@ -32890,7 +32891,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="349" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>339</v>
       </c>
@@ -32981,7 +32982,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="350" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>339</v>
       </c>
@@ -33070,7 +33071,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="351" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>339</v>
       </c>
@@ -33161,7 +33162,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="352" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>339</v>
       </c>
@@ -33250,7 +33251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="353" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>339</v>
       </c>
@@ -33341,7 +33342,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="354" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>339</v>
       </c>
@@ -33430,7 +33431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="355" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>339</v>
       </c>
@@ -33521,7 +33522,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="356" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>339</v>
       </c>
@@ -33610,7 +33611,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="357" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>361</v>
       </c>
@@ -33695,7 +33696,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="358" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>361</v>
       </c>
@@ -33784,7 +33785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="359" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>361</v>
       </c>
@@ -33871,7 +33872,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="360" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>361</v>
       </c>
@@ -33961,7 +33962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="361" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>361</v>
       </c>
@@ -34049,7 +34050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="362" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>364</v>
       </c>
@@ -34132,7 +34133,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="363" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>364</v>
       </c>
@@ -34215,7 +34216,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="364" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>364</v>
       </c>
@@ -34296,7 +34297,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="365" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -34387,7 +34388,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="366" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>364</v>
       </c>
@@ -34478,7 +34479,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="367" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>364</v>
       </c>
@@ -34567,7 +34568,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="368" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>364</v>
       </c>
@@ -34658,7 +34659,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="369" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>364</v>
       </c>
@@ -34749,7 +34750,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="370" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>367</v>
       </c>
@@ -34838,7 +34839,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="371" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>367</v>
       </c>
@@ -34929,7 +34930,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="372" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>367</v>
       </c>
@@ -35018,7 +35019,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="373" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>367</v>
       </c>
@@ -35109,7 +35110,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="374" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>367</v>
       </c>
@@ -35198,7 +35199,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="375" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>367</v>
       </c>
@@ -35289,7 +35290,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="376" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>369</v>
       </c>
@@ -35372,7 +35373,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="377" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>369</v>
       </c>
@@ -35455,7 +35456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="378" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>369</v>
       </c>
@@ -35536,7 +35537,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="379" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>369</v>
       </c>
@@ -35627,7 +35628,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="380" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>369</v>
       </c>
@@ -35718,7 +35719,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="381" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>369</v>
       </c>
@@ -35807,7 +35808,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="382" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>369</v>
       </c>
@@ -35898,7 +35899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="383" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>369</v>
       </c>
@@ -35991,7 +35992,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="384" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>376</v>
       </c>
@@ -36082,7 +36083,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="385" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>376</v>
       </c>
@@ -36171,7 +36172,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="386" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>376</v>
       </c>
@@ -36262,7 +36263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="387" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>376</v>
       </c>
@@ -36351,7 +36352,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="388" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>376</v>
       </c>
@@ -36442,7 +36443,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="389" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>376</v>
       </c>
@@ -36531,7 +36532,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="390" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>376</v>
       </c>
@@ -36623,7 +36624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="391" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>376</v>
       </c>
@@ -36713,7 +36714,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>377</v>
       </c>
@@ -36802,7 +36803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="393" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>377</v>
       </c>
@@ -36889,7 +36890,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="394" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>377</v>
       </c>
@@ -36978,7 +36979,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="395" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>377</v>
       </c>
@@ -37065,7 +37066,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="396" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>377</v>
       </c>
@@ -37157,7 +37158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="397" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>379</v>
       </c>
@@ -37244,7 +37245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="398" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>379</v>
       </c>
@@ -37329,7 +37330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="399" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>379</v>
       </c>
@@ -37416,7 +37417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="400" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>379</v>
       </c>
@@ -37503,7 +37504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="401" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>379</v>
       </c>
@@ -37590,7 +37591,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>379</v>
       </c>
@@ -37675,7 +37676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="403" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>379</v>
       </c>
@@ -37762,7 +37763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="404" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>379</v>
       </c>
@@ -37849,7 +37850,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="405" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>379</v>
       </c>
@@ -37934,7 +37935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="406" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>379</v>
       </c>
@@ -38021,7 +38022,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="407" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>379</v>
       </c>
@@ -38108,7 +38109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="408" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>379</v>
       </c>
@@ -38193,7 +38194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="409" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>379</v>
       </c>
@@ -38284,7 +38285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="410" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>379</v>
       </c>
@@ -38375,7 +38376,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="411" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>379</v>
       </c>
@@ -38464,7 +38465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="412" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>379</v>
       </c>
@@ -38555,7 +38556,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="413" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>379</v>
       </c>
@@ -38646,7 +38647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>379</v>
       </c>
@@ -38735,7 +38736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="415" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>379</v>
       </c>
@@ -38826,7 +38827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="416" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>379</v>
       </c>
@@ -38917,7 +38918,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="417" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>379</v>
       </c>
@@ -39006,7 +39007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="418" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>379</v>
       </c>
@@ -39097,7 +39098,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="419" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>379</v>
       </c>
@@ -39192,7 +39193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="420" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>385</v>
       </c>
@@ -39283,7 +39284,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="421" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>385</v>
       </c>
@@ -39372,7 +39373,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="422" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>385</v>
       </c>
@@ -39463,7 +39464,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="423" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>385</v>
       </c>
@@ -39552,7 +39553,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="424" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>385</v>
       </c>
@@ -39643,7 +39644,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="425" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>385</v>
       </c>
@@ -39732,7 +39733,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="426" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>385</v>
       </c>
@@ -39825,7 +39826,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="427" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>386.1</v>
       </c>
@@ -39918,7 +39919,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="428" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>386.1</v>
       </c>
@@ -40009,7 +40010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="429" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>386.1</v>
       </c>
@@ -40101,7 +40102,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="430" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>386.1</v>
       </c>
@@ -40191,7 +40192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="431" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>386.1</v>
       </c>
@@ -40282,7 +40283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="432" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>386.1</v>
       </c>
@@ -40371,7 +40372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="433" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>386.1</v>
       </c>
@@ -40460,7 +40461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="434" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>386.2</v>
       </c>
@@ -40554,7 +40555,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="435" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>386.2</v>
       </c>
@@ -40646,7 +40647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="436" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>386.2</v>
       </c>
@@ -40738,7 +40739,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="437" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>386.2</v>
       </c>
@@ -40828,7 +40829,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="438" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>386.2</v>
       </c>
@@ -40919,7 +40920,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="439" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>386.2</v>
       </c>
@@ -41008,7 +41009,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="440" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>386.2</v>
       </c>
@@ -41097,7 +41098,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="441" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>386.2</v>
       </c>
@@ -41184,7 +41185,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="442" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>386.3</v>
       </c>
@@ -41277,7 +41278,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="443" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>386.3</v>
       </c>
@@ -41368,7 +41369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="444" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>386.3</v>
       </c>
@@ -41460,7 +41461,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="445" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>386.3</v>
       </c>
@@ -41550,7 +41551,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="446" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>386.3</v>
       </c>
@@ -41641,7 +41642,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="447" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>386.3</v>
       </c>
@@ -41730,7 +41731,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="448" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>386.3</v>
       </c>
@@ -41819,7 +41820,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="449" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>386.3</v>
       </c>
@@ -41906,7 +41907,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="450" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>423</v>
       </c>
@@ -41997,7 +41998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="451" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>423</v>
       </c>
@@ -42086,7 +42087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="452" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>423</v>
       </c>
@@ -42177,7 +42178,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>423</v>
       </c>
@@ -42266,7 +42267,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="454" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>423</v>
       </c>
@@ -42357,7 +42358,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="455" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>423</v>
       </c>
@@ -42446,7 +42447,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="456" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>423</v>
       </c>
@@ -42537,7 +42538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="457" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>424</v>
       </c>
@@ -42628,7 +42629,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="458" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>424</v>
       </c>
@@ -42717,7 +42718,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="459" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>424</v>
       </c>
@@ -42808,7 +42809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="460" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>424</v>
       </c>
@@ -42897,7 +42898,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="461" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>424</v>
       </c>
@@ -42988,7 +42989,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="462" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>424</v>
       </c>
@@ -43077,7 +43078,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="463" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>424</v>
       </c>
@@ -43168,7 +43169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="464" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>460</v>
       </c>
@@ -43251,7 +43252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="465" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>460</v>
       </c>
@@ -43332,7 +43333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="466" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>460</v>
       </c>
@@ -43423,7 +43424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="467" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>460</v>
       </c>
@@ -43512,7 +43513,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="468" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>460</v>
       </c>
@@ -43603,7 +43604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="469" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>466</v>
       </c>
@@ -43693,7 +43694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="470" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>466</v>
       </c>
@@ -43781,7 +43782,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="471" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>466</v>
       </c>
@@ -43871,7 +43872,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="472" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>466</v>
       </c>
@@ -43959,7 +43960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="473" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>466</v>
       </c>
@@ -44049,7 +44050,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="474" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>466</v>
       </c>
@@ -44137,7 +44138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="475" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>466</v>
       </c>
@@ -44228,7 +44229,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="476" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>203</v>
       </c>
@@ -44325,7 +44326,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="477" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>203</v>
       </c>
@@ -44420,7 +44421,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>148</v>
       </c>
@@ -44509,7 +44510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="479" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>466</v>
       </c>
@@ -44598,7 +44599,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="480" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>109</v>
       </c>
@@ -44686,7 +44687,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="481" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>109</v>
       </c>
@@ -44772,7 +44773,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="482" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>386.1</v>
       </c>
@@ -44859,7 +44860,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="483" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>385</v>
       </c>
@@ -44950,7 +44951,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="484" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>423</v>
       </c>
@@ -45039,7 +45040,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="485" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>424</v>
       </c>
@@ -45128,7 +45129,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="486" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>377</v>
       </c>
@@ -45218,7 +45219,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="487" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>367</v>
       </c>
@@ -45307,7 +45308,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="488" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>244</v>
       </c>
@@ -45396,7 +45397,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="489" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>334</v>
       </c>
@@ -45485,7 +45486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="490" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>77</v>
       </c>
@@ -45574,7 +45575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="491" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3">
         <v>96</v>
       </c>
@@ -45665,7 +45666,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="492" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>96</v>
       </c>
@@ -45754,7 +45755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="493" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3">
         <v>193</v>
       </c>
@@ -45843,7 +45844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="494" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>194</v>
       </c>
@@ -45932,7 +45933,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="495" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3">
         <v>200</v>
       </c>
@@ -46023,7 +46024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="496" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>200</v>
       </c>
@@ -46112,7 +46113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="497" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3">
         <v>245</v>
       </c>
@@ -46201,7 +46202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="498" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>276</v>
       </c>
@@ -46290,7 +46291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="499" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3">
         <v>277</v>
       </c>
@@ -46377,7 +46378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="500" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>364</v>
       </c>
@@ -46466,7 +46467,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="501" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3">
         <v>369</v>
       </c>
@@ -46555,7 +46556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="502" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>379</v>
       </c>
@@ -46647,7 +46648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="503" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3">
         <v>98</v>
       </c>
@@ -46736,7 +46737,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="504" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>460</v>
       </c>
@@ -46825,7 +46826,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="505" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3">
         <v>207</v>
       </c>
@@ -46917,7 +46918,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="506" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>331</v>
       </c>
@@ -47002,7 +47003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="507" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3">
         <v>325</v>
       </c>
@@ -47089,7 +47090,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="508" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:29" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>323</v>
       </c>
@@ -47177,6 +47178,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC508" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Utilidad Neta"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC475">
     <sortCondition ref="A2:A475"/>
     <sortCondition ref="F2:F475"/>
